--- a/InitializationResults/WithTrack/Comparison of SPEA2 with SPEA2_SI for each generation (on average).xlsx
+++ b/InitializationResults/WithTrack/Comparison of SPEA2 with SPEA2_SI for each generation (on average).xlsx
@@ -675,214 +675,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>717.8</c:v>
+                  <c:v>438.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>626.20000000000005</c:v>
+                  <c:v>375.7</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>573.20000000000005</c:v>
+                  <c:v>337.4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>549.5</c:v>
+                  <c:v>266.89999999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>468.8</c:v>
+                  <c:v>227.4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>446.4</c:v>
+                  <c:v>216</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>408.2</c:v>
+                  <c:v>197</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>385.9</c:v>
+                  <c:v>188.7</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>353.4</c:v>
+                  <c:v>170.9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>342.1</c:v>
+                  <c:v>163.9</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>297.89999999999998</c:v>
+                  <c:v>150.1</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>292.7</c:v>
+                  <c:v>129.80000000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>270.8</c:v>
+                  <c:v>127.9</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>267.39999999999998</c:v>
+                  <c:v>127.8</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>259.8</c:v>
+                  <c:v>123.2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>248.4</c:v>
+                  <c:v>111.6</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>229.7</c:v>
+                  <c:v>107.2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>223.7</c:v>
+                  <c:v>106.8</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>219.2</c:v>
+                  <c:v>106.1</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>216.9</c:v>
+                  <c:v>93.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>201.6</c:v>
+                  <c:v>84.5</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>195.3</c:v>
+                  <c:v>84.5</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>194.5</c:v>
+                  <c:v>79.099999999999994</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>194.5</c:v>
+                  <c:v>79.099999999999994</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>189.5</c:v>
+                  <c:v>77.400000000000006</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>162.30000000000001</c:v>
+                  <c:v>77.400000000000006</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>158.6</c:v>
+                  <c:v>72.7</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>142.4</c:v>
+                  <c:v>71.400000000000006</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>141.19999999999999</c:v>
+                  <c:v>67.599999999999994</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>133</c:v>
+                  <c:v>66.400000000000006</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>132.6</c:v>
+                  <c:v>58.9</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>131.80000000000001</c:v>
+                  <c:v>57.2</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>124.6</c:v>
+                  <c:v>56.7</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>121.4</c:v>
+                  <c:v>55.7</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>121.4</c:v>
+                  <c:v>55.3</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>106.7</c:v>
+                  <c:v>54.9</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>106.7</c:v>
+                  <c:v>54.9</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>104.7</c:v>
+                  <c:v>54.9</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>101.4</c:v>
+                  <c:v>50.4</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>99.3</c:v>
+                  <c:v>43.9</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>97.2</c:v>
+                  <c:v>43.2</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>96.3</c:v>
+                  <c:v>42.6</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>91.6</c:v>
+                  <c:v>42.3</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>90.8</c:v>
+                  <c:v>42.3</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>90.7</c:v>
+                  <c:v>39.1</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>87.4</c:v>
+                  <c:v>38.700000000000003</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>84.4</c:v>
+                  <c:v>38.299999999999997</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>82.1</c:v>
+                  <c:v>38.1</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>79.400000000000006</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>77.400000000000006</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>75.2</c:v>
+                  <c:v>36.4</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>74.5</c:v>
+                  <c:v>36.299999999999997</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>73.3</c:v>
+                  <c:v>35.6</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>70.2</c:v>
+                  <c:v>35.4</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>69.8</c:v>
+                  <c:v>34.200000000000003</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>66.3</c:v>
+                  <c:v>34.200000000000003</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>63.6</c:v>
+                  <c:v>34.200000000000003</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>63.6</c:v>
+                  <c:v>34.200000000000003</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>63.6</c:v>
+                  <c:v>33.799999999999997</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>63.1</c:v>
+                  <c:v>31.8</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>63.1</c:v>
+                  <c:v>30.6</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>62</c:v>
+                  <c:v>29.7</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>60.8</c:v>
+                  <c:v>29.3</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>60.8</c:v>
+                  <c:v>28.9</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>58.2</c:v>
+                  <c:v>28.9</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>56.7</c:v>
+                  <c:v>28.1</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>56.5</c:v>
+                  <c:v>28.1</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>56.5</c:v>
+                  <c:v>28</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>56.5</c:v>
+                  <c:v>28</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>56.5</c:v>
+                  <c:v>28</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -897,11 +897,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="214114144"/>
-        <c:axId val="243002824"/>
+        <c:axId val="343719704"/>
+        <c:axId val="346466048"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="214114144"/>
+        <c:axId val="343719704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1014,12 +1014,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="243002824"/>
+        <c:crossAx val="346466048"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="243002824"/>
+        <c:axId val="346466048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1076,7 +1076,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="214114144"/>
+        <c:crossAx val="343719704"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1489,214 +1489,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>1.06781992190215E-2</c:v>
+                  <c:v>1.06383523139125E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.6070134032264203E-3</c:v>
+                  <c:v>7.5810539785954702E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.3088430850243502E-3</c:v>
+                  <c:v>6.2869038803537204E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.14319654744808E-3</c:v>
+                  <c:v>5.1250426202196402E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.5209876419255801E-3</c:v>
+                  <c:v>4.5059768851830901E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.5002167601666401E-3</c:v>
+                  <c:v>3.4832735193812002E-3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.88908292407962E-3</c:v>
+                  <c:v>2.87457600733278E-3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.5149211050479901E-3</c:v>
+                  <c:v>2.5010040884948801E-3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.1650362279302198E-3</c:v>
+                  <c:v>2.1536991348774198E-3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.81194548273461E-3</c:v>
+                  <c:v>1.7999949864495901E-3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.6907631656901301E-3</c:v>
+                  <c:v>1.6782209008272E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.4287484182603199E-3</c:v>
+                  <c:v>1.41802598362938E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.2124055910930501E-3</c:v>
+                  <c:v>1.20121949107636E-3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.1255039435876201E-3</c:v>
+                  <c:v>1.11484019260655E-3</c:v>
                 </c:pt>
                 <c:pt idx="14" formatCode="0.00E+00">
-                  <c:v>9.6643318273581102E-4</c:v>
+                  <c:v>9.5723548459934E-4</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00E+00">
-                  <c:v>9.1195662817974499E-4</c:v>
+                  <c:v>9.0294871873444402E-4</c:v>
                 </c:pt>
                 <c:pt idx="16" formatCode="0.00E+00">
-                  <c:v>8.4671781066048002E-4</c:v>
+                  <c:v>8.3926885306566802E-4</c:v>
                 </c:pt>
                 <c:pt idx="17" formatCode="0.00E+00">
-                  <c:v>7.5722430330121999E-4</c:v>
+                  <c:v>7.4997845979743699E-4</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00E+00">
-                  <c:v>7.3875294342389897E-4</c:v>
+                  <c:v>7.3177891081085598E-4</c:v>
                 </c:pt>
                 <c:pt idx="19" formatCode="0.00E+00">
-                  <c:v>7.0918912700350801E-4</c:v>
+                  <c:v>7.04195703866309E-4</c:v>
                 </c:pt>
                 <c:pt idx="20" formatCode="0.00E+00">
-                  <c:v>6.8388166372369895E-4</c:v>
+                  <c:v>6.7935852139595497E-4</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00E+00">
-                  <c:v>6.7336949791291299E-4</c:v>
+                  <c:v>6.6737580397042799E-4</c:v>
                 </c:pt>
                 <c:pt idx="22" formatCode="0.00E+00">
-                  <c:v>6.5123705738613798E-4</c:v>
+                  <c:v>6.4437470837393597E-4</c:v>
                 </c:pt>
                 <c:pt idx="23" formatCode="0.00E+00">
-                  <c:v>6.2364843509593701E-4</c:v>
+                  <c:v>6.1737335842525904E-4</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00E+00">
-                  <c:v>5.8917008964648303E-4</c:v>
+                  <c:v>5.8332341370480399E-4</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="0.00E+00">
-                  <c:v>5.7321345900343199E-4</c:v>
+                  <c:v>5.6668102385006296E-4</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="0.00E+00">
-                  <c:v>5.6408384683349195E-4</c:v>
+                  <c:v>5.5714372536035302E-4</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00E+00">
-                  <c:v>5.4845346216626995E-4</c:v>
+                  <c:v>5.4061174476971398E-4</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="0.00E+00">
-                  <c:v>5.3695263973907404E-4</c:v>
+                  <c:v>5.3013223536924905E-4</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="0.00E+00">
-                  <c:v>5.1609847349489801E-4</c:v>
+                  <c:v>5.0993600629680195E-4</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00E+00">
-                  <c:v>4.8675432350870398E-4</c:v>
+                  <c:v>4.7889329939988399E-4</c:v>
                 </c:pt>
                 <c:pt idx="31" formatCode="0.00E+00">
-                  <c:v>4.72051261406956E-4</c:v>
+                  <c:v>4.6504341579952898E-4</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="0.00E+00">
-                  <c:v>4.6471766609864203E-4</c:v>
+                  <c:v>4.5707094722044998E-4</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00E+00">
-                  <c:v>4.5213620733499901E-4</c:v>
+                  <c:v>4.4372899727806601E-4</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="0.00E+00">
-                  <c:v>4.4560758374261798E-4</c:v>
+                  <c:v>4.3632795608312898E-4</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="0.00E+00">
-                  <c:v>4.5525545576513099E-4</c:v>
+                  <c:v>4.46962550879127E-4</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00E+00">
-                  <c:v>4.4206691557685703E-4</c:v>
+                  <c:v>4.3345505970351998E-4</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="0.00E+00">
-                  <c:v>4.3827225519026402E-4</c:v>
+                  <c:v>4.3111628003847803E-4</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="0.00E+00">
-                  <c:v>4.2094980648900698E-4</c:v>
+                  <c:v>4.1353249983020298E-4</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="0.00E+00">
-                  <c:v>4.15425623352167E-4</c:v>
+                  <c:v>4.0872445589815702E-4</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="0.00E+00">
-                  <c:v>4.0858981575244102E-4</c:v>
+                  <c:v>4.0146132370063502E-4</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="0.00E+00">
-                  <c:v>3.9614539811790001E-4</c:v>
+                  <c:v>3.8761300124531302E-4</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00E+00">
-                  <c:v>3.8445909648602498E-4</c:v>
+                  <c:v>3.7493819419275103E-4</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="0.00E+00">
-                  <c:v>3.7787812047388499E-4</c:v>
+                  <c:v>3.6665950189994801E-4</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="0.00E+00">
-                  <c:v>3.7857173997224799E-4</c:v>
+                  <c:v>3.6733870067678399E-4</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00E+00">
-                  <c:v>3.5989340747307299E-4</c:v>
+                  <c:v>3.4827981707836699E-4</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="0.00E+00">
-                  <c:v>3.5426648344953599E-4</c:v>
+                  <c:v>3.4345794781199998E-4</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="0.00E+00">
-                  <c:v>3.5129340434709099E-4</c:v>
+                  <c:v>3.4229131937222798E-4</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00E+00">
-                  <c:v>3.5504880050335599E-4</c:v>
+                  <c:v>3.4546140721874899E-4</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="0.00E+00">
-                  <c:v>3.5334175445693997E-4</c:v>
+                  <c:v>3.4471096962063202E-4</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="0.00E+00">
-                  <c:v>3.5155624913891099E-4</c:v>
+                  <c:v>3.4531297199252799E-4</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00E+00">
-                  <c:v>3.5672541299453799E-4</c:v>
+                  <c:v>3.4998657382968298E-4</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="0.00E+00">
-                  <c:v>3.5837526047046E-4</c:v>
+                  <c:v>3.5101251010564202E-4</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="0.00E+00">
-                  <c:v>3.48869110961332E-4</c:v>
+                  <c:v>3.4101093831140702E-4</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00E+00">
-                  <c:v>3.3913382564382401E-4</c:v>
+                  <c:v>3.3151175073857102E-4</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00E+00">
-                  <c:v>3.2457488414832801E-4</c:v>
+                  <c:v>3.1925096472942599E-4</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00E+00">
-                  <c:v>3.2316240281241802E-4</c:v>
+                  <c:v>3.1761089153413299E-4</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00E+00">
-                  <c:v>3.21743578578844E-4</c:v>
+                  <c:v>3.16854934871136E-4</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="0.00E+00">
-                  <c:v>3.2336879706169701E-4</c:v>
+                  <c:v>3.1767748020337201E-4</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="0.00E+00">
-                  <c:v>3.1850875109979099E-4</c:v>
+                  <c:v>3.1232163065188998E-4</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="0.00E+00">
-                  <c:v>3.2371871778956701E-4</c:v>
+                  <c:v>3.1639879080852399E-4</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="0.00E+00">
-                  <c:v>3.2003331792847099E-4</c:v>
+                  <c:v>3.1211756715020901E-4</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="0.00E+00">
-                  <c:v>3.1821019312708402E-4</c:v>
+                  <c:v>3.1034440173116401E-4</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="0.00E+00">
-                  <c:v>3.1329074916322102E-4</c:v>
+                  <c:v>3.0606112048333701E-4</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="0.00E+00">
-                  <c:v>3.0945618258688002E-4</c:v>
+                  <c:v>3.0265676087775598E-4</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="0.00E+00">
-                  <c:v>3.06429676555956E-4</c:v>
+                  <c:v>2.9961387722659898E-4</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="0.00E+00">
-                  <c:v>2.9673017512174598E-4</c:v>
+                  <c:v>2.9217166176705899E-4</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="0.00E+00">
-                  <c:v>2.9383933622128302E-4</c:v>
+                  <c:v>2.8864145059779098E-4</c:v>
                 </c:pt>
                 <c:pt idx="68" formatCode="0.00E+00">
-                  <c:v>2.9647199923165502E-4</c:v>
+                  <c:v>2.8955412195869398E-4</c:v>
                 </c:pt>
                 <c:pt idx="69" formatCode="0.00E+00">
-                  <c:v>2.9647199923165502E-4</c:v>
+                  <c:v>2.8955412195869398E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1740,214 +1740,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>1.40112913580365E-2</c:v>
+                  <c:v>1.0922005258687899E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.6983549702528192E-3</c:v>
+                  <c:v>8.0870889854810207E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.9021863287374299E-3</c:v>
+                  <c:v>6.3536332778655899E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.5464238772389698E-3</c:v>
+                  <c:v>4.5626268386532703E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.2608613422501799E-3</c:v>
+                  <c:v>3.4088873750394099E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.3976218109198699E-3</c:v>
+                  <c:v>2.82323478039429E-3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.78144555802068E-3</c:v>
+                  <c:v>2.2822973171864902E-3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.4000952593642398E-3</c:v>
+                  <c:v>1.91130874129758E-3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.9389368581487899E-3</c:v>
+                  <c:v>1.56063567460619E-3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.6662959489540899E-3</c:v>
+                  <c:v>1.37017979641644E-3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.4262434512450201E-3</c:v>
+                  <c:v>1.16922732111627E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.3534081022253E-3</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1.2051573279659199E-3</c:v>
+                  <c:v>1.03575950156211E-3</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="0.00E+00">
+                  <c:v>9.7026855783229103E-4</c:v>
                 </c:pt>
                 <c:pt idx="13" formatCode="0.00E+00">
-                  <c:v>1.12310377086171E-3</c:v>
+                  <c:v>9.0182313150035396E-4</c:v>
                 </c:pt>
                 <c:pt idx="14" formatCode="0.00E+00">
-                  <c:v>1.0369411604964399E-3</c:v>
+                  <c:v>8.4284057047047801E-4</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00E+00">
-                  <c:v>9.5325492573456101E-4</c:v>
+                  <c:v>8.0849268787772295E-4</c:v>
                 </c:pt>
                 <c:pt idx="16" formatCode="0.00E+00">
-                  <c:v>8.7647429414077903E-4</c:v>
+                  <c:v>7.6646872313275796E-4</c:v>
                 </c:pt>
                 <c:pt idx="17" formatCode="0.00E+00">
-                  <c:v>7.8440445829697496E-4</c:v>
+                  <c:v>7.40578425652974E-4</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00E+00">
-                  <c:v>7.3391891187808895E-4</c:v>
+                  <c:v>7.1458306061550998E-4</c:v>
                 </c:pt>
                 <c:pt idx="19" formatCode="0.00E+00">
-                  <c:v>6.9739587845491597E-4</c:v>
+                  <c:v>6.9821868185286E-4</c:v>
                 </c:pt>
                 <c:pt idx="20" formatCode="0.00E+00">
-                  <c:v>6.3118187204573096E-4</c:v>
+                  <c:v>6.6646549987467798E-4</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00E+00">
-                  <c:v>6.1402924113447901E-4</c:v>
+                  <c:v>6.4680385897619404E-4</c:v>
                 </c:pt>
                 <c:pt idx="22" formatCode="0.00E+00">
-                  <c:v>6.0486207245796602E-4</c:v>
+                  <c:v>6.1812803158358201E-4</c:v>
                 </c:pt>
                 <c:pt idx="23" formatCode="0.00E+00">
-                  <c:v>5.8553666858782399E-4</c:v>
+                  <c:v>5.9525635907166905E-4</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00E+00">
-                  <c:v>5.5969937980902102E-4</c:v>
+                  <c:v>5.8159001371037398E-4</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="0.00E+00">
-                  <c:v>5.4629309409860401E-4</c:v>
+                  <c:v>5.6020073221486498E-4</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="0.00E+00">
-                  <c:v>5.17177882686277E-4</c:v>
+                  <c:v>5.3868931951656595E-4</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00E+00">
-                  <c:v>5.0561883845297501E-4</c:v>
+                  <c:v>5.2855522554097999E-4</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="0.00E+00">
-                  <c:v>4.9123748786515198E-4</c:v>
+                  <c:v>5.1616230201372004E-4</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="0.00E+00">
-                  <c:v>4.9604813517689303E-4</c:v>
+                  <c:v>5.0006729246403095E-4</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00E+00">
-                  <c:v>4.9002617845334895E-4</c:v>
+                  <c:v>4.8719786797702801E-4</c:v>
                 </c:pt>
                 <c:pt idx="31" formatCode="0.00E+00">
-                  <c:v>4.7442878151700502E-4</c:v>
+                  <c:v>4.7143359059263198E-4</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="0.00E+00">
-                  <c:v>4.7622100323014698E-4</c:v>
+                  <c:v>3.8057015153041798E-4</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00E+00">
-                  <c:v>4.6513443631319599E-4</c:v>
+                  <c:v>3.7369445028088798E-4</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="0.00E+00">
-                  <c:v>4.4289387201258001E-4</c:v>
+                  <c:v>3.6844290072597598E-4</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="0.00E+00">
-                  <c:v>4.4344602020525599E-4</c:v>
+                  <c:v>3.6820191319592602E-4</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00E+00">
-                  <c:v>4.3255043719184498E-4</c:v>
+                  <c:v>3.6779144520681002E-4</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="0.00E+00">
-                  <c:v>4.2806424273099901E-4</c:v>
+                  <c:v>3.6795697023902401E-4</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="0.00E+00">
-                  <c:v>4.1157281180693301E-4</c:v>
+                  <c:v>3.6697157192033602E-4</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="0.00E+00">
-                  <c:v>4.0917431105600099E-4</c:v>
+                  <c:v>3.5964089930351202E-4</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="0.00E+00">
-                  <c:v>3.9923347473694602E-4</c:v>
+                  <c:v>3.5248017675008003E-4</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="0.00E+00">
-                  <c:v>4.0151206039316998E-4</c:v>
+                  <c:v>3.4820992340059003E-4</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00E+00">
-                  <c:v>3.9574931603648998E-4</c:v>
+                  <c:v>3.4408588864611399E-4</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="0.00E+00">
-                  <c:v>4.0996425665791901E-4</c:v>
+                  <c:v>3.4064144432624402E-4</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="0.00E+00">
-                  <c:v>4.0872356638500698E-4</c:v>
+                  <c:v>3.3922988482544899E-4</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00E+00">
-                  <c:v>4.0252393645992199E-4</c:v>
+                  <c:v>3.2792017884209E-4</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="0.00E+00">
-                  <c:v>4.0118151988220903E-4</c:v>
+                  <c:v>3.2778187583548001E-4</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="0.00E+00">
-                  <c:v>3.9471471701426502E-4</c:v>
+                  <c:v>3.27853566781995E-4</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00E+00">
-                  <c:v>3.9482439390904498E-4</c:v>
+                  <c:v>3.3059523947906097E-4</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="0.00E+00">
-                  <c:v>3.9135723937296101E-4</c:v>
+                  <c:v>3.1666884658662099E-4</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="0.00E+00">
-                  <c:v>3.92592535680285E-4</c:v>
+                  <c:v>3.1079372213412899E-4</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00E+00">
-                  <c:v>3.8534015394380499E-4</c:v>
+                  <c:v>3.1294027433858797E-4</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="0.00E+00">
-                  <c:v>3.74176060624665E-4</c:v>
+                  <c:v>3.1133532772313101E-4</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="0.00E+00">
-                  <c:v>3.6227792541459499E-4</c:v>
+                  <c:v>3.1650291388515302E-4</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00E+00">
-                  <c:v>3.5383734694146999E-4</c:v>
+                  <c:v>3.1520524222449501E-4</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00E+00">
-                  <c:v>3.5824967275855703E-4</c:v>
+                  <c:v>3.1704801362872001E-4</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00E+00">
-                  <c:v>3.57091169162113E-4</c:v>
+                  <c:v>3.1606769777886698E-4</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00E+00">
-                  <c:v>3.6422007319308002E-4</c:v>
+                  <c:v>3.1582121565974601E-4</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="0.00E+00">
-                  <c:v>3.6415645174408699E-4</c:v>
+                  <c:v>3.11569460307142E-4</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="0.00E+00">
-                  <c:v>3.6653667858978499E-4</c:v>
+                  <c:v>3.0277785548266502E-4</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="0.00E+00">
-                  <c:v>3.6002679451843103E-4</c:v>
+                  <c:v>3.0864410596062798E-4</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="0.00E+00">
-                  <c:v>3.5698340583257898E-4</c:v>
+                  <c:v>3.0721391337254299E-4</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="0.00E+00">
-                  <c:v>3.5524476009695099E-4</c:v>
+                  <c:v>3.0793946533693898E-4</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="0.00E+00">
-                  <c:v>3.5439067254422002E-4</c:v>
+                  <c:v>3.0629558161670802E-4</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="0.00E+00">
-                  <c:v>3.5563085508972099E-4</c:v>
+                  <c:v>3.0854584300282002E-4</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="0.00E+00">
-                  <c:v>3.5695721257338801E-4</c:v>
+                  <c:v>3.0825622966724201E-4</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="0.00E+00">
-                  <c:v>3.5581290282943502E-4</c:v>
+                  <c:v>3.1048046448416198E-4</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="0.00E+00">
-                  <c:v>3.5399873888567498E-4</c:v>
+                  <c:v>3.1209820508750402E-4</c:v>
                 </c:pt>
                 <c:pt idx="68" formatCode="0.00E+00">
-                  <c:v>3.5403581663122097E-4</c:v>
+                  <c:v>3.1497390436151701E-4</c:v>
                 </c:pt>
                 <c:pt idx="69" formatCode="0.00E+00">
-                  <c:v>3.5403581663122097E-4</c:v>
+                  <c:v>3.1497390436151701E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1962,11 +1962,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="243003216"/>
-        <c:axId val="242993024"/>
+        <c:axId val="346471536"/>
+        <c:axId val="346474672"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="243003216"/>
+        <c:axId val="346471536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2079,12 +2079,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="242993024"/>
+        <c:crossAx val="346474672"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="242993024"/>
+        <c:axId val="346474672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2141,7 +2141,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="243003216"/>
+        <c:crossAx val="346471536"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2554,214 +2554,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>0.69368489072778095</c:v>
+                  <c:v>0.69425629338408201</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.70085050498079704</c:v>
+                  <c:v>0.70141418729654004</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.72039635686076398</c:v>
+                  <c:v>0.72091290943217901</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.73638279729770695</c:v>
+                  <c:v>0.73686820114812002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.74857058909023999</c:v>
+                  <c:v>0.74902749170497596</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.761700612627081</c:v>
+                  <c:v>0.76212710247193005</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.77105462513057099</c:v>
+                  <c:v>0.771461098885034</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.775098052747202</c:v>
+                  <c:v>0.77549909805487904</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.78010010215679404</c:v>
+                  <c:v>0.78049096619076297</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.78459690936486004</c:v>
+                  <c:v>0.78497928528354499</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.79263054268575095</c:v>
+                  <c:v>0.79298986323327103</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.79634449634190796</c:v>
+                  <c:v>0.79669637472882904</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.80011501788528105</c:v>
+                  <c:v>0.800457812202234</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.80245871642131195</c:v>
+                  <c:v>0.80279777894382298</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.80662814090318302</c:v>
+                  <c:v>0.80695427099078199</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.80952099756057505</c:v>
+                  <c:v>0.80983874630933395</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.81029263686866904</c:v>
+                  <c:v>0.81060953738438501</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.81155725851733496</c:v>
+                  <c:v>0.81187163402173501</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.81232678045072304</c:v>
+                  <c:v>0.81263931854195504</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.81291164639737801</c:v>
+                  <c:v>0.81322306368959496</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.81465625859366597</c:v>
+                  <c:v>0.81496328261034101</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.816382572490022</c:v>
+                  <c:v>0.81668256491785896</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.81850998512086803</c:v>
+                  <c:v>0.81880368922965296</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.81984866260339795</c:v>
+                  <c:v>0.82013710610059498</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.82051038140976296</c:v>
+                  <c:v>0.82079791469243801</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.82121510122096697</c:v>
+                  <c:v>0.82150033545571099</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.82240564089534096</c:v>
+                  <c:v>0.82268578633690204</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.82308463852492697</c:v>
+                  <c:v>0.82336228433591496</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.82345881261808895</c:v>
+                  <c:v>0.82373501870459198</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.82389781497386405</c:v>
+                  <c:v>0.82417366946778703</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.824476799324113</c:v>
+                  <c:v>0.82475130592777601</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.82459003966025801</c:v>
+                  <c:v>0.82486439496581399</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.82509839257277195</c:v>
+                  <c:v>0.82537021518765896</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.82609826396186403</c:v>
+                  <c:v>0.82636705381127196</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.82650372814790796</c:v>
+                  <c:v>0.82677106257227995</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.82700852596215002</c:v>
+                  <c:v>0.82727406339982401</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.82716871450783302</c:v>
+                  <c:v>0.82743403792085302</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.827576975719724</c:v>
+                  <c:v>0.82784044838811599</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.82782342767936701</c:v>
+                  <c:v>0.82808602285275701</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.82812412102809196</c:v>
+                  <c:v>0.82838527023111197</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.82828943309775505</c:v>
+                  <c:v>0.82855049195819996</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.82855520283404005</c:v>
+                  <c:v>0.82881551502241102</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.82947220906487296</c:v>
+                  <c:v>0.829726127170346</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.82969568358788803</c:v>
+                  <c:v>0.82994859826502798</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.82989604997213395</c:v>
+                  <c:v>0.83014833146679001</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.83061240227400801</c:v>
+                  <c:v>0.83086171654122898</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.83078092961637295</c:v>
+                  <c:v>0.83102957492409801</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.83083253082217901</c:v>
+                  <c:v>0.83108084613155597</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.83103430878956197</c:v>
+                  <c:v>0.83128188460845698</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.83122670234312301</c:v>
+                  <c:v>0.83147342068234498</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.83135507798735397</c:v>
+                  <c:v>0.83160112880194004</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.83196987472461004</c:v>
+                  <c:v>0.832208760484622</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.83207482854492898</c:v>
+                  <c:v>0.83231297365171597</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.832209634734564</c:v>
+                  <c:v>0.83244757362404398</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.83235178638460094</c:v>
+                  <c:v>0.83258943092614501</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.83257249002219802</c:v>
+                  <c:v>0.83280955252557698</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.83275029721667104</c:v>
+                  <c:v>0.83298712215547899</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.83299544215489096</c:v>
+                  <c:v>0.83323126081746701</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.83305187933996405</c:v>
+                  <c:v>0.83328759649246398</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.83326413961916501</c:v>
+                  <c:v>0.83349871169343703</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.83356872789173198</c:v>
+                  <c:v>0.833800491305562</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.83365930447639103</c:v>
+                  <c:v>0.83389071192316599</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.83385031258724296</c:v>
+                  <c:v>0.834081125460435</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.83395589377784596</c:v>
+                  <c:v>0.83418651337515404</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.83408902698005905</c:v>
+                  <c:v>0.83431907711826503</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.83421923245428298</c:v>
+                  <c:v>0.83444887367808196</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.83445290174440301</c:v>
+                  <c:v>0.83468066443725597</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.83449062238268901</c:v>
+                  <c:v>0.83471833467776702</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.834589407061889</c:v>
+                  <c:v>0.83481696126726501</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.834589407061889</c:v>
+                  <c:v>0.83481696126726501</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2805,214 +2805,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>0.69636862395738897</c:v>
+                  <c:v>0.74241248782830904</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.71971040587720503</c:v>
+                  <c:v>0.75927961865081495</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.73317554970707</c:v>
+                  <c:v>0.77059329976165603</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.74505684497575697</c:v>
+                  <c:v>0.78319868114999902</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.76121045345278404</c:v>
+                  <c:v>0.79420635355726599</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.76978770312419897</c:v>
+                  <c:v>0.799583538914167</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.77824086418165295</c:v>
+                  <c:v>0.80443430680753103</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.78446874284405699</c:v>
+                  <c:v>0.80824025416317502</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.79123213432415995</c:v>
+                  <c:v>0.81290032135873902</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.79534695145095002</c:v>
+                  <c:v>0.81581541843205096</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.801463602590202</c:v>
+                  <c:v>0.81890001853490701</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.80346229975124706</c:v>
+                  <c:v>0.82123656545563195</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.80697000542675201</c:v>
+                  <c:v>0.82255886138238998</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.80900244988095604</c:v>
+                  <c:v>0.82392449244376198</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.81128618227407101</c:v>
+                  <c:v>0.82493062462636502</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.81320711166040804</c:v>
+                  <c:v>0.82622785927045495</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.81568020531738095</c:v>
+                  <c:v>0.82689135672908498</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.81725161103460697</c:v>
+                  <c:v>0.82753258619384396</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.81816359830317198</c:v>
+                  <c:v>0.82801044742221197</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.81883373432750595</c:v>
+                  <c:v>0.82844455582792198</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.82014313453014598</c:v>
+                  <c:v>0.82915530424658201</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.82088831972462595</c:v>
+                  <c:v>0.82939576203267895</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.821365147280402</c:v>
+                  <c:v>0.82992385024839299</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.82165303181917504</c:v>
+                  <c:v>0.83014193561860805</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.82259863567875702</c:v>
+                  <c:v>0.83054114096710396</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.82450895205113395</c:v>
+                  <c:v>0.83087675331083</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.82507881339184597</c:v>
+                  <c:v>0.83138244300516095</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.82669374292247899</c:v>
+                  <c:v>0.83161204090210195</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.82703150339877796</c:v>
+                  <c:v>0.83192188711458503</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.82787231028061203</c:v>
+                  <c:v>0.83214464536979704</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.828043948333965</c:v>
+                  <c:v>0.83241676913076501</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.82849202141842104</c:v>
+                  <c:v>0.83268777035511299</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.82893978081773501</c:v>
+                  <c:v>0.83282811353805197</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.82922978273121395</c:v>
+                  <c:v>0.83289405603807198</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.82950070213190796</c:v>
+                  <c:v>0.83316552716146997</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.83008078438015298</c:v>
+                  <c:v>0.83317249733071197</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.83019478278872305</c:v>
+                  <c:v>0.83335714155186702</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.83033411127248402</c:v>
+                  <c:v>0.83346083260890502</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.83090109716606297</c:v>
+                  <c:v>0.83367941398367296</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.83103653072598205</c:v>
+                  <c:v>0.83386157818206497</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.83123182586710398</c:v>
+                  <c:v>0.83401317283670195</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.83126013595114001</c:v>
+                  <c:v>0.834177533082198</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.83154841259634005</c:v>
+                  <c:v>0.83429088317526401</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.83168036947927104</c:v>
+                  <c:v>0.83427634241021598</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.83188938834534198</c:v>
+                  <c:v>0.83438186085244903</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.83205587673428605</c:v>
+                  <c:v>0.83448260198767299</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.83223020725177299</c:v>
+                  <c:v>0.834503512495399</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.83241177866794602</c:v>
+                  <c:v>0.83455050240040096</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.83237003240367502</c:v>
+                  <c:v>0.834554731491851</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.83250065612475399</c:v>
+                  <c:v>0.83461406929966697</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.83248931117879699</c:v>
+                  <c:v>0.83473452008948901</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.83252904463007604</c:v>
+                  <c:v>0.83481667410673499</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.83260879907734697</c:v>
+                  <c:v>0.83487394957983196</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.83273327979773504</c:v>
+                  <c:v>0.83492958040625298</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.83291568770762003</c:v>
+                  <c:v>0.83499212919091204</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.83309101156138798</c:v>
+                  <c:v>0.83508480372577698</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.83329642304832896</c:v>
+                  <c:v>0.83518118524203699</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.83352622355503503</c:v>
+                  <c:v>0.83520063384160703</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.83358571917024005</c:v>
+                  <c:v>0.83523407499066704</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.83361159819442798</c:v>
+                  <c:v>0.835346067597589</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.83369025474370295</c:v>
+                  <c:v>0.83533499886440998</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.83383266779802401</c:v>
+                  <c:v>0.83529229026186402</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.83390583485731995</c:v>
+                  <c:v>0.83528158700572497</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.83390037150776897</c:v>
+                  <c:v>0.83522650439486101</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.833981903504176</c:v>
+                  <c:v>0.83527665306569998</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.83401562465690604</c:v>
+                  <c:v>0.83533988059343001</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.83402085274260096</c:v>
+                  <c:v>0.83534995731750294</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.834043960881371</c:v>
+                  <c:v>0.83539282255306602</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.83405624688275304</c:v>
+                  <c:v>0.83534799940479398</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.83405624688275304</c:v>
+                  <c:v>0.83534799940479398</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3027,11 +3027,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="243000864"/>
-        <c:axId val="242995376"/>
+        <c:axId val="346472320"/>
+        <c:axId val="346466832"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="243000864"/>
+        <c:axId val="346472320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3144,12 +3144,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="242995376"/>
+        <c:crossAx val="346466832"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="242995376"/>
+        <c:axId val="346466832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0.65000000000000013"/>
@@ -3207,7 +3207,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="243000864"/>
+        <c:crossAx val="346472320"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3620,214 +3620,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>0.22705846104178001</c:v>
+                  <c:v>0.20689670811171099</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.232761277371657</c:v>
+                  <c:v>0.21150055103502</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.20436656297514799</c:v>
+                  <c:v>0.184356912631786</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.20510957914783401</c:v>
+                  <c:v>0.184238732988981</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.19190928448911601</c:v>
+                  <c:v>0.171947391045396</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.16900183213400799</c:v>
+                  <c:v>0.15008252837397501</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.158264438959791</c:v>
+                  <c:v>0.13934777445180699</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.15404905232260699</c:v>
+                  <c:v>0.135293462500226</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.15094150046784599</c:v>
+                  <c:v>0.13225062366019999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.16278480906746001</c:v>
+                  <c:v>0.14287431528126401</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.13100523463202099</c:v>
+                  <c:v>0.113534608659102</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.130221607516642</c:v>
+                  <c:v>0.112653039370742</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.124027549675437</c:v>
+                  <c:v>0.107266967844664</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.12183996970809401</c:v>
+                  <c:v>0.105081440969646</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.11138332208724799</c:v>
+                  <c:v>9.5692205881676207E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.10440363424996101</c:v>
+                  <c:v>8.94335803147112E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.104240086017603</c:v>
+                  <c:v>8.9210131841901005E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.102456924382116</c:v>
+                  <c:v>8.7510674506344296E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.10048737349672</c:v>
+                  <c:v>8.5705867646785797E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>9.9741531242611606E-2</c:v>
+                  <c:v>8.5140029293306801E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>9.4483384704428006E-2</c:v>
+                  <c:v>8.0236298839995904E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>8.5575835333582803E-2</c:v>
+                  <c:v>7.2378565466757805E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>8.3064175421297001E-2</c:v>
+                  <c:v>7.0068228089801607E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>7.5441233082178705E-2</c:v>
+                  <c:v>6.3238193289494801E-2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>7.5043750420236005E-2</c:v>
+                  <c:v>6.2863364551558096E-2</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>7.2077589389001995E-2</c:v>
+                  <c:v>6.02806564643645E-2</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>6.8033507929230796E-2</c:v>
+                  <c:v>5.7045943611740701E-2</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>6.5819057002055897E-2</c:v>
+                  <c:v>5.5229037692836297E-2</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>6.3665696215743306E-2</c:v>
+                  <c:v>5.3524914720911899E-2</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>6.3178903683248896E-2</c:v>
+                  <c:v>5.3021046470156701E-2</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>6.2442702003366997E-2</c:v>
+                  <c:v>5.2557143621047901E-2</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>6.2391556561641602E-2</c:v>
+                  <c:v>5.2467228642085202E-2</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>5.9967998895956998E-2</c:v>
+                  <c:v>5.0435500444749197E-2</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>5.6151181435308402E-2</c:v>
+                  <c:v>4.6996193581275103E-2</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>5.55663671251325E-2</c:v>
+                  <c:v>4.6576635875247699E-2</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>4.8661599228051203E-2</c:v>
+                  <c:v>4.05625402342027E-2</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>4.8592422205311799E-2</c:v>
+                  <c:v>4.0475999363821999E-2</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>4.5266801612062903E-2</c:v>
+                  <c:v>3.7546501047758703E-2</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>4.4246882054319599E-2</c:v>
+                  <c:v>3.6654382590880899E-2</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>4.3316478494867597E-2</c:v>
+                  <c:v>3.5859342632056E-2</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>4.3288919884169101E-2</c:v>
+                  <c:v>3.5841697297351302E-2</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>4.4958609766982197E-2</c:v>
+                  <c:v>3.7290335481191102E-2</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>4.0608657506717702E-2</c:v>
+                  <c:v>3.3820711211019601E-2</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>3.9848503634984399E-2</c:v>
+                  <c:v>3.3248005341182801E-2</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>3.8712584118613502E-2</c:v>
+                  <c:v>3.22048557546614E-2</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>3.7563613382074798E-2</c:v>
+                  <c:v>3.1233314658641102E-2</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>3.7298901546513601E-2</c:v>
+                  <c:v>3.10310454193077E-2</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>3.6460757512713E-2</c:v>
+                  <c:v>3.0286599823272201E-2</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>3.4558707164723403E-2</c:v>
+                  <c:v>2.8607938875435699E-2</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>3.3833587327076302E-2</c:v>
+                  <c:v>2.8111089714841501E-2</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>3.3206336919010301E-2</c:v>
+                  <c:v>2.77310851253387E-2</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>2.5374377553603E-2</c:v>
+                  <c:v>2.1687810160028E-2</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>2.48627311504943E-2</c:v>
+                  <c:v>2.1340779399450699E-2</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>2.4997007821845801E-2</c:v>
+                  <c:v>2.1423073122327101E-2</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>2.5026836401864198E-2</c:v>
+                  <c:v>2.1471044193833801E-2</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>2.45345562703232E-2</c:v>
+                  <c:v>2.1180421965927301E-2</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>2.3161149370546901E-2</c:v>
+                  <c:v>1.9908333879016599E-2</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>2.29979904244682E-2</c:v>
+                  <c:v>1.9799130552775601E-2</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>2.29212252983776E-2</c:v>
+                  <c:v>1.9789685995265101E-2</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>2.2071606531093801E-2</c:v>
+                  <c:v>1.91214658959321E-2</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>1.7390404298746401E-2</c:v>
+                  <c:v>1.535015886913E-2</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>1.7264713121366002E-2</c:v>
+                  <c:v>1.5269924438015401E-2</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>1.6676865513127099E-2</c:v>
+                  <c:v>1.4761033838664899E-2</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>1.6661048206211001E-2</c:v>
+                  <c:v>1.4738941472839899E-2</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>1.63783769143435E-2</c:v>
+                  <c:v>1.45491297266364E-2</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>1.6612501287114299E-2</c:v>
+                  <c:v>1.4592903529605201E-2</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>1.53097728581746E-2</c:v>
+                  <c:v>1.35755395924946E-2</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>1.53824238053015E-2</c:v>
+                  <c:v>1.36649998054532E-2</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>1.5187217179679699E-2</c:v>
+                  <c:v>1.34901695137603E-2</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>1.5187217179679699E-2</c:v>
+                  <c:v>1.34901695137603E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3871,214 +3871,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>0.234109042658696</c:v>
+                  <c:v>0.119373200482033</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.18996590305625699</c:v>
+                  <c:v>9.9465607145709303E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.16997031311843599</c:v>
+                  <c:v>9.2098726189586005E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.178114048068584</c:v>
+                  <c:v>7.9296180558503501E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.159336614410857</c:v>
+                  <c:v>6.3678988309036802E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.154327246898325</c:v>
+                  <c:v>5.5052706064113499E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.13570215780092201</c:v>
+                  <c:v>4.8166642965889399E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.13575320202098601</c:v>
+                  <c:v>4.4853545276119802E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.122726237597531</c:v>
+                  <c:v>4.0424528282248601E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.11814586906899199</c:v>
+                  <c:v>3.7298704605417198E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.108471919373894</c:v>
+                  <c:v>3.4776877990154997E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.105051084475143</c:v>
+                  <c:v>2.9723095521513698E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>9.9046116848441307E-2</c:v>
+                  <c:v>2.8884922180892399E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>9.5319197298587899E-2</c:v>
+                  <c:v>2.8518443845116499E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>9.3460173634191193E-2</c:v>
+                  <c:v>2.7257517732615099E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>9.0423356851932604E-2</c:v>
+                  <c:v>2.5166806272539501E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>8.4043630189008206E-2</c:v>
+                  <c:v>2.3018710234849499E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>7.9322540979125694E-2</c:v>
+                  <c:v>2.2765438837354799E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>7.7346799559316795E-2</c:v>
+                  <c:v>2.2840550038611299E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>7.6374846938402005E-2</c:v>
+                  <c:v>2.1341426244348E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>7.0633230093421207E-2</c:v>
+                  <c:v>1.89123461686195E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>6.8148830721828396E-2</c:v>
+                  <c:v>1.8948521865011999E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>6.8220820627370699E-2</c:v>
+                  <c:v>1.8136346038928702E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>6.8161082953630006E-2</c:v>
+                  <c:v>1.8242102354701899E-2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>6.8356743621947394E-2</c:v>
+                  <c:v>1.8308204378322899E-2</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>5.44177955534529E-2</c:v>
+                  <c:v>1.81374360462991E-2</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>5.2851372340958998E-2</c:v>
+                  <c:v>1.69724196494585E-2</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>4.5832033433721997E-2</c:v>
+                  <c:v>1.6529589011411602E-2</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>4.5771340562048998E-2</c:v>
+                  <c:v>1.6529660604745599E-2</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>4.0877231432417303E-2</c:v>
+                  <c:v>1.6904971045586199E-2</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>4.0752045914164203E-2</c:v>
+                  <c:v>1.5486833928566601E-2</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>4.0734873645254903E-2</c:v>
+                  <c:v>1.52972810114376E-2</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>3.8904636899125801E-2</c:v>
+                  <c:v>1.5095387273163599E-2</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>3.7716298636486199E-2</c:v>
+                  <c:v>1.5031602059784399E-2</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>3.7664640975153603E-2</c:v>
+                  <c:v>1.48089462634176E-2</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>3.1422077706536697E-2</c:v>
+                  <c:v>1.4112874129750401E-2</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>3.1434067627933299E-2</c:v>
+                  <c:v>1.3976971131468599E-2</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>3.0841310890813E-2</c:v>
+                  <c:v>1.3821676415756001E-2</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>2.9188438157157499E-2</c:v>
+                  <c:v>1.3291493908073901E-2</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>2.9211199158110698E-2</c:v>
+                  <c:v>1.2006102307381E-2</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>2.8599058894310501E-2</c:v>
+                  <c:v>1.19108353772023E-2</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>2.79101580855118E-2</c:v>
+                  <c:v>1.1717671395947499E-2</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>2.5703941257829901E-2</c:v>
+                  <c:v>1.16755750676809E-2</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>2.54013809040654E-2</c:v>
+                  <c:v>1.1760922035034699E-2</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>2.5336997652667E-2</c:v>
+                  <c:v>1.1527255363824099E-2</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>2.4528236003505299E-2</c:v>
+                  <c:v>1.1456327252177699E-2</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>2.3830463585710199E-2</c:v>
+                  <c:v>1.1111932175548201E-2</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>2.3329310219337599E-2</c:v>
+                  <c:v>1.0899726319140201E-2</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>2.2855012346960201E-2</c:v>
+                  <c:v>1.1146585841051399E-2</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>2.2193084431577501E-2</c:v>
+                  <c:v>1.09315415812936E-2</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>2.2388384917042099E-2</c:v>
+                  <c:v>1.07899784362556E-2</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>2.2298750386182901E-2</c:v>
+                  <c:v>1.06861998500122E-2</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>2.2185788914806499E-2</c:v>
+                  <c:v>1.0553808619354999E-2</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>2.1555100094476899E-2</c:v>
+                  <c:v>1.0687394497913E-2</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>2.1243638028556399E-2</c:v>
+                  <c:v>1.0354702478019799E-2</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>1.9587985985368501E-2</c:v>
+                  <c:v>1.03281977748609E-2</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>1.89491444705037E-2</c:v>
+                  <c:v>1.01957206141788E-2</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>1.8544190336650002E-2</c:v>
+                  <c:v>1.01976375570285E-2</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>1.85088283535642E-2</c:v>
+                  <c:v>1.0217414336975201E-2</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>1.8457277281487799E-2</c:v>
+                  <c:v>1.0067593494196199E-2</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>1.8403778286226399E-2</c:v>
+                  <c:v>9.9146375854633796E-3</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>1.8083786211369999E-2</c:v>
+                  <c:v>9.9637900078251903E-3</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>1.7875228852947501E-2</c:v>
+                  <c:v>1.00110463918555E-2</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>1.78723377970871E-2</c:v>
+                  <c:v>1.0005148925731301E-2</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>1.73222231925803E-2</c:v>
+                  <c:v>9.9184793972403994E-3</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>1.7271314934080802E-2</c:v>
+                  <c:v>9.59099997414521E-3</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>1.72629395309335E-2</c:v>
+                  <c:v>9.6041204877854499E-3</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>1.7267021478822E-2</c:v>
+                  <c:v>9.4792808436466505E-3</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>1.7319321510186499E-2</c:v>
+                  <c:v>9.5163058430269305E-3</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>1.7319321510186499E-2</c:v>
+                  <c:v>9.5163058430269305E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4093,11 +4093,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="242994592"/>
-        <c:axId val="242997336"/>
+        <c:axId val="346469576"/>
+        <c:axId val="346473496"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="242994592"/>
+        <c:axId val="346469576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4210,12 +4210,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="242997336"/>
+        <c:crossAx val="346473496"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="242997336"/>
+        <c:axId val="346473496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4272,7 +4272,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="242994592"/>
+        <c:crossAx val="346469576"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -4685,214 +4685,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>0.76761147728628298</c:v>
+                  <c:v>0.76771750755111101</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.84004348448080002</c:v>
+                  <c:v>0.84029172078523195</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.83176798187120704</c:v>
+                  <c:v>0.83200283543641895</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.814300155568494</c:v>
+                  <c:v>0.81446152776780401</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.82240287656271205</c:v>
+                  <c:v>0.82262943424466295</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.82751571645289501</c:v>
+                  <c:v>0.82779661007531502</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.84623431945016303</c:v>
+                  <c:v>0.84650471551143402</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.83134635260906897</c:v>
+                  <c:v>0.83167634795045098</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.86190761177700204</c:v>
+                  <c:v>0.86220569509672995</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.85317394197989205</c:v>
+                  <c:v>0.85342214911288306</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.85206988323772304</c:v>
+                  <c:v>0.85238662777469199</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.87918432179869799</c:v>
+                  <c:v>0.87946137473936603</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.871270958246533</c:v>
+                  <c:v>0.87153611095483996</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.82900279665050602</c:v>
+                  <c:v>0.82930273579021596</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.81641590570450895</c:v>
+                  <c:v>0.81676503511639997</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.79788783111981698</c:v>
+                  <c:v>0.798290686931456</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.78021719166172399</c:v>
+                  <c:v>0.780651124365491</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.77556645191115403</c:v>
+                  <c:v>0.77604232124692596</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.75594308530131704</c:v>
+                  <c:v>0.75644501057044899</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.74867350143154199</c:v>
+                  <c:v>0.74920197795838195</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.72822976871387701</c:v>
+                  <c:v>0.72877685964977801</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.71299134498682004</c:v>
+                  <c:v>0.71355221829691295</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.71144786886825395</c:v>
+                  <c:v>0.71203387995664902</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.70579325584008701</c:v>
+                  <c:v>0.70641271681094298</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.70539780584219502</c:v>
+                  <c:v>0.70603720778679502</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.70105139193045896</c:v>
+                  <c:v>0.701714199626982</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.69942034665025699</c:v>
+                  <c:v>0.70009356265797695</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.68988742760076804</c:v>
+                  <c:v>0.69057527120504802</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.68503005800439398</c:v>
+                  <c:v>0.68572314436945503</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.68391339947978902</c:v>
+                  <c:v>0.68461025632928696</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.68369733492519502</c:v>
+                  <c:v>0.68439613911465802</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.68300926880799895</c:v>
+                  <c:v>0.68373615810402899</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.67764331678419498</c:v>
+                  <c:v>0.67839887634306495</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.67018096247831904</c:v>
+                  <c:v>0.67093876190771395</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.65983432844716605</c:v>
+                  <c:v>0.66060469284326395</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.65419332864314705</c:v>
+                  <c:v>0.65499780072176295</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.65503492001946095</c:v>
+                  <c:v>0.65582900628761298</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.65832554827050804</c:v>
+                  <c:v>0.65913284413578599</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.65724627329243601</c:v>
+                  <c:v>0.65807038538162799</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.64942781450367604</c:v>
+                  <c:v>0.65026188996391099</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.64697906668442795</c:v>
+                  <c:v>0.64781523725415702</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.64598144805404001</c:v>
+                  <c:v>0.64682072027791604</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.64805261324263197</c:v>
+                  <c:v>0.64890026185244298</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.64435147511229895</c:v>
+                  <c:v>0.64520800386561805</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.64483825137783002</c:v>
+                  <c:v>0.64570769635700898</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.64647977758607</c:v>
+                  <c:v>0.64736271607277096</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.64401996242418502</c:v>
+                  <c:v>0.64490592890669296</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.64171430684896202</c:v>
+                  <c:v>0.64259863031019704</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.64307256453565298</c:v>
+                  <c:v>0.64395496402260999</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.63734463714761802</c:v>
+                  <c:v>0.63823855763806503</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.63082550245563795</c:v>
+                  <c:v>0.63175320892431197</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.62998806007560204</c:v>
+                  <c:v>0.63095600450072198</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.62403952735493295</c:v>
+                  <c:v>0.62499638716074402</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.61852793446951504</c:v>
+                  <c:v>0.61949692429891601</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.61430593990339499</c:v>
+                  <c:v>0.61528336269322004</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.61645023458648496</c:v>
+                  <c:v>0.61743388561663204</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.61035162635837403</c:v>
+                  <c:v>0.61134705954841795</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.60745167997462401</c:v>
+                  <c:v>0.608456464240691</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.60670402396466305</c:v>
+                  <c:v>0.60771758140620102</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.59893204106050002</c:v>
+                  <c:v>0.59994233117439</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.60119597881178399</c:v>
+                  <c:v>0.60220976584931896</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.59972685665803704</c:v>
+                  <c:v>0.60074733808977099</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.590078231206281</c:v>
+                  <c:v>0.59111840449851705</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.58960899248835497</c:v>
+                  <c:v>0.59064203856828601</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.58598585076936205</c:v>
+                  <c:v>0.587024337256005</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.582750855804398</c:v>
+                  <c:v>0.58379151659845396</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.57878005618438799</c:v>
+                  <c:v>0.57982089190990305</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.58035180373404704</c:v>
+                  <c:v>0.58140130410654001</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.57591694300164598</c:v>
+                  <c:v>0.57696909372309102</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.57591694300164598</c:v>
+                  <c:v>0.57696909372309102</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4936,214 +4936,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>0.69411711188485103</c:v>
+                  <c:v>0.66701421116973103</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.80424210838530696</c:v>
+                  <c:v>0.73899085096005901</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.82810369383833604</c:v>
+                  <c:v>0.77538745348101101</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.80968381258928002</c:v>
+                  <c:v>0.78516183876153001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.83541662658596805</c:v>
+                  <c:v>0.80308959846161199</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.84352356259416195</c:v>
+                  <c:v>0.82596452057717495</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.84480626082522703</c:v>
+                  <c:v>0.83893596972796503</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.84566308734857898</c:v>
+                  <c:v>0.85364362187459697</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.85539411295110501</c:v>
+                  <c:v>0.84044337634338995</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.87170165444577397</c:v>
+                  <c:v>0.81840478060594601</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.86079655146923395</c:v>
+                  <c:v>0.78536684283249802</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.82996882038800301</c:v>
+                  <c:v>0.76371007240125599</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.81273575497345796</c:v>
+                  <c:v>0.74275277961987296</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.79466153228319103</c:v>
+                  <c:v>0.72823873838502495</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.78048170176814702</c:v>
+                  <c:v>0.70417912025706397</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.76431019844584203</c:v>
+                  <c:v>0.68789709766645302</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.77020100134218605</c:v>
+                  <c:v>0.69231984599127405</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.76164688187515805</c:v>
+                  <c:v>0.68383636681303195</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.75581987207756995</c:v>
+                  <c:v>0.676594662878655</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.74727491703386995</c:v>
+                  <c:v>0.66062550751193105</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.75064463303107498</c:v>
+                  <c:v>0.65661803374213101</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.73486879788243298</c:v>
+                  <c:v>0.66589933984816896</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.72749290774633102</c:v>
+                  <c:v>0.67363447739359905</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.71590908981648804</c:v>
+                  <c:v>0.67903158689402898</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.70812133906547303</c:v>
+                  <c:v>0.66383082571386298</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.69792973513165002</c:v>
+                  <c:v>0.65501035002130004</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.69646027847965297</c:v>
+                  <c:v>0.66103629440308997</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.68562337220383995</c:v>
+                  <c:v>0.65196850773374004</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.68440746178323997</c:v>
+                  <c:v>0.65204646995820303</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.67191520170899699</c:v>
+                  <c:v>0.64431509987807301</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.667649251706953</c:v>
+                  <c:v>0.63609799676098699</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.65762754733482698</c:v>
+                  <c:v>0.63355567206997598</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.650932219012062</c:v>
+                  <c:v>0.62869424318627798</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.64997763937641195</c:v>
+                  <c:v>0.62622291462129598</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.64746447325742895</c:v>
+                  <c:v>0.61040180973718206</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.64613492525057503</c:v>
+                  <c:v>0.61409591904022398</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.63976142615333897</c:v>
+                  <c:v>0.61179686845173598</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.63909959889572798</c:v>
+                  <c:v>0.61511033251131098</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.63187336788168502</c:v>
+                  <c:v>0.60664776257425701</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.62455005055522606</c:v>
+                  <c:v>0.60802014054188402</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.62341768749568105</c:v>
+                  <c:v>0.60306642974028701</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.62147611774132505</c:v>
+                  <c:v>0.60006292540463702</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.62208713942888405</c:v>
+                  <c:v>0.59770364964266098</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.61466445513277901</c:v>
+                  <c:v>0.60382099947779799</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.60374593507159102</c:v>
+                  <c:v>0.60525583688915396</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.59827703498941298</c:v>
+                  <c:v>0.60219727701604397</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.59947470118794399</c:v>
+                  <c:v>0.597454574095028</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.593238825513979</c:v>
+                  <c:v>0.591069846853432</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.59463975611014297</c:v>
+                  <c:v>0.59238385066855104</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.58753093601934903</c:v>
+                  <c:v>0.58524359838634699</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.591318553834558</c:v>
+                  <c:v>0.58159434954741196</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.59523514966272495</c:v>
+                  <c:v>0.57845712991113496</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.60121182277058205</c:v>
+                  <c:v>0.582732557220208</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.60559039365989098</c:v>
+                  <c:v>0.58277815622320495</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.60779777146742697</c:v>
+                  <c:v>0.57599098937774595</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.60718338459742904</c:v>
+                  <c:v>0.57538057710219703</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.60137180303770599</c:v>
+                  <c:v>0.56602151291208502</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.59084468330164097</c:v>
+                  <c:v>0.56472236270056897</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.58708711657150003</c:v>
+                  <c:v>0.56648774670616397</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.58448581712525605</c:v>
+                  <c:v>0.56734714163703204</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.58662166070071897</c:v>
+                  <c:v>0.56398337275302801</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.57784615970153697</c:v>
+                  <c:v>0.56256926684067199</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.57525253339920701</c:v>
+                  <c:v>0.56904980042366904</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.57108990557694395</c:v>
+                  <c:v>0.57706727927472801</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.56994127077765799</c:v>
+                  <c:v>0.57620998077638896</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.570202770498075</c:v>
+                  <c:v>0.57349459106536205</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.57371369467324795</c:v>
+                  <c:v>0.57194400301579595</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.57582976000942598</c:v>
+                  <c:v>0.56372406312326095</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.56942482302522002</c:v>
+                  <c:v>0.56885973039349103</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.56942482302522002</c:v>
+                  <c:v>0.56885973039349103</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5158,11 +5158,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="242996944"/>
-        <c:axId val="242997728"/>
+        <c:axId val="346474280"/>
+        <c:axId val="346464872"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="242996944"/>
+        <c:axId val="346474280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5275,12 +5275,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="242997728"/>
+        <c:crossAx val="346464872"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="242997728"/>
+        <c:axId val="346464872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5337,7 +5337,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="242996944"/>
+        <c:crossAx val="346474280"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -9375,7 +9375,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>717.8</v>
+        <v>438.3</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -9389,7 +9389,7 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>626.20000000000005</v>
+        <v>375.7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -9403,7 +9403,7 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>573.20000000000005</v>
+        <v>337.4</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -9417,7 +9417,7 @@
         <v>4</v>
       </c>
       <c r="D5">
-        <v>549.5</v>
+        <v>266.89999999999998</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -9431,7 +9431,7 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>468.8</v>
+        <v>227.4</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -9445,7 +9445,7 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>446.4</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -9459,7 +9459,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>408.2</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -9473,7 +9473,7 @@
         <v>8</v>
       </c>
       <c r="D9">
-        <v>385.9</v>
+        <v>188.7</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -9487,7 +9487,7 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>353.4</v>
+        <v>170.9</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -9501,7 +9501,7 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>342.1</v>
+        <v>163.9</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -9515,7 +9515,7 @@
         <v>11</v>
       </c>
       <c r="D12">
-        <v>297.89999999999998</v>
+        <v>150.1</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -9529,7 +9529,7 @@
         <v>12</v>
       </c>
       <c r="D13">
-        <v>292.7</v>
+        <v>129.80000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -9543,7 +9543,7 @@
         <v>13</v>
       </c>
       <c r="D14">
-        <v>270.8</v>
+        <v>127.9</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -9557,7 +9557,7 @@
         <v>14</v>
       </c>
       <c r="D15">
-        <v>267.39999999999998</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -9571,7 +9571,7 @@
         <v>15</v>
       </c>
       <c r="D16">
-        <v>259.8</v>
+        <v>123.2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -9585,7 +9585,7 @@
         <v>16</v>
       </c>
       <c r="D17">
-        <v>248.4</v>
+        <v>111.6</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -9599,7 +9599,7 @@
         <v>17</v>
       </c>
       <c r="D18">
-        <v>229.7</v>
+        <v>107.2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -9613,7 +9613,7 @@
         <v>18</v>
       </c>
       <c r="D19">
-        <v>223.7</v>
+        <v>106.8</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -9627,7 +9627,7 @@
         <v>19</v>
       </c>
       <c r="D20">
-        <v>219.2</v>
+        <v>106.1</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -9641,7 +9641,7 @@
         <v>20</v>
       </c>
       <c r="D21">
-        <v>216.9</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -9655,7 +9655,7 @@
         <v>21</v>
       </c>
       <c r="D22">
-        <v>201.6</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -9669,7 +9669,7 @@
         <v>22</v>
       </c>
       <c r="D23">
-        <v>195.3</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -9683,7 +9683,7 @@
         <v>23</v>
       </c>
       <c r="D24">
-        <v>194.5</v>
+        <v>79.099999999999994</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -9697,7 +9697,7 @@
         <v>24</v>
       </c>
       <c r="D25">
-        <v>194.5</v>
+        <v>79.099999999999994</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -9711,7 +9711,7 @@
         <v>25</v>
       </c>
       <c r="D26">
-        <v>189.5</v>
+        <v>77.400000000000006</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -9725,7 +9725,7 @@
         <v>26</v>
       </c>
       <c r="D27">
-        <v>162.30000000000001</v>
+        <v>77.400000000000006</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -9739,7 +9739,7 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>158.6</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -9753,7 +9753,7 @@
         <v>28</v>
       </c>
       <c r="D29">
-        <v>142.4</v>
+        <v>71.400000000000006</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -9767,7 +9767,7 @@
         <v>29</v>
       </c>
       <c r="D30">
-        <v>141.19999999999999</v>
+        <v>67.599999999999994</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -9781,7 +9781,7 @@
         <v>30</v>
       </c>
       <c r="D31">
-        <v>133</v>
+        <v>66.400000000000006</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -9795,7 +9795,7 @@
         <v>31</v>
       </c>
       <c r="D32">
-        <v>132.6</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -9809,7 +9809,7 @@
         <v>32</v>
       </c>
       <c r="D33">
-        <v>131.80000000000001</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -9823,7 +9823,7 @@
         <v>33</v>
       </c>
       <c r="D34">
-        <v>124.6</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -9837,7 +9837,7 @@
         <v>34</v>
       </c>
       <c r="D35">
-        <v>121.4</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -9851,7 +9851,7 @@
         <v>35</v>
       </c>
       <c r="D36">
-        <v>121.4</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -9865,7 +9865,7 @@
         <v>36</v>
       </c>
       <c r="D37">
-        <v>106.7</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -9879,7 +9879,7 @@
         <v>37</v>
       </c>
       <c r="D38">
-        <v>106.7</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -9893,7 +9893,7 @@
         <v>38</v>
       </c>
       <c r="D39">
-        <v>104.7</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -9907,7 +9907,7 @@
         <v>39</v>
       </c>
       <c r="D40">
-        <v>101.4</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -9921,7 +9921,7 @@
         <v>40</v>
       </c>
       <c r="D41">
-        <v>99.3</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -9935,7 +9935,7 @@
         <v>41</v>
       </c>
       <c r="D42">
-        <v>97.2</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -9949,7 +9949,7 @@
         <v>42</v>
       </c>
       <c r="D43">
-        <v>96.3</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -9963,7 +9963,7 @@
         <v>43</v>
       </c>
       <c r="D44">
-        <v>91.6</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -9977,7 +9977,7 @@
         <v>44</v>
       </c>
       <c r="D45">
-        <v>90.8</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -9991,7 +9991,7 @@
         <v>45</v>
       </c>
       <c r="D46">
-        <v>90.7</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -10005,7 +10005,7 @@
         <v>46</v>
       </c>
       <c r="D47">
-        <v>87.4</v>
+        <v>38.700000000000003</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -10019,7 +10019,7 @@
         <v>47</v>
       </c>
       <c r="D48">
-        <v>84.4</v>
+        <v>38.299999999999997</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -10033,7 +10033,7 @@
         <v>48</v>
       </c>
       <c r="D49">
-        <v>82.1</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -10047,7 +10047,7 @@
         <v>49</v>
       </c>
       <c r="D50">
-        <v>79.400000000000006</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -10061,7 +10061,7 @@
         <v>50</v>
       </c>
       <c r="D51">
-        <v>77.400000000000006</v>
+        <v>37</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -10075,7 +10075,7 @@
         <v>51</v>
       </c>
       <c r="D52">
-        <v>75.2</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -10089,7 +10089,7 @@
         <v>52</v>
       </c>
       <c r="D53">
-        <v>74.5</v>
+        <v>36.299999999999997</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -10103,7 +10103,7 @@
         <v>53</v>
       </c>
       <c r="D54">
-        <v>73.3</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -10117,7 +10117,7 @@
         <v>54</v>
       </c>
       <c r="D55">
-        <v>70.2</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -10131,7 +10131,7 @@
         <v>55</v>
       </c>
       <c r="D56">
-        <v>69.8</v>
+        <v>34.200000000000003</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -10145,7 +10145,7 @@
         <v>56</v>
       </c>
       <c r="D57">
-        <v>66.3</v>
+        <v>34.200000000000003</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -10159,7 +10159,7 @@
         <v>57</v>
       </c>
       <c r="D58">
-        <v>63.6</v>
+        <v>34.200000000000003</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -10173,7 +10173,7 @@
         <v>58</v>
       </c>
       <c r="D59">
-        <v>63.6</v>
+        <v>34.200000000000003</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -10187,7 +10187,7 @@
         <v>59</v>
       </c>
       <c r="D60">
-        <v>63.6</v>
+        <v>33.799999999999997</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -10201,7 +10201,7 @@
         <v>60</v>
       </c>
       <c r="D61">
-        <v>63.1</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -10215,7 +10215,7 @@
         <v>61</v>
       </c>
       <c r="D62">
-        <v>63.1</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -10229,7 +10229,7 @@
         <v>62</v>
       </c>
       <c r="D63">
-        <v>62</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -10243,7 +10243,7 @@
         <v>63</v>
       </c>
       <c r="D64">
-        <v>60.8</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -10257,7 +10257,7 @@
         <v>64</v>
       </c>
       <c r="D65">
-        <v>60.8</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -10271,7 +10271,7 @@
         <v>65</v>
       </c>
       <c r="D66">
-        <v>58.2</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -10285,7 +10285,7 @@
         <v>66</v>
       </c>
       <c r="D67">
-        <v>56.7</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -10299,7 +10299,7 @@
         <v>67</v>
       </c>
       <c r="D68">
-        <v>56.5</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -10313,7 +10313,7 @@
         <v>68</v>
       </c>
       <c r="D69">
-        <v>56.5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -10327,7 +10327,7 @@
         <v>69</v>
       </c>
       <c r="D70">
-        <v>56.5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -10341,7 +10341,7 @@
         <v>70</v>
       </c>
       <c r="D71">
-        <v>56.5</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -10374,13 +10374,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.06781992190215E-2</v>
+        <v>1.06383523139125E-2</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>1.40112913580365E-2</v>
+        <v>1.0922005258687899E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -10388,13 +10388,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>7.6070134032264203E-3</v>
+        <v>7.5810539785954702E-3</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>8.6983549702528192E-3</v>
+        <v>8.0870889854810207E-3</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -10402,13 +10402,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>6.3088430850243502E-3</v>
+        <v>6.2869038803537204E-3</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4">
-        <v>6.9021863287374299E-3</v>
+        <v>6.3536332778655899E-3</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -10416,13 +10416,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>5.14319654744808E-3</v>
+        <v>5.1250426202196402E-3</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>5.5464238772389698E-3</v>
+        <v>4.5626268386532703E-3</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -10430,13 +10430,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>4.5209876419255801E-3</v>
+        <v>4.5059768851830901E-3</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6">
-        <v>4.2608613422501799E-3</v>
+        <v>3.4088873750394099E-3</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -10444,13 +10444,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>3.5002167601666401E-3</v>
+        <v>3.4832735193812002E-3</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7">
-        <v>3.3976218109198699E-3</v>
+        <v>2.82323478039429E-3</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -10458,13 +10458,13 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2.88908292407962E-3</v>
+        <v>2.87457600733278E-3</v>
       </c>
       <c r="C8">
         <v>7</v>
       </c>
       <c r="D8">
-        <v>2.78144555802068E-3</v>
+        <v>2.2822973171864902E-3</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -10472,13 +10472,13 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>2.5149211050479901E-3</v>
+        <v>2.5010040884948801E-3</v>
       </c>
       <c r="C9">
         <v>8</v>
       </c>
       <c r="D9">
-        <v>2.4000952593642398E-3</v>
+        <v>1.91130874129758E-3</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -10486,13 +10486,13 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>2.1650362279302198E-3</v>
+        <v>2.1536991348774198E-3</v>
       </c>
       <c r="C10">
         <v>9</v>
       </c>
       <c r="D10">
-        <v>1.9389368581487899E-3</v>
+        <v>1.56063567460619E-3</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -10500,13 +10500,13 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1.81194548273461E-3</v>
+        <v>1.7999949864495901E-3</v>
       </c>
       <c r="C11">
         <v>10</v>
       </c>
       <c r="D11">
-        <v>1.6662959489540899E-3</v>
+        <v>1.37017979641644E-3</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -10514,13 +10514,13 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>1.6907631656901301E-3</v>
+        <v>1.6782209008272E-3</v>
       </c>
       <c r="C12">
         <v>11</v>
       </c>
       <c r="D12">
-        <v>1.4262434512450201E-3</v>
+        <v>1.16922732111627E-3</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -10528,13 +10528,13 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1.4287484182603199E-3</v>
+        <v>1.41802598362938E-3</v>
       </c>
       <c r="C13">
         <v>12</v>
       </c>
       <c r="D13">
-        <v>1.3534081022253E-3</v>
+        <v>1.03575950156211E-3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -10542,13 +10542,13 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>1.2124055910930501E-3</v>
+        <v>1.20121949107636E-3</v>
       </c>
       <c r="C14">
         <v>13</v>
       </c>
-      <c r="D14">
-        <v>1.2051573279659199E-3</v>
+      <c r="D14" s="1">
+        <v>9.7026855783229103E-4</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -10556,13 +10556,13 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>1.1255039435876201E-3</v>
+        <v>1.11484019260655E-3</v>
       </c>
       <c r="C15">
         <v>14</v>
       </c>
       <c r="D15" s="1">
-        <v>1.12310377086171E-3</v>
+        <v>9.0182313150035396E-4</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -10570,13 +10570,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>9.6643318273581102E-4</v>
+        <v>9.5723548459934E-4</v>
       </c>
       <c r="C16">
         <v>15</v>
       </c>
       <c r="D16" s="1">
-        <v>1.0369411604964399E-3</v>
+        <v>8.4284057047047801E-4</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -10584,13 +10584,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>9.1195662817974499E-4</v>
+        <v>9.0294871873444402E-4</v>
       </c>
       <c r="C17">
         <v>16</v>
       </c>
       <c r="D17" s="1">
-        <v>9.5325492573456101E-4</v>
+        <v>8.0849268787772295E-4</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -10598,13 +10598,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <v>8.4671781066048002E-4</v>
+        <v>8.3926885306566802E-4</v>
       </c>
       <c r="C18">
         <v>17</v>
       </c>
       <c r="D18" s="1">
-        <v>8.7647429414077903E-4</v>
+        <v>7.6646872313275796E-4</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -10612,13 +10612,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>7.5722430330121999E-4</v>
+        <v>7.4997845979743699E-4</v>
       </c>
       <c r="C19">
         <v>18</v>
       </c>
       <c r="D19" s="1">
-        <v>7.8440445829697496E-4</v>
+        <v>7.40578425652974E-4</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -10626,13 +10626,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="1">
-        <v>7.3875294342389897E-4</v>
+        <v>7.3177891081085598E-4</v>
       </c>
       <c r="C20">
         <v>19</v>
       </c>
       <c r="D20" s="1">
-        <v>7.3391891187808895E-4</v>
+        <v>7.1458306061550998E-4</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -10640,13 +10640,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="1">
-        <v>7.0918912700350801E-4</v>
+        <v>7.04195703866309E-4</v>
       </c>
       <c r="C21">
         <v>20</v>
       </c>
       <c r="D21" s="1">
-        <v>6.9739587845491597E-4</v>
+        <v>6.9821868185286E-4</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -10654,13 +10654,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="1">
-        <v>6.8388166372369895E-4</v>
+        <v>6.7935852139595497E-4</v>
       </c>
       <c r="C22">
         <v>21</v>
       </c>
       <c r="D22" s="1">
-        <v>6.3118187204573096E-4</v>
+        <v>6.6646549987467798E-4</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -10668,13 +10668,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="1">
-        <v>6.7336949791291299E-4</v>
+        <v>6.6737580397042799E-4</v>
       </c>
       <c r="C23">
         <v>22</v>
       </c>
       <c r="D23" s="1">
-        <v>6.1402924113447901E-4</v>
+        <v>6.4680385897619404E-4</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -10682,13 +10682,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="1">
-        <v>6.5123705738613798E-4</v>
+        <v>6.4437470837393597E-4</v>
       </c>
       <c r="C24">
         <v>23</v>
       </c>
       <c r="D24" s="1">
-        <v>6.0486207245796602E-4</v>
+        <v>6.1812803158358201E-4</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -10696,13 +10696,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="1">
-        <v>6.2364843509593701E-4</v>
+        <v>6.1737335842525904E-4</v>
       </c>
       <c r="C25">
         <v>24</v>
       </c>
       <c r="D25" s="1">
-        <v>5.8553666858782399E-4</v>
+        <v>5.9525635907166905E-4</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -10710,13 +10710,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="1">
-        <v>5.8917008964648303E-4</v>
+        <v>5.8332341370480399E-4</v>
       </c>
       <c r="C26">
         <v>25</v>
       </c>
       <c r="D26" s="1">
-        <v>5.5969937980902102E-4</v>
+        <v>5.8159001371037398E-4</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -10724,13 +10724,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <v>5.7321345900343199E-4</v>
+        <v>5.6668102385006296E-4</v>
       </c>
       <c r="C27">
         <v>26</v>
       </c>
       <c r="D27" s="1">
-        <v>5.4629309409860401E-4</v>
+        <v>5.6020073221486498E-4</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -10738,13 +10738,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <v>5.6408384683349195E-4</v>
+        <v>5.5714372536035302E-4</v>
       </c>
       <c r="C28">
         <v>27</v>
       </c>
       <c r="D28" s="1">
-        <v>5.17177882686277E-4</v>
+        <v>5.3868931951656595E-4</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -10752,13 +10752,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="1">
-        <v>5.4845346216626995E-4</v>
+        <v>5.4061174476971398E-4</v>
       </c>
       <c r="C29">
         <v>28</v>
       </c>
       <c r="D29" s="1">
-        <v>5.0561883845297501E-4</v>
+        <v>5.2855522554097999E-4</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -10766,13 +10766,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="1">
-        <v>5.3695263973907404E-4</v>
+        <v>5.3013223536924905E-4</v>
       </c>
       <c r="C30">
         <v>29</v>
       </c>
       <c r="D30" s="1">
-        <v>4.9123748786515198E-4</v>
+        <v>5.1616230201372004E-4</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -10780,13 +10780,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="1">
-        <v>5.1609847349489801E-4</v>
+        <v>5.0993600629680195E-4</v>
       </c>
       <c r="C31">
         <v>30</v>
       </c>
       <c r="D31" s="1">
-        <v>4.9604813517689303E-4</v>
+        <v>5.0006729246403095E-4</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -10794,13 +10794,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="1">
-        <v>4.8675432350870398E-4</v>
+        <v>4.7889329939988399E-4</v>
       </c>
       <c r="C32">
         <v>31</v>
       </c>
       <c r="D32" s="1">
-        <v>4.9002617845334895E-4</v>
+        <v>4.8719786797702801E-4</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -10808,13 +10808,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="1">
-        <v>4.72051261406956E-4</v>
+        <v>4.6504341579952898E-4</v>
       </c>
       <c r="C33">
         <v>32</v>
       </c>
       <c r="D33" s="1">
-        <v>4.7442878151700502E-4</v>
+        <v>4.7143359059263198E-4</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -10822,13 +10822,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="1">
-        <v>4.6471766609864203E-4</v>
+        <v>4.5707094722044998E-4</v>
       </c>
       <c r="C34">
         <v>33</v>
       </c>
       <c r="D34" s="1">
-        <v>4.7622100323014698E-4</v>
+        <v>3.8057015153041798E-4</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -10836,13 +10836,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="1">
-        <v>4.5213620733499901E-4</v>
+        <v>4.4372899727806601E-4</v>
       </c>
       <c r="C35">
         <v>34</v>
       </c>
       <c r="D35" s="1">
-        <v>4.6513443631319599E-4</v>
+        <v>3.7369445028088798E-4</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -10850,13 +10850,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="1">
-        <v>4.4560758374261798E-4</v>
+        <v>4.3632795608312898E-4</v>
       </c>
       <c r="C36">
         <v>35</v>
       </c>
       <c r="D36" s="1">
-        <v>4.4289387201258001E-4</v>
+        <v>3.6844290072597598E-4</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -10864,13 +10864,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="1">
-        <v>4.5525545576513099E-4</v>
+        <v>4.46962550879127E-4</v>
       </c>
       <c r="C37">
         <v>36</v>
       </c>
       <c r="D37" s="1">
-        <v>4.4344602020525599E-4</v>
+        <v>3.6820191319592602E-4</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -10878,13 +10878,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="1">
-        <v>4.4206691557685703E-4</v>
+        <v>4.3345505970351998E-4</v>
       </c>
       <c r="C38">
         <v>37</v>
       </c>
       <c r="D38" s="1">
-        <v>4.3255043719184498E-4</v>
+        <v>3.6779144520681002E-4</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -10892,13 +10892,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="1">
-        <v>4.3827225519026402E-4</v>
+        <v>4.3111628003847803E-4</v>
       </c>
       <c r="C39">
         <v>38</v>
       </c>
       <c r="D39" s="1">
-        <v>4.2806424273099901E-4</v>
+        <v>3.6795697023902401E-4</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -10906,13 +10906,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="1">
-        <v>4.2094980648900698E-4</v>
+        <v>4.1353249983020298E-4</v>
       </c>
       <c r="C40">
         <v>39</v>
       </c>
       <c r="D40" s="1">
-        <v>4.1157281180693301E-4</v>
+        <v>3.6697157192033602E-4</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -10920,13 +10920,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="1">
-        <v>4.15425623352167E-4</v>
+        <v>4.0872445589815702E-4</v>
       </c>
       <c r="C41">
         <v>40</v>
       </c>
       <c r="D41" s="1">
-        <v>4.0917431105600099E-4</v>
+        <v>3.5964089930351202E-4</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -10934,13 +10934,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="1">
-        <v>4.0858981575244102E-4</v>
+        <v>4.0146132370063502E-4</v>
       </c>
       <c r="C42">
         <v>41</v>
       </c>
       <c r="D42" s="1">
-        <v>3.9923347473694602E-4</v>
+        <v>3.5248017675008003E-4</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -10948,13 +10948,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="1">
-        <v>3.9614539811790001E-4</v>
+        <v>3.8761300124531302E-4</v>
       </c>
       <c r="C43">
         <v>42</v>
       </c>
       <c r="D43" s="1">
-        <v>4.0151206039316998E-4</v>
+        <v>3.4820992340059003E-4</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -10962,13 +10962,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="1">
-        <v>3.8445909648602498E-4</v>
+        <v>3.7493819419275103E-4</v>
       </c>
       <c r="C44">
         <v>43</v>
       </c>
       <c r="D44" s="1">
-        <v>3.9574931603648998E-4</v>
+        <v>3.4408588864611399E-4</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -10976,13 +10976,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="1">
-        <v>3.7787812047388499E-4</v>
+        <v>3.6665950189994801E-4</v>
       </c>
       <c r="C45">
         <v>44</v>
       </c>
       <c r="D45" s="1">
-        <v>4.0996425665791901E-4</v>
+        <v>3.4064144432624402E-4</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -10990,13 +10990,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="1">
-        <v>3.7857173997224799E-4</v>
+        <v>3.6733870067678399E-4</v>
       </c>
       <c r="C46">
         <v>45</v>
       </c>
       <c r="D46" s="1">
-        <v>4.0872356638500698E-4</v>
+        <v>3.3922988482544899E-4</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -11004,13 +11004,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="1">
-        <v>3.5989340747307299E-4</v>
+        <v>3.4827981707836699E-4</v>
       </c>
       <c r="C47">
         <v>46</v>
       </c>
       <c r="D47" s="1">
-        <v>4.0252393645992199E-4</v>
+        <v>3.2792017884209E-4</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -11018,13 +11018,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="1">
-        <v>3.5426648344953599E-4</v>
+        <v>3.4345794781199998E-4</v>
       </c>
       <c r="C48">
         <v>47</v>
       </c>
       <c r="D48" s="1">
-        <v>4.0118151988220903E-4</v>
+        <v>3.2778187583548001E-4</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -11032,13 +11032,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="1">
-        <v>3.5129340434709099E-4</v>
+        <v>3.4229131937222798E-4</v>
       </c>
       <c r="C49">
         <v>48</v>
       </c>
       <c r="D49" s="1">
-        <v>3.9471471701426502E-4</v>
+        <v>3.27853566781995E-4</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -11046,13 +11046,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="1">
-        <v>3.5504880050335599E-4</v>
+        <v>3.4546140721874899E-4</v>
       </c>
       <c r="C50">
         <v>49</v>
       </c>
       <c r="D50" s="1">
-        <v>3.9482439390904498E-4</v>
+        <v>3.3059523947906097E-4</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -11060,13 +11060,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="1">
-        <v>3.5334175445693997E-4</v>
+        <v>3.4471096962063202E-4</v>
       </c>
       <c r="C51">
         <v>50</v>
       </c>
       <c r="D51" s="1">
-        <v>3.9135723937296101E-4</v>
+        <v>3.1666884658662099E-4</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -11074,13 +11074,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="1">
-        <v>3.5155624913891099E-4</v>
+        <v>3.4531297199252799E-4</v>
       </c>
       <c r="C52">
         <v>51</v>
       </c>
       <c r="D52" s="1">
-        <v>3.92592535680285E-4</v>
+        <v>3.1079372213412899E-4</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -11088,13 +11088,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="1">
-        <v>3.5672541299453799E-4</v>
+        <v>3.4998657382968298E-4</v>
       </c>
       <c r="C53">
         <v>52</v>
       </c>
       <c r="D53" s="1">
-        <v>3.8534015394380499E-4</v>
+        <v>3.1294027433858797E-4</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -11102,13 +11102,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="1">
-        <v>3.5837526047046E-4</v>
+        <v>3.5101251010564202E-4</v>
       </c>
       <c r="C54">
         <v>53</v>
       </c>
       <c r="D54" s="1">
-        <v>3.74176060624665E-4</v>
+        <v>3.1133532772313101E-4</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -11116,13 +11116,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="1">
-        <v>3.48869110961332E-4</v>
+        <v>3.4101093831140702E-4</v>
       </c>
       <c r="C55">
         <v>54</v>
       </c>
       <c r="D55" s="1">
-        <v>3.6227792541459499E-4</v>
+        <v>3.1650291388515302E-4</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -11130,13 +11130,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="1">
-        <v>3.3913382564382401E-4</v>
+        <v>3.3151175073857102E-4</v>
       </c>
       <c r="C56">
         <v>55</v>
       </c>
       <c r="D56" s="1">
-        <v>3.5383734694146999E-4</v>
+        <v>3.1520524222449501E-4</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -11144,13 +11144,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="1">
-        <v>3.2457488414832801E-4</v>
+        <v>3.1925096472942599E-4</v>
       </c>
       <c r="C57">
         <v>56</v>
       </c>
       <c r="D57" s="1">
-        <v>3.5824967275855703E-4</v>
+        <v>3.1704801362872001E-4</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -11158,13 +11158,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="1">
-        <v>3.2316240281241802E-4</v>
+        <v>3.1761089153413299E-4</v>
       </c>
       <c r="C58">
         <v>57</v>
       </c>
       <c r="D58" s="1">
-        <v>3.57091169162113E-4</v>
+        <v>3.1606769777886698E-4</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -11172,13 +11172,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="1">
-        <v>3.21743578578844E-4</v>
+        <v>3.16854934871136E-4</v>
       </c>
       <c r="C59">
         <v>58</v>
       </c>
       <c r="D59" s="1">
-        <v>3.6422007319308002E-4</v>
+        <v>3.1582121565974601E-4</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -11186,13 +11186,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="1">
-        <v>3.2336879706169701E-4</v>
+        <v>3.1767748020337201E-4</v>
       </c>
       <c r="C60">
         <v>59</v>
       </c>
       <c r="D60" s="1">
-        <v>3.6415645174408699E-4</v>
+        <v>3.11569460307142E-4</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -11200,13 +11200,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="1">
-        <v>3.1850875109979099E-4</v>
+        <v>3.1232163065188998E-4</v>
       </c>
       <c r="C61">
         <v>60</v>
       </c>
       <c r="D61" s="1">
-        <v>3.6653667858978499E-4</v>
+        <v>3.0277785548266502E-4</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -11214,13 +11214,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="1">
-        <v>3.2371871778956701E-4</v>
+        <v>3.1639879080852399E-4</v>
       </c>
       <c r="C62">
         <v>61</v>
       </c>
       <c r="D62" s="1">
-        <v>3.6002679451843103E-4</v>
+        <v>3.0864410596062798E-4</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -11228,13 +11228,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="1">
-        <v>3.2003331792847099E-4</v>
+        <v>3.1211756715020901E-4</v>
       </c>
       <c r="C63">
         <v>62</v>
       </c>
       <c r="D63" s="1">
-        <v>3.5698340583257898E-4</v>
+        <v>3.0721391337254299E-4</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -11242,13 +11242,13 @@
         <v>63</v>
       </c>
       <c r="B64" s="1">
-        <v>3.1821019312708402E-4</v>
+        <v>3.1034440173116401E-4</v>
       </c>
       <c r="C64">
         <v>63</v>
       </c>
       <c r="D64" s="1">
-        <v>3.5524476009695099E-4</v>
+        <v>3.0793946533693898E-4</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -11256,13 +11256,13 @@
         <v>64</v>
       </c>
       <c r="B65" s="1">
-        <v>3.1329074916322102E-4</v>
+        <v>3.0606112048333701E-4</v>
       </c>
       <c r="C65">
         <v>64</v>
       </c>
       <c r="D65" s="1">
-        <v>3.5439067254422002E-4</v>
+        <v>3.0629558161670802E-4</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -11270,13 +11270,13 @@
         <v>65</v>
       </c>
       <c r="B66" s="1">
-        <v>3.0945618258688002E-4</v>
+        <v>3.0265676087775598E-4</v>
       </c>
       <c r="C66">
         <v>65</v>
       </c>
       <c r="D66" s="1">
-        <v>3.5563085508972099E-4</v>
+        <v>3.0854584300282002E-4</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -11284,13 +11284,13 @@
         <v>66</v>
       </c>
       <c r="B67" s="1">
-        <v>3.06429676555956E-4</v>
+        <v>2.9961387722659898E-4</v>
       </c>
       <c r="C67">
         <v>66</v>
       </c>
       <c r="D67" s="1">
-        <v>3.5695721257338801E-4</v>
+        <v>3.0825622966724201E-4</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -11298,13 +11298,13 @@
         <v>67</v>
       </c>
       <c r="B68" s="1">
-        <v>2.9673017512174598E-4</v>
+        <v>2.9217166176705899E-4</v>
       </c>
       <c r="C68">
         <v>67</v>
       </c>
       <c r="D68" s="1">
-        <v>3.5581290282943502E-4</v>
+        <v>3.1048046448416198E-4</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -11312,13 +11312,13 @@
         <v>68</v>
       </c>
       <c r="B69" s="1">
-        <v>2.9383933622128302E-4</v>
+        <v>2.8864145059779098E-4</v>
       </c>
       <c r="C69">
         <v>68</v>
       </c>
       <c r="D69" s="1">
-        <v>3.5399873888567498E-4</v>
+        <v>3.1209820508750402E-4</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -11326,13 +11326,13 @@
         <v>69</v>
       </c>
       <c r="B70" s="1">
-        <v>2.9647199923165502E-4</v>
+        <v>2.8955412195869398E-4</v>
       </c>
       <c r="C70">
         <v>69</v>
       </c>
       <c r="D70" s="1">
-        <v>3.5403581663122097E-4</v>
+        <v>3.1497390436151701E-4</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -11340,13 +11340,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="1">
-        <v>2.9647199923165502E-4</v>
+        <v>2.8955412195869398E-4</v>
       </c>
       <c r="C71">
         <v>70</v>
       </c>
       <c r="D71" s="1">
-        <v>3.5403581663122097E-4</v>
+        <v>3.1497390436151701E-4</v>
       </c>
     </row>
   </sheetData>
@@ -11379,13 +11379,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.69368489072778095</v>
+        <v>0.69425629338408201</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0.69636862395738897</v>
+        <v>0.74241248782830904</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -11393,13 +11393,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.70085050498079704</v>
+        <v>0.70141418729654004</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>0.71971040587720503</v>
+        <v>0.75927961865081495</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -11407,13 +11407,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.72039635686076398</v>
+        <v>0.72091290943217901</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4">
-        <v>0.73317554970707</v>
+        <v>0.77059329976165603</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -11421,13 +11421,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.73638279729770695</v>
+        <v>0.73686820114812002</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>0.74505684497575697</v>
+        <v>0.78319868114999902</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -11435,13 +11435,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.74857058909023999</v>
+        <v>0.74902749170497596</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6">
-        <v>0.76121045345278404</v>
+        <v>0.79420635355726599</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -11449,13 +11449,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.761700612627081</v>
+        <v>0.76212710247193005</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7">
-        <v>0.76978770312419897</v>
+        <v>0.799583538914167</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -11463,13 +11463,13 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.77105462513057099</v>
+        <v>0.771461098885034</v>
       </c>
       <c r="C8">
         <v>7</v>
       </c>
       <c r="D8">
-        <v>0.77824086418165295</v>
+        <v>0.80443430680753103</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -11477,13 +11477,13 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.775098052747202</v>
+        <v>0.77549909805487904</v>
       </c>
       <c r="C9">
         <v>8</v>
       </c>
       <c r="D9">
-        <v>0.78446874284405699</v>
+        <v>0.80824025416317502</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -11491,13 +11491,13 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.78010010215679404</v>
+        <v>0.78049096619076297</v>
       </c>
       <c r="C10">
         <v>9</v>
       </c>
       <c r="D10">
-        <v>0.79123213432415995</v>
+        <v>0.81290032135873902</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -11505,13 +11505,13 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.78459690936486004</v>
+        <v>0.78497928528354499</v>
       </c>
       <c r="C11">
         <v>10</v>
       </c>
       <c r="D11">
-        <v>0.79534695145095002</v>
+        <v>0.81581541843205096</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -11519,13 +11519,13 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.79263054268575095</v>
+        <v>0.79298986323327103</v>
       </c>
       <c r="C12">
         <v>11</v>
       </c>
       <c r="D12">
-        <v>0.801463602590202</v>
+        <v>0.81890001853490701</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -11533,13 +11533,13 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.79634449634190796</v>
+        <v>0.79669637472882904</v>
       </c>
       <c r="C13">
         <v>12</v>
       </c>
       <c r="D13">
-        <v>0.80346229975124706</v>
+        <v>0.82123656545563195</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -11547,13 +11547,13 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.80011501788528105</v>
+        <v>0.800457812202234</v>
       </c>
       <c r="C14">
         <v>13</v>
       </c>
       <c r="D14">
-        <v>0.80697000542675201</v>
+        <v>0.82255886138238998</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -11561,13 +11561,13 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0.80245871642131195</v>
+        <v>0.80279777894382298</v>
       </c>
       <c r="C15">
         <v>14</v>
       </c>
       <c r="D15">
-        <v>0.80900244988095604</v>
+        <v>0.82392449244376198</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -11575,13 +11575,13 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0.80662814090318302</v>
+        <v>0.80695427099078199</v>
       </c>
       <c r="C16">
         <v>15</v>
       </c>
       <c r="D16">
-        <v>0.81128618227407101</v>
+        <v>0.82493062462636502</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -11589,13 +11589,13 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.80952099756057505</v>
+        <v>0.80983874630933395</v>
       </c>
       <c r="C17">
         <v>16</v>
       </c>
       <c r="D17">
-        <v>0.81320711166040804</v>
+        <v>0.82622785927045495</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -11603,13 +11603,13 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.81029263686866904</v>
+        <v>0.81060953738438501</v>
       </c>
       <c r="C18">
         <v>17</v>
       </c>
       <c r="D18">
-        <v>0.81568020531738095</v>
+        <v>0.82689135672908498</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -11617,13 +11617,13 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.81155725851733496</v>
+        <v>0.81187163402173501</v>
       </c>
       <c r="C19">
         <v>18</v>
       </c>
       <c r="D19">
-        <v>0.81725161103460697</v>
+        <v>0.82753258619384396</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -11631,13 +11631,13 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.81232678045072304</v>
+        <v>0.81263931854195504</v>
       </c>
       <c r="C20">
         <v>19</v>
       </c>
       <c r="D20">
-        <v>0.81816359830317198</v>
+        <v>0.82801044742221197</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -11645,13 +11645,13 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.81291164639737801</v>
+        <v>0.81322306368959496</v>
       </c>
       <c r="C21">
         <v>20</v>
       </c>
       <c r="D21">
-        <v>0.81883373432750595</v>
+        <v>0.82844455582792198</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -11659,13 +11659,13 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>0.81465625859366597</v>
+        <v>0.81496328261034101</v>
       </c>
       <c r="C22">
         <v>21</v>
       </c>
       <c r="D22">
-        <v>0.82014313453014598</v>
+        <v>0.82915530424658201</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -11673,13 +11673,13 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.816382572490022</v>
+        <v>0.81668256491785896</v>
       </c>
       <c r="C23">
         <v>22</v>
       </c>
       <c r="D23">
-        <v>0.82088831972462595</v>
+        <v>0.82939576203267895</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -11687,13 +11687,13 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>0.81850998512086803</v>
+        <v>0.81880368922965296</v>
       </c>
       <c r="C24">
         <v>23</v>
       </c>
       <c r="D24">
-        <v>0.821365147280402</v>
+        <v>0.82992385024839299</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -11701,13 +11701,13 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0.81984866260339795</v>
+        <v>0.82013710610059498</v>
       </c>
       <c r="C25">
         <v>24</v>
       </c>
       <c r="D25">
-        <v>0.82165303181917504</v>
+        <v>0.83014193561860805</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -11715,13 +11715,13 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>0.82051038140976296</v>
+        <v>0.82079791469243801</v>
       </c>
       <c r="C26">
         <v>25</v>
       </c>
       <c r="D26">
-        <v>0.82259863567875702</v>
+        <v>0.83054114096710396</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -11729,13 +11729,13 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>0.82121510122096697</v>
+        <v>0.82150033545571099</v>
       </c>
       <c r="C27">
         <v>26</v>
       </c>
       <c r="D27">
-        <v>0.82450895205113395</v>
+        <v>0.83087675331083</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -11743,13 +11743,13 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>0.82240564089534096</v>
+        <v>0.82268578633690204</v>
       </c>
       <c r="C28">
         <v>27</v>
       </c>
       <c r="D28">
-        <v>0.82507881339184597</v>
+        <v>0.83138244300516095</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -11757,13 +11757,13 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>0.82308463852492697</v>
+        <v>0.82336228433591496</v>
       </c>
       <c r="C29">
         <v>28</v>
       </c>
       <c r="D29">
-        <v>0.82669374292247899</v>
+        <v>0.83161204090210195</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -11771,13 +11771,13 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>0.82345881261808895</v>
+        <v>0.82373501870459198</v>
       </c>
       <c r="C30">
         <v>29</v>
       </c>
       <c r="D30">
-        <v>0.82703150339877796</v>
+        <v>0.83192188711458503</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -11785,13 +11785,13 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.82389781497386405</v>
+        <v>0.82417366946778703</v>
       </c>
       <c r="C31">
         <v>30</v>
       </c>
       <c r="D31">
-        <v>0.82787231028061203</v>
+        <v>0.83214464536979704</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -11799,13 +11799,13 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>0.824476799324113</v>
+        <v>0.82475130592777601</v>
       </c>
       <c r="C32">
         <v>31</v>
       </c>
       <c r="D32">
-        <v>0.828043948333965</v>
+        <v>0.83241676913076501</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -11813,13 +11813,13 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.82459003966025801</v>
+        <v>0.82486439496581399</v>
       </c>
       <c r="C33">
         <v>32</v>
       </c>
       <c r="D33">
-        <v>0.82849202141842104</v>
+        <v>0.83268777035511299</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -11827,13 +11827,13 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>0.82509839257277195</v>
+        <v>0.82537021518765896</v>
       </c>
       <c r="C34">
         <v>33</v>
       </c>
       <c r="D34">
-        <v>0.82893978081773501</v>
+        <v>0.83282811353805197</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -11841,13 +11841,13 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>0.82609826396186403</v>
+        <v>0.82636705381127196</v>
       </c>
       <c r="C35">
         <v>34</v>
       </c>
       <c r="D35">
-        <v>0.82922978273121395</v>
+        <v>0.83289405603807198</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -11855,13 +11855,13 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>0.82650372814790796</v>
+        <v>0.82677106257227995</v>
       </c>
       <c r="C36">
         <v>35</v>
       </c>
       <c r="D36">
-        <v>0.82950070213190796</v>
+        <v>0.83316552716146997</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -11869,13 +11869,13 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>0.82700852596215002</v>
+        <v>0.82727406339982401</v>
       </c>
       <c r="C37">
         <v>36</v>
       </c>
       <c r="D37">
-        <v>0.83008078438015298</v>
+        <v>0.83317249733071197</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -11883,13 +11883,13 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>0.82716871450783302</v>
+        <v>0.82743403792085302</v>
       </c>
       <c r="C38">
         <v>37</v>
       </c>
       <c r="D38">
-        <v>0.83019478278872305</v>
+        <v>0.83335714155186702</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -11897,13 +11897,13 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>0.827576975719724</v>
+        <v>0.82784044838811599</v>
       </c>
       <c r="C39">
         <v>38</v>
       </c>
       <c r="D39">
-        <v>0.83033411127248402</v>
+        <v>0.83346083260890502</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -11911,13 +11911,13 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>0.82782342767936701</v>
+        <v>0.82808602285275701</v>
       </c>
       <c r="C40">
         <v>39</v>
       </c>
       <c r="D40">
-        <v>0.83090109716606297</v>
+        <v>0.83367941398367296</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -11925,13 +11925,13 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>0.82812412102809196</v>
+        <v>0.82838527023111197</v>
       </c>
       <c r="C41">
         <v>40</v>
       </c>
       <c r="D41">
-        <v>0.83103653072598205</v>
+        <v>0.83386157818206497</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -11939,13 +11939,13 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>0.82828943309775505</v>
+        <v>0.82855049195819996</v>
       </c>
       <c r="C42">
         <v>41</v>
       </c>
       <c r="D42">
-        <v>0.83123182586710398</v>
+        <v>0.83401317283670195</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -11953,13 +11953,13 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>0.82855520283404005</v>
+        <v>0.82881551502241102</v>
       </c>
       <c r="C43">
         <v>42</v>
       </c>
       <c r="D43">
-        <v>0.83126013595114001</v>
+        <v>0.834177533082198</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -11967,13 +11967,13 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>0.82947220906487296</v>
+        <v>0.829726127170346</v>
       </c>
       <c r="C44">
         <v>43</v>
       </c>
       <c r="D44">
-        <v>0.83154841259634005</v>
+        <v>0.83429088317526401</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -11981,13 +11981,13 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>0.82969568358788803</v>
+        <v>0.82994859826502798</v>
       </c>
       <c r="C45">
         <v>44</v>
       </c>
       <c r="D45">
-        <v>0.83168036947927104</v>
+        <v>0.83427634241021598</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -11995,13 +11995,13 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>0.82989604997213395</v>
+        <v>0.83014833146679001</v>
       </c>
       <c r="C46">
         <v>45</v>
       </c>
       <c r="D46">
-        <v>0.83188938834534198</v>
+        <v>0.83438186085244903</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -12009,13 +12009,13 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>0.83061240227400801</v>
+        <v>0.83086171654122898</v>
       </c>
       <c r="C47">
         <v>46</v>
       </c>
       <c r="D47">
-        <v>0.83205587673428605</v>
+        <v>0.83448260198767299</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -12023,13 +12023,13 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>0.83078092961637295</v>
+        <v>0.83102957492409801</v>
       </c>
       <c r="C48">
         <v>47</v>
       </c>
       <c r="D48">
-        <v>0.83223020725177299</v>
+        <v>0.834503512495399</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -12037,13 +12037,13 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>0.83083253082217901</v>
+        <v>0.83108084613155597</v>
       </c>
       <c r="C49">
         <v>48</v>
       </c>
       <c r="D49">
-        <v>0.83241177866794602</v>
+        <v>0.83455050240040096</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -12051,13 +12051,13 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>0.83103430878956197</v>
+        <v>0.83128188460845698</v>
       </c>
       <c r="C50">
         <v>49</v>
       </c>
       <c r="D50">
-        <v>0.83237003240367502</v>
+        <v>0.834554731491851</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -12065,13 +12065,13 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>0.83122670234312301</v>
+        <v>0.83147342068234498</v>
       </c>
       <c r="C51">
         <v>50</v>
       </c>
       <c r="D51">
-        <v>0.83250065612475399</v>
+        <v>0.83461406929966697</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -12079,13 +12079,13 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>0.83135507798735397</v>
+        <v>0.83160112880194004</v>
       </c>
       <c r="C52">
         <v>51</v>
       </c>
       <c r="D52">
-        <v>0.83248931117879699</v>
+        <v>0.83473452008948901</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -12093,13 +12093,13 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>0.83196987472461004</v>
+        <v>0.832208760484622</v>
       </c>
       <c r="C53">
         <v>52</v>
       </c>
       <c r="D53">
-        <v>0.83252904463007604</v>
+        <v>0.83481667410673499</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -12107,13 +12107,13 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>0.83207482854492898</v>
+        <v>0.83231297365171597</v>
       </c>
       <c r="C54">
         <v>53</v>
       </c>
       <c r="D54">
-        <v>0.83260879907734697</v>
+        <v>0.83487394957983196</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -12121,13 +12121,13 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>0.832209634734564</v>
+        <v>0.83244757362404398</v>
       </c>
       <c r="C55">
         <v>54</v>
       </c>
       <c r="D55">
-        <v>0.83273327979773504</v>
+        <v>0.83492958040625298</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -12135,13 +12135,13 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>0.83235178638460094</v>
+        <v>0.83258943092614501</v>
       </c>
       <c r="C56">
         <v>55</v>
       </c>
       <c r="D56">
-        <v>0.83291568770762003</v>
+        <v>0.83499212919091204</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -12149,13 +12149,13 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>0.83257249002219802</v>
+        <v>0.83280955252557698</v>
       </c>
       <c r="C57">
         <v>56</v>
       </c>
       <c r="D57">
-        <v>0.83309101156138798</v>
+        <v>0.83508480372577698</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -12163,13 +12163,13 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>0.83275029721667104</v>
+        <v>0.83298712215547899</v>
       </c>
       <c r="C58">
         <v>57</v>
       </c>
       <c r="D58">
-        <v>0.83329642304832896</v>
+        <v>0.83518118524203699</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -12177,13 +12177,13 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>0.83299544215489096</v>
+        <v>0.83323126081746701</v>
       </c>
       <c r="C59">
         <v>58</v>
       </c>
       <c r="D59">
-        <v>0.83352622355503503</v>
+        <v>0.83520063384160703</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -12191,13 +12191,13 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>0.83305187933996405</v>
+        <v>0.83328759649246398</v>
       </c>
       <c r="C60">
         <v>59</v>
       </c>
       <c r="D60">
-        <v>0.83358571917024005</v>
+        <v>0.83523407499066704</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -12205,13 +12205,13 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>0.83326413961916501</v>
+        <v>0.83349871169343703</v>
       </c>
       <c r="C61">
         <v>60</v>
       </c>
       <c r="D61">
-        <v>0.83361159819442798</v>
+        <v>0.835346067597589</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -12219,13 +12219,13 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>0.83356872789173198</v>
+        <v>0.833800491305562</v>
       </c>
       <c r="C62">
         <v>61</v>
       </c>
       <c r="D62">
-        <v>0.83369025474370295</v>
+        <v>0.83533499886440998</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -12233,13 +12233,13 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>0.83365930447639103</v>
+        <v>0.83389071192316599</v>
       </c>
       <c r="C63">
         <v>62</v>
       </c>
       <c r="D63">
-        <v>0.83383266779802401</v>
+        <v>0.83529229026186402</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -12247,13 +12247,13 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>0.83385031258724296</v>
+        <v>0.834081125460435</v>
       </c>
       <c r="C64">
         <v>63</v>
       </c>
       <c r="D64">
-        <v>0.83390583485731995</v>
+        <v>0.83528158700572497</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -12261,13 +12261,13 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>0.83395589377784596</v>
+        <v>0.83418651337515404</v>
       </c>
       <c r="C65">
         <v>64</v>
       </c>
       <c r="D65">
-        <v>0.83390037150776897</v>
+        <v>0.83522650439486101</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -12275,13 +12275,13 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>0.83408902698005905</v>
+        <v>0.83431907711826503</v>
       </c>
       <c r="C66">
         <v>65</v>
       </c>
       <c r="D66">
-        <v>0.833981903504176</v>
+        <v>0.83527665306569998</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -12289,13 +12289,13 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>0.83421923245428298</v>
+        <v>0.83444887367808196</v>
       </c>
       <c r="C67">
         <v>66</v>
       </c>
       <c r="D67">
-        <v>0.83401562465690604</v>
+        <v>0.83533988059343001</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -12303,13 +12303,13 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>0.83445290174440301</v>
+        <v>0.83468066443725597</v>
       </c>
       <c r="C68">
         <v>67</v>
       </c>
       <c r="D68">
-        <v>0.83402085274260096</v>
+        <v>0.83534995731750294</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -12317,13 +12317,13 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>0.83449062238268901</v>
+        <v>0.83471833467776702</v>
       </c>
       <c r="C69">
         <v>68</v>
       </c>
       <c r="D69">
-        <v>0.834043960881371</v>
+        <v>0.83539282255306602</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -12331,13 +12331,13 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>0.834589407061889</v>
+        <v>0.83481696126726501</v>
       </c>
       <c r="C70">
         <v>69</v>
       </c>
       <c r="D70">
-        <v>0.83405624688275304</v>
+        <v>0.83534799940479398</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -12345,13 +12345,13 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>0.834589407061889</v>
+        <v>0.83481696126726501</v>
       </c>
       <c r="C71">
         <v>70</v>
       </c>
       <c r="D71">
-        <v>0.83405624688275304</v>
+        <v>0.83534799940479398</v>
       </c>
     </row>
   </sheetData>
@@ -12384,13 +12384,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.22705846104178001</v>
+        <v>0.20689670811171099</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0.234109042658696</v>
+        <v>0.119373200482033</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -12398,13 +12398,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.232761277371657</v>
+        <v>0.21150055103502</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>0.18996590305625699</v>
+        <v>9.9465607145709303E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -12412,13 +12412,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.20436656297514799</v>
+        <v>0.184356912631786</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4">
-        <v>0.16997031311843599</v>
+        <v>9.2098726189586005E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -12426,13 +12426,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.20510957914783401</v>
+        <v>0.184238732988981</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>0.178114048068584</v>
+        <v>7.9296180558503501E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -12440,13 +12440,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.19190928448911601</v>
+        <v>0.171947391045396</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6">
-        <v>0.159336614410857</v>
+        <v>6.3678988309036802E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -12454,13 +12454,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.16900183213400799</v>
+        <v>0.15008252837397501</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7">
-        <v>0.154327246898325</v>
+        <v>5.5052706064113499E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -12468,13 +12468,13 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.158264438959791</v>
+        <v>0.13934777445180699</v>
       </c>
       <c r="C8">
         <v>7</v>
       </c>
       <c r="D8">
-        <v>0.13570215780092201</v>
+        <v>4.8166642965889399E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -12482,13 +12482,13 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.15404905232260699</v>
+        <v>0.135293462500226</v>
       </c>
       <c r="C9">
         <v>8</v>
       </c>
       <c r="D9">
-        <v>0.13575320202098601</v>
+        <v>4.4853545276119802E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -12496,13 +12496,13 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.15094150046784599</v>
+        <v>0.13225062366019999</v>
       </c>
       <c r="C10">
         <v>9</v>
       </c>
       <c r="D10">
-        <v>0.122726237597531</v>
+        <v>4.0424528282248601E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -12510,13 +12510,13 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.16278480906746001</v>
+        <v>0.14287431528126401</v>
       </c>
       <c r="C11">
         <v>10</v>
       </c>
       <c r="D11">
-        <v>0.11814586906899199</v>
+        <v>3.7298704605417198E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -12524,13 +12524,13 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.13100523463202099</v>
+        <v>0.113534608659102</v>
       </c>
       <c r="C12">
         <v>11</v>
       </c>
       <c r="D12">
-        <v>0.108471919373894</v>
+        <v>3.4776877990154997E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -12538,13 +12538,13 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.130221607516642</v>
+        <v>0.112653039370742</v>
       </c>
       <c r="C13">
         <v>12</v>
       </c>
       <c r="D13">
-        <v>0.105051084475143</v>
+        <v>2.9723095521513698E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -12552,13 +12552,13 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.124027549675437</v>
+        <v>0.107266967844664</v>
       </c>
       <c r="C14">
         <v>13</v>
       </c>
       <c r="D14">
-        <v>9.9046116848441307E-2</v>
+        <v>2.8884922180892399E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -12566,13 +12566,13 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0.12183996970809401</v>
+        <v>0.105081440969646</v>
       </c>
       <c r="C15">
         <v>14</v>
       </c>
       <c r="D15">
-        <v>9.5319197298587899E-2</v>
+        <v>2.8518443845116499E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -12580,13 +12580,13 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0.11138332208724799</v>
+        <v>9.5692205881676207E-2</v>
       </c>
       <c r="C16">
         <v>15</v>
       </c>
       <c r="D16">
-        <v>9.3460173634191193E-2</v>
+        <v>2.7257517732615099E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -12594,13 +12594,13 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.10440363424996101</v>
+        <v>8.94335803147112E-2</v>
       </c>
       <c r="C17">
         <v>16</v>
       </c>
       <c r="D17">
-        <v>9.0423356851932604E-2</v>
+        <v>2.5166806272539501E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -12608,13 +12608,13 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.104240086017603</v>
+        <v>8.9210131841901005E-2</v>
       </c>
       <c r="C18">
         <v>17</v>
       </c>
       <c r="D18">
-        <v>8.4043630189008206E-2</v>
+        <v>2.3018710234849499E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -12622,13 +12622,13 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.102456924382116</v>
+        <v>8.7510674506344296E-2</v>
       </c>
       <c r="C19">
         <v>18</v>
       </c>
       <c r="D19">
-        <v>7.9322540979125694E-2</v>
+        <v>2.2765438837354799E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -12636,13 +12636,13 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.10048737349672</v>
+        <v>8.5705867646785797E-2</v>
       </c>
       <c r="C20">
         <v>19</v>
       </c>
       <c r="D20">
-        <v>7.7346799559316795E-2</v>
+        <v>2.2840550038611299E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -12650,13 +12650,13 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>9.9741531242611606E-2</v>
+        <v>8.5140029293306801E-2</v>
       </c>
       <c r="C21">
         <v>20</v>
       </c>
       <c r="D21">
-        <v>7.6374846938402005E-2</v>
+        <v>2.1341426244348E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -12664,13 +12664,13 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>9.4483384704428006E-2</v>
+        <v>8.0236298839995904E-2</v>
       </c>
       <c r="C22">
         <v>21</v>
       </c>
       <c r="D22">
-        <v>7.0633230093421207E-2</v>
+        <v>1.89123461686195E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -12678,13 +12678,13 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>8.5575835333582803E-2</v>
+        <v>7.2378565466757805E-2</v>
       </c>
       <c r="C23">
         <v>22</v>
       </c>
       <c r="D23">
-        <v>6.8148830721828396E-2</v>
+        <v>1.8948521865011999E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -12692,13 +12692,13 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>8.3064175421297001E-2</v>
+        <v>7.0068228089801607E-2</v>
       </c>
       <c r="C24">
         <v>23</v>
       </c>
       <c r="D24">
-        <v>6.8220820627370699E-2</v>
+        <v>1.8136346038928702E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -12706,13 +12706,13 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>7.5441233082178705E-2</v>
+        <v>6.3238193289494801E-2</v>
       </c>
       <c r="C25">
         <v>24</v>
       </c>
       <c r="D25">
-        <v>6.8161082953630006E-2</v>
+        <v>1.8242102354701899E-2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -12720,13 +12720,13 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>7.5043750420236005E-2</v>
+        <v>6.2863364551558096E-2</v>
       </c>
       <c r="C26">
         <v>25</v>
       </c>
       <c r="D26">
-        <v>6.8356743621947394E-2</v>
+        <v>1.8308204378322899E-2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -12734,13 +12734,13 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>7.2077589389001995E-2</v>
+        <v>6.02806564643645E-2</v>
       </c>
       <c r="C27">
         <v>26</v>
       </c>
       <c r="D27">
-        <v>5.44177955534529E-2</v>
+        <v>1.81374360462991E-2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -12748,13 +12748,13 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>6.8033507929230796E-2</v>
+        <v>5.7045943611740701E-2</v>
       </c>
       <c r="C28">
         <v>27</v>
       </c>
       <c r="D28">
-        <v>5.2851372340958998E-2</v>
+        <v>1.69724196494585E-2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -12762,13 +12762,13 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>6.5819057002055897E-2</v>
+        <v>5.5229037692836297E-2</v>
       </c>
       <c r="C29">
         <v>28</v>
       </c>
       <c r="D29">
-        <v>4.5832033433721997E-2</v>
+        <v>1.6529589011411602E-2</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -12776,13 +12776,13 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>6.3665696215743306E-2</v>
+        <v>5.3524914720911899E-2</v>
       </c>
       <c r="C30">
         <v>29</v>
       </c>
       <c r="D30">
-        <v>4.5771340562048998E-2</v>
+        <v>1.6529660604745599E-2</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -12790,13 +12790,13 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>6.3178903683248896E-2</v>
+        <v>5.3021046470156701E-2</v>
       </c>
       <c r="C31">
         <v>30</v>
       </c>
       <c r="D31">
-        <v>4.0877231432417303E-2</v>
+        <v>1.6904971045586199E-2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -12804,13 +12804,13 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>6.2442702003366997E-2</v>
+        <v>5.2557143621047901E-2</v>
       </c>
       <c r="C32">
         <v>31</v>
       </c>
       <c r="D32">
-        <v>4.0752045914164203E-2</v>
+        <v>1.5486833928566601E-2</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -12818,13 +12818,13 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>6.2391556561641602E-2</v>
+        <v>5.2467228642085202E-2</v>
       </c>
       <c r="C33">
         <v>32</v>
       </c>
       <c r="D33">
-        <v>4.0734873645254903E-2</v>
+        <v>1.52972810114376E-2</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -12832,13 +12832,13 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>5.9967998895956998E-2</v>
+        <v>5.0435500444749197E-2</v>
       </c>
       <c r="C34">
         <v>33</v>
       </c>
       <c r="D34">
-        <v>3.8904636899125801E-2</v>
+        <v>1.5095387273163599E-2</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -12846,13 +12846,13 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>5.6151181435308402E-2</v>
+        <v>4.6996193581275103E-2</v>
       </c>
       <c r="C35">
         <v>34</v>
       </c>
       <c r="D35">
-        <v>3.7716298636486199E-2</v>
+        <v>1.5031602059784399E-2</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -12860,13 +12860,13 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>5.55663671251325E-2</v>
+        <v>4.6576635875247699E-2</v>
       </c>
       <c r="C36">
         <v>35</v>
       </c>
       <c r="D36">
-        <v>3.7664640975153603E-2</v>
+        <v>1.48089462634176E-2</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -12874,13 +12874,13 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>4.8661599228051203E-2</v>
+        <v>4.05625402342027E-2</v>
       </c>
       <c r="C37">
         <v>36</v>
       </c>
       <c r="D37">
-        <v>3.1422077706536697E-2</v>
+        <v>1.4112874129750401E-2</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -12888,13 +12888,13 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>4.8592422205311799E-2</v>
+        <v>4.0475999363821999E-2</v>
       </c>
       <c r="C38">
         <v>37</v>
       </c>
       <c r="D38">
-        <v>3.1434067627933299E-2</v>
+        <v>1.3976971131468599E-2</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -12902,13 +12902,13 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>4.5266801612062903E-2</v>
+        <v>3.7546501047758703E-2</v>
       </c>
       <c r="C39">
         <v>38</v>
       </c>
       <c r="D39">
-        <v>3.0841310890813E-2</v>
+        <v>1.3821676415756001E-2</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -12916,13 +12916,13 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>4.4246882054319599E-2</v>
+        <v>3.6654382590880899E-2</v>
       </c>
       <c r="C40">
         <v>39</v>
       </c>
       <c r="D40">
-        <v>2.9188438157157499E-2</v>
+        <v>1.3291493908073901E-2</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -12930,13 +12930,13 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>4.3316478494867597E-2</v>
+        <v>3.5859342632056E-2</v>
       </c>
       <c r="C41">
         <v>40</v>
       </c>
       <c r="D41">
-        <v>2.9211199158110698E-2</v>
+        <v>1.2006102307381E-2</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -12944,13 +12944,13 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>4.3288919884169101E-2</v>
+        <v>3.5841697297351302E-2</v>
       </c>
       <c r="C42">
         <v>41</v>
       </c>
       <c r="D42">
-        <v>2.8599058894310501E-2</v>
+        <v>1.19108353772023E-2</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -12958,13 +12958,13 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>4.4958609766982197E-2</v>
+        <v>3.7290335481191102E-2</v>
       </c>
       <c r="C43">
         <v>42</v>
       </c>
       <c r="D43">
-        <v>2.79101580855118E-2</v>
+        <v>1.1717671395947499E-2</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -12972,13 +12972,13 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>4.0608657506717702E-2</v>
+        <v>3.3820711211019601E-2</v>
       </c>
       <c r="C44">
         <v>43</v>
       </c>
       <c r="D44">
-        <v>2.5703941257829901E-2</v>
+        <v>1.16755750676809E-2</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -12986,13 +12986,13 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>3.9848503634984399E-2</v>
+        <v>3.3248005341182801E-2</v>
       </c>
       <c r="C45">
         <v>44</v>
       </c>
       <c r="D45">
-        <v>2.54013809040654E-2</v>
+        <v>1.1760922035034699E-2</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -13000,13 +13000,13 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>3.8712584118613502E-2</v>
+        <v>3.22048557546614E-2</v>
       </c>
       <c r="C46">
         <v>45</v>
       </c>
       <c r="D46">
-        <v>2.5336997652667E-2</v>
+        <v>1.1527255363824099E-2</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -13014,13 +13014,13 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>3.7563613382074798E-2</v>
+        <v>3.1233314658641102E-2</v>
       </c>
       <c r="C47">
         <v>46</v>
       </c>
       <c r="D47">
-        <v>2.4528236003505299E-2</v>
+        <v>1.1456327252177699E-2</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -13028,13 +13028,13 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>3.7298901546513601E-2</v>
+        <v>3.10310454193077E-2</v>
       </c>
       <c r="C48">
         <v>47</v>
       </c>
       <c r="D48">
-        <v>2.3830463585710199E-2</v>
+        <v>1.1111932175548201E-2</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -13042,13 +13042,13 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>3.6460757512713E-2</v>
+        <v>3.0286599823272201E-2</v>
       </c>
       <c r="C49">
         <v>48</v>
       </c>
       <c r="D49">
-        <v>2.3329310219337599E-2</v>
+        <v>1.0899726319140201E-2</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -13056,13 +13056,13 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>3.4558707164723403E-2</v>
+        <v>2.8607938875435699E-2</v>
       </c>
       <c r="C50">
         <v>49</v>
       </c>
       <c r="D50">
-        <v>2.2855012346960201E-2</v>
+        <v>1.1146585841051399E-2</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -13070,13 +13070,13 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>3.3833587327076302E-2</v>
+        <v>2.8111089714841501E-2</v>
       </c>
       <c r="C51">
         <v>50</v>
       </c>
       <c r="D51">
-        <v>2.2193084431577501E-2</v>
+        <v>1.09315415812936E-2</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -13084,13 +13084,13 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>3.3206336919010301E-2</v>
+        <v>2.77310851253387E-2</v>
       </c>
       <c r="C52">
         <v>51</v>
       </c>
       <c r="D52">
-        <v>2.2388384917042099E-2</v>
+        <v>1.07899784362556E-2</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -13098,13 +13098,13 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>2.5374377553603E-2</v>
+        <v>2.1687810160028E-2</v>
       </c>
       <c r="C53">
         <v>52</v>
       </c>
       <c r="D53">
-        <v>2.2298750386182901E-2</v>
+        <v>1.06861998500122E-2</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -13112,13 +13112,13 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>2.48627311504943E-2</v>
+        <v>2.1340779399450699E-2</v>
       </c>
       <c r="C54">
         <v>53</v>
       </c>
       <c r="D54">
-        <v>2.2185788914806499E-2</v>
+        <v>1.0553808619354999E-2</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -13126,13 +13126,13 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>2.4997007821845801E-2</v>
+        <v>2.1423073122327101E-2</v>
       </c>
       <c r="C55">
         <v>54</v>
       </c>
       <c r="D55">
-        <v>2.1555100094476899E-2</v>
+        <v>1.0687394497913E-2</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -13140,13 +13140,13 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>2.5026836401864198E-2</v>
+        <v>2.1471044193833801E-2</v>
       </c>
       <c r="C56">
         <v>55</v>
       </c>
       <c r="D56">
-        <v>2.1243638028556399E-2</v>
+        <v>1.0354702478019799E-2</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -13154,13 +13154,13 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>2.45345562703232E-2</v>
+        <v>2.1180421965927301E-2</v>
       </c>
       <c r="C57">
         <v>56</v>
       </c>
       <c r="D57">
-        <v>1.9587985985368501E-2</v>
+        <v>1.03281977748609E-2</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -13168,13 +13168,13 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>2.3161149370546901E-2</v>
+        <v>1.9908333879016599E-2</v>
       </c>
       <c r="C58">
         <v>57</v>
       </c>
       <c r="D58">
-        <v>1.89491444705037E-2</v>
+        <v>1.01957206141788E-2</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -13182,13 +13182,13 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>2.29979904244682E-2</v>
+        <v>1.9799130552775601E-2</v>
       </c>
       <c r="C59">
         <v>58</v>
       </c>
       <c r="D59">
-        <v>1.8544190336650002E-2</v>
+        <v>1.01976375570285E-2</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -13196,13 +13196,13 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>2.29212252983776E-2</v>
+        <v>1.9789685995265101E-2</v>
       </c>
       <c r="C60">
         <v>59</v>
       </c>
       <c r="D60">
-        <v>1.85088283535642E-2</v>
+        <v>1.0217414336975201E-2</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -13210,13 +13210,13 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>2.2071606531093801E-2</v>
+        <v>1.91214658959321E-2</v>
       </c>
       <c r="C61">
         <v>60</v>
       </c>
       <c r="D61">
-        <v>1.8457277281487799E-2</v>
+        <v>1.0067593494196199E-2</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -13224,13 +13224,13 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>1.7390404298746401E-2</v>
+        <v>1.535015886913E-2</v>
       </c>
       <c r="C62">
         <v>61</v>
       </c>
       <c r="D62">
-        <v>1.8403778286226399E-2</v>
+        <v>9.9146375854633796E-3</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -13238,13 +13238,13 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>1.7264713121366002E-2</v>
+        <v>1.5269924438015401E-2</v>
       </c>
       <c r="C63">
         <v>62</v>
       </c>
       <c r="D63">
-        <v>1.8083786211369999E-2</v>
+        <v>9.9637900078251903E-3</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -13252,13 +13252,13 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>1.6676865513127099E-2</v>
+        <v>1.4761033838664899E-2</v>
       </c>
       <c r="C64">
         <v>63</v>
       </c>
       <c r="D64">
-        <v>1.7875228852947501E-2</v>
+        <v>1.00110463918555E-2</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -13266,13 +13266,13 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>1.6661048206211001E-2</v>
+        <v>1.4738941472839899E-2</v>
       </c>
       <c r="C65">
         <v>64</v>
       </c>
       <c r="D65">
-        <v>1.78723377970871E-2</v>
+        <v>1.0005148925731301E-2</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -13280,13 +13280,13 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>1.63783769143435E-2</v>
+        <v>1.45491297266364E-2</v>
       </c>
       <c r="C66">
         <v>65</v>
       </c>
       <c r="D66">
-        <v>1.73222231925803E-2</v>
+        <v>9.9184793972403994E-3</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -13294,13 +13294,13 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>1.6612501287114299E-2</v>
+        <v>1.4592903529605201E-2</v>
       </c>
       <c r="C67">
         <v>66</v>
       </c>
       <c r="D67">
-        <v>1.7271314934080802E-2</v>
+        <v>9.59099997414521E-3</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -13308,13 +13308,13 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>1.53097728581746E-2</v>
+        <v>1.35755395924946E-2</v>
       </c>
       <c r="C68">
         <v>67</v>
       </c>
       <c r="D68">
-        <v>1.72629395309335E-2</v>
+        <v>9.6041204877854499E-3</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -13322,13 +13322,13 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>1.53824238053015E-2</v>
+        <v>1.36649998054532E-2</v>
       </c>
       <c r="C69">
         <v>68</v>
       </c>
       <c r="D69">
-        <v>1.7267021478822E-2</v>
+        <v>9.4792808436466505E-3</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -13336,13 +13336,13 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>1.5187217179679699E-2</v>
+        <v>1.34901695137603E-2</v>
       </c>
       <c r="C70">
         <v>69</v>
       </c>
       <c r="D70">
-        <v>1.7319321510186499E-2</v>
+        <v>9.5163058430269305E-3</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -13350,13 +13350,13 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>1.5187217179679699E-2</v>
+        <v>1.34901695137603E-2</v>
       </c>
       <c r="C71">
         <v>70</v>
       </c>
       <c r="D71">
-        <v>1.7319321510186499E-2</v>
+        <v>9.5163058430269305E-3</v>
       </c>
     </row>
   </sheetData>
@@ -13389,13 +13389,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.76761147728628298</v>
+        <v>0.76771750755111101</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0.69411711188485103</v>
+        <v>0.66701421116973103</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -13403,13 +13403,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.84004348448080002</v>
+        <v>0.84029172078523195</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>0.80424210838530696</v>
+        <v>0.73899085096005901</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -13417,13 +13417,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.83176798187120704</v>
+        <v>0.83200283543641895</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4">
-        <v>0.82810369383833604</v>
+        <v>0.77538745348101101</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -13431,13 +13431,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.814300155568494</v>
+        <v>0.81446152776780401</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>0.80968381258928002</v>
+        <v>0.78516183876153001</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -13445,13 +13445,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.82240287656271205</v>
+        <v>0.82262943424466295</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6">
-        <v>0.83541662658596805</v>
+        <v>0.80308959846161199</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -13459,13 +13459,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.82751571645289501</v>
+        <v>0.82779661007531502</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7">
-        <v>0.84352356259416195</v>
+        <v>0.82596452057717495</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -13473,13 +13473,13 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.84623431945016303</v>
+        <v>0.84650471551143402</v>
       </c>
       <c r="C8">
         <v>7</v>
       </c>
       <c r="D8">
-        <v>0.84480626082522703</v>
+        <v>0.83893596972796503</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -13487,13 +13487,13 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.83134635260906897</v>
+        <v>0.83167634795045098</v>
       </c>
       <c r="C9">
         <v>8</v>
       </c>
       <c r="D9">
-        <v>0.84566308734857898</v>
+        <v>0.85364362187459697</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -13501,13 +13501,13 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.86190761177700204</v>
+        <v>0.86220569509672995</v>
       </c>
       <c r="C10">
         <v>9</v>
       </c>
       <c r="D10">
-        <v>0.85539411295110501</v>
+        <v>0.84044337634338995</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -13515,13 +13515,13 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.85317394197989205</v>
+        <v>0.85342214911288306</v>
       </c>
       <c r="C11">
         <v>10</v>
       </c>
       <c r="D11">
-        <v>0.87170165444577397</v>
+        <v>0.81840478060594601</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -13529,13 +13529,13 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.85206988323772304</v>
+        <v>0.85238662777469199</v>
       </c>
       <c r="C12">
         <v>11</v>
       </c>
       <c r="D12">
-        <v>0.86079655146923395</v>
+        <v>0.78536684283249802</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -13543,13 +13543,13 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.87918432179869799</v>
+        <v>0.87946137473936603</v>
       </c>
       <c r="C13">
         <v>12</v>
       </c>
       <c r="D13">
-        <v>0.82996882038800301</v>
+        <v>0.76371007240125599</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -13557,13 +13557,13 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.871270958246533</v>
+        <v>0.87153611095483996</v>
       </c>
       <c r="C14">
         <v>13</v>
       </c>
       <c r="D14">
-        <v>0.81273575497345796</v>
+        <v>0.74275277961987296</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -13571,13 +13571,13 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0.82900279665050602</v>
+        <v>0.82930273579021596</v>
       </c>
       <c r="C15">
         <v>14</v>
       </c>
       <c r="D15">
-        <v>0.79466153228319103</v>
+        <v>0.72823873838502495</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -13585,13 +13585,13 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0.81641590570450895</v>
+        <v>0.81676503511639997</v>
       </c>
       <c r="C16">
         <v>15</v>
       </c>
       <c r="D16">
-        <v>0.78048170176814702</v>
+        <v>0.70417912025706397</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -13599,13 +13599,13 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.79788783111981698</v>
+        <v>0.798290686931456</v>
       </c>
       <c r="C17">
         <v>16</v>
       </c>
       <c r="D17">
-        <v>0.76431019844584203</v>
+        <v>0.68789709766645302</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -13613,13 +13613,13 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.78021719166172399</v>
+        <v>0.780651124365491</v>
       </c>
       <c r="C18">
         <v>17</v>
       </c>
       <c r="D18">
-        <v>0.77020100134218605</v>
+        <v>0.69231984599127405</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -13627,13 +13627,13 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.77556645191115403</v>
+        <v>0.77604232124692596</v>
       </c>
       <c r="C19">
         <v>18</v>
       </c>
       <c r="D19">
-        <v>0.76164688187515805</v>
+        <v>0.68383636681303195</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -13641,13 +13641,13 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.75594308530131704</v>
+        <v>0.75644501057044899</v>
       </c>
       <c r="C20">
         <v>19</v>
       </c>
       <c r="D20">
-        <v>0.75581987207756995</v>
+        <v>0.676594662878655</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -13655,13 +13655,13 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.74867350143154199</v>
+        <v>0.74920197795838195</v>
       </c>
       <c r="C21">
         <v>20</v>
       </c>
       <c r="D21">
-        <v>0.74727491703386995</v>
+        <v>0.66062550751193105</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -13669,13 +13669,13 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>0.72822976871387701</v>
+        <v>0.72877685964977801</v>
       </c>
       <c r="C22">
         <v>21</v>
       </c>
       <c r="D22">
-        <v>0.75064463303107498</v>
+        <v>0.65661803374213101</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -13683,13 +13683,13 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.71299134498682004</v>
+        <v>0.71355221829691295</v>
       </c>
       <c r="C23">
         <v>22</v>
       </c>
       <c r="D23">
-        <v>0.73486879788243298</v>
+        <v>0.66589933984816896</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -13697,13 +13697,13 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>0.71144786886825395</v>
+        <v>0.71203387995664902</v>
       </c>
       <c r="C24">
         <v>23</v>
       </c>
       <c r="D24">
-        <v>0.72749290774633102</v>
+        <v>0.67363447739359905</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -13711,13 +13711,13 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0.70579325584008701</v>
+        <v>0.70641271681094298</v>
       </c>
       <c r="C25">
         <v>24</v>
       </c>
       <c r="D25">
-        <v>0.71590908981648804</v>
+        <v>0.67903158689402898</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -13725,13 +13725,13 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>0.70539780584219502</v>
+        <v>0.70603720778679502</v>
       </c>
       <c r="C26">
         <v>25</v>
       </c>
       <c r="D26">
-        <v>0.70812133906547303</v>
+        <v>0.66383082571386298</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -13739,13 +13739,13 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>0.70105139193045896</v>
+        <v>0.701714199626982</v>
       </c>
       <c r="C27">
         <v>26</v>
       </c>
       <c r="D27">
-        <v>0.69792973513165002</v>
+        <v>0.65501035002130004</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -13753,13 +13753,13 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>0.69942034665025699</v>
+        <v>0.70009356265797695</v>
       </c>
       <c r="C28">
         <v>27</v>
       </c>
       <c r="D28">
-        <v>0.69646027847965297</v>
+        <v>0.66103629440308997</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -13767,13 +13767,13 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>0.68988742760076804</v>
+        <v>0.69057527120504802</v>
       </c>
       <c r="C29">
         <v>28</v>
       </c>
       <c r="D29">
-        <v>0.68562337220383995</v>
+        <v>0.65196850773374004</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -13781,13 +13781,13 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>0.68503005800439398</v>
+        <v>0.68572314436945503</v>
       </c>
       <c r="C30">
         <v>29</v>
       </c>
       <c r="D30">
-        <v>0.68440746178323997</v>
+        <v>0.65204646995820303</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -13795,13 +13795,13 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.68391339947978902</v>
+        <v>0.68461025632928696</v>
       </c>
       <c r="C31">
         <v>30</v>
       </c>
       <c r="D31">
-        <v>0.67191520170899699</v>
+        <v>0.64431509987807301</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -13809,13 +13809,13 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>0.68369733492519502</v>
+        <v>0.68439613911465802</v>
       </c>
       <c r="C32">
         <v>31</v>
       </c>
       <c r="D32">
-        <v>0.667649251706953</v>
+        <v>0.63609799676098699</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -13823,13 +13823,13 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.68300926880799895</v>
+        <v>0.68373615810402899</v>
       </c>
       <c r="C33">
         <v>32</v>
       </c>
       <c r="D33">
-        <v>0.65762754733482698</v>
+        <v>0.63355567206997598</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -13837,13 +13837,13 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>0.67764331678419498</v>
+        <v>0.67839887634306495</v>
       </c>
       <c r="C34">
         <v>33</v>
       </c>
       <c r="D34">
-        <v>0.650932219012062</v>
+        <v>0.62869424318627798</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -13851,13 +13851,13 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>0.67018096247831904</v>
+        <v>0.67093876190771395</v>
       </c>
       <c r="C35">
         <v>34</v>
       </c>
       <c r="D35">
-        <v>0.64997763937641195</v>
+        <v>0.62622291462129598</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -13865,13 +13865,13 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>0.65983432844716605</v>
+        <v>0.66060469284326395</v>
       </c>
       <c r="C36">
         <v>35</v>
       </c>
       <c r="D36">
-        <v>0.64746447325742895</v>
+        <v>0.61040180973718206</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -13879,13 +13879,13 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>0.65419332864314705</v>
+        <v>0.65499780072176295</v>
       </c>
       <c r="C37">
         <v>36</v>
       </c>
       <c r="D37">
-        <v>0.64613492525057503</v>
+        <v>0.61409591904022398</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -13893,13 +13893,13 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>0.65503492001946095</v>
+        <v>0.65582900628761298</v>
       </c>
       <c r="C38">
         <v>37</v>
       </c>
       <c r="D38">
-        <v>0.63976142615333897</v>
+        <v>0.61179686845173598</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -13907,13 +13907,13 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>0.65832554827050804</v>
+        <v>0.65913284413578599</v>
       </c>
       <c r="C39">
         <v>38</v>
       </c>
       <c r="D39">
-        <v>0.63909959889572798</v>
+        <v>0.61511033251131098</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -13921,13 +13921,13 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>0.65724627329243601</v>
+        <v>0.65807038538162799</v>
       </c>
       <c r="C40">
         <v>39</v>
       </c>
       <c r="D40">
-        <v>0.63187336788168502</v>
+        <v>0.60664776257425701</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -13935,13 +13935,13 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>0.64942781450367604</v>
+        <v>0.65026188996391099</v>
       </c>
       <c r="C41">
         <v>40</v>
       </c>
       <c r="D41">
-        <v>0.62455005055522606</v>
+        <v>0.60802014054188402</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -13949,13 +13949,13 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>0.64697906668442795</v>
+        <v>0.64781523725415702</v>
       </c>
       <c r="C42">
         <v>41</v>
       </c>
       <c r="D42">
-        <v>0.62341768749568105</v>
+        <v>0.60306642974028701</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -13963,13 +13963,13 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>0.64598144805404001</v>
+        <v>0.64682072027791604</v>
       </c>
       <c r="C43">
         <v>42</v>
       </c>
       <c r="D43">
-        <v>0.62147611774132505</v>
+        <v>0.60006292540463702</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -13977,13 +13977,13 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>0.64805261324263197</v>
+        <v>0.64890026185244298</v>
       </c>
       <c r="C44">
         <v>43</v>
       </c>
       <c r="D44">
-        <v>0.62208713942888405</v>
+        <v>0.59770364964266098</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -13991,13 +13991,13 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>0.64435147511229895</v>
+        <v>0.64520800386561805</v>
       </c>
       <c r="C45">
         <v>44</v>
       </c>
       <c r="D45">
-        <v>0.61466445513277901</v>
+        <v>0.60382099947779799</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -14005,13 +14005,13 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>0.64483825137783002</v>
+        <v>0.64570769635700898</v>
       </c>
       <c r="C46">
         <v>45</v>
       </c>
       <c r="D46">
-        <v>0.60374593507159102</v>
+        <v>0.60525583688915396</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -14019,13 +14019,13 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>0.64647977758607</v>
+        <v>0.64736271607277096</v>
       </c>
       <c r="C47">
         <v>46</v>
       </c>
       <c r="D47">
-        <v>0.59827703498941298</v>
+        <v>0.60219727701604397</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -14033,13 +14033,13 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>0.64401996242418502</v>
+        <v>0.64490592890669296</v>
       </c>
       <c r="C48">
         <v>47</v>
       </c>
       <c r="D48">
-        <v>0.59947470118794399</v>
+        <v>0.597454574095028</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -14047,13 +14047,13 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>0.64171430684896202</v>
+        <v>0.64259863031019704</v>
       </c>
       <c r="C49">
         <v>48</v>
       </c>
       <c r="D49">
-        <v>0.593238825513979</v>
+        <v>0.591069846853432</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -14061,13 +14061,13 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>0.64307256453565298</v>
+        <v>0.64395496402260999</v>
       </c>
       <c r="C50">
         <v>49</v>
       </c>
       <c r="D50">
-        <v>0.59463975611014297</v>
+        <v>0.59238385066855104</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -14075,13 +14075,13 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>0.63734463714761802</v>
+        <v>0.63823855763806503</v>
       </c>
       <c r="C51">
         <v>50</v>
       </c>
       <c r="D51">
-        <v>0.58753093601934903</v>
+        <v>0.58524359838634699</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -14089,13 +14089,13 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>0.63082550245563795</v>
+        <v>0.63175320892431197</v>
       </c>
       <c r="C52">
         <v>51</v>
       </c>
       <c r="D52">
-        <v>0.591318553834558</v>
+        <v>0.58159434954741196</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -14103,13 +14103,13 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>0.62998806007560204</v>
+        <v>0.63095600450072198</v>
       </c>
       <c r="C53">
         <v>52</v>
       </c>
       <c r="D53">
-        <v>0.59523514966272495</v>
+        <v>0.57845712991113496</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -14117,13 +14117,13 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>0.62403952735493295</v>
+        <v>0.62499638716074402</v>
       </c>
       <c r="C54">
         <v>53</v>
       </c>
       <c r="D54">
-        <v>0.60121182277058205</v>
+        <v>0.582732557220208</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -14131,13 +14131,13 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>0.61852793446951504</v>
+        <v>0.61949692429891601</v>
       </c>
       <c r="C55">
         <v>54</v>
       </c>
       <c r="D55">
-        <v>0.60559039365989098</v>
+        <v>0.58277815622320495</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -14145,13 +14145,13 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>0.61430593990339499</v>
+        <v>0.61528336269322004</v>
       </c>
       <c r="C56">
         <v>55</v>
       </c>
       <c r="D56">
-        <v>0.60779777146742697</v>
+        <v>0.57599098937774595</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -14159,13 +14159,13 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>0.61645023458648496</v>
+        <v>0.61743388561663204</v>
       </c>
       <c r="C57">
         <v>56</v>
       </c>
       <c r="D57">
-        <v>0.60718338459742904</v>
+        <v>0.57538057710219703</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -14173,13 +14173,13 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>0.61035162635837403</v>
+        <v>0.61134705954841795</v>
       </c>
       <c r="C58">
         <v>57</v>
       </c>
       <c r="D58">
-        <v>0.60137180303770599</v>
+        <v>0.56602151291208502</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -14187,13 +14187,13 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>0.60745167997462401</v>
+        <v>0.608456464240691</v>
       </c>
       <c r="C59">
         <v>58</v>
       </c>
       <c r="D59">
-        <v>0.59084468330164097</v>
+        <v>0.56472236270056897</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -14201,13 +14201,13 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>0.60670402396466305</v>
+        <v>0.60771758140620102</v>
       </c>
       <c r="C60">
         <v>59</v>
       </c>
       <c r="D60">
-        <v>0.58708711657150003</v>
+        <v>0.56648774670616397</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -14215,13 +14215,13 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>0.59893204106050002</v>
+        <v>0.59994233117439</v>
       </c>
       <c r="C61">
         <v>60</v>
       </c>
       <c r="D61">
-        <v>0.58448581712525605</v>
+        <v>0.56734714163703204</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -14229,13 +14229,13 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>0.60119597881178399</v>
+        <v>0.60220976584931896</v>
       </c>
       <c r="C62">
         <v>61</v>
       </c>
       <c r="D62">
-        <v>0.58662166070071897</v>
+        <v>0.56398337275302801</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -14243,13 +14243,13 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>0.59972685665803704</v>
+        <v>0.60074733808977099</v>
       </c>
       <c r="C63">
         <v>62</v>
       </c>
       <c r="D63">
-        <v>0.57784615970153697</v>
+        <v>0.56256926684067199</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -14257,13 +14257,13 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>0.590078231206281</v>
+        <v>0.59111840449851705</v>
       </c>
       <c r="C64">
         <v>63</v>
       </c>
       <c r="D64">
-        <v>0.57525253339920701</v>
+        <v>0.56904980042366904</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -14271,13 +14271,13 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>0.58960899248835497</v>
+        <v>0.59064203856828601</v>
       </c>
       <c r="C65">
         <v>64</v>
       </c>
       <c r="D65">
-        <v>0.57108990557694395</v>
+        <v>0.57706727927472801</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -14285,13 +14285,13 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>0.58598585076936205</v>
+        <v>0.587024337256005</v>
       </c>
       <c r="C66">
         <v>65</v>
       </c>
       <c r="D66">
-        <v>0.56994127077765799</v>
+        <v>0.57620998077638896</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -14299,13 +14299,13 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>0.582750855804398</v>
+        <v>0.58379151659845396</v>
       </c>
       <c r="C67">
         <v>66</v>
       </c>
       <c r="D67">
-        <v>0.570202770498075</v>
+        <v>0.57349459106536205</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -14313,13 +14313,13 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>0.57878005618438799</v>
+        <v>0.57982089190990305</v>
       </c>
       <c r="C68">
         <v>67</v>
       </c>
       <c r="D68">
-        <v>0.57371369467324795</v>
+        <v>0.57194400301579595</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -14327,13 +14327,13 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>0.58035180373404704</v>
+        <v>0.58140130410654001</v>
       </c>
       <c r="C69">
         <v>68</v>
       </c>
       <c r="D69">
-        <v>0.57582976000942598</v>
+        <v>0.56372406312326095</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -14341,13 +14341,13 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>0.57591694300164598</v>
+        <v>0.57696909372309102</v>
       </c>
       <c r="C70">
         <v>69</v>
       </c>
       <c r="D70">
-        <v>0.56942482302522002</v>
+        <v>0.56885973039349103</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -14355,13 +14355,13 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>0.57591694300164598</v>
+        <v>0.57696909372309102</v>
       </c>
       <c r="C71">
         <v>70</v>
       </c>
       <c r="D71">
-        <v>0.56942482302522002</v>
+        <v>0.56885973039349103</v>
       </c>
     </row>
   </sheetData>

--- a/InitializationResults/WithTrack/Comparison of SPEA2 with SPEA2_SI for each generation (on average).xlsx
+++ b/InitializationResults/WithTrack/Comparison of SPEA2 with SPEA2_SI for each generation (on average).xlsx
@@ -28,12 +28,222 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="72">
   <si>
     <t>SPEA2</t>
   </si>
   <si>
     <t>SPEA2_SI</t>
+  </si>
+  <si>
+    <t>1 0.657859671844684</t>
+  </si>
+  <si>
+    <t>2 0.7687851902625128</t>
+  </si>
+  <si>
+    <t>3 0.7958571026972172</t>
+  </si>
+  <si>
+    <t>4 0.7956027258673871</t>
+  </si>
+  <si>
+    <t>5 0.7903472497039553</t>
+  </si>
+  <si>
+    <t>6 0.8388715828811718</t>
+  </si>
+  <si>
+    <t>7 0.8481279571116311</t>
+  </si>
+  <si>
+    <t>8 0.8576840259744329</t>
+  </si>
+  <si>
+    <t>9 0.848052528681821</t>
+  </si>
+  <si>
+    <t>10 0.8112998193416588</t>
+  </si>
+  <si>
+    <t>11 0.7782125691316707</t>
+  </si>
+  <si>
+    <t>12 0.743891953250883</t>
+  </si>
+  <si>
+    <t>13 0.7264149703654817</t>
+  </si>
+  <si>
+    <t>14 0.7037820249004605</t>
+  </si>
+  <si>
+    <t>15 0.6897710507032292</t>
+  </si>
+  <si>
+    <t>16 0.6792730554997299</t>
+  </si>
+  <si>
+    <t>17 0.6703119256682791</t>
+  </si>
+  <si>
+    <t>18 0.6684944266480952</t>
+  </si>
+  <si>
+    <t>19 0.6644081142905648</t>
+  </si>
+  <si>
+    <t>20 0.6551997404378601</t>
+  </si>
+  <si>
+    <t>21 0.6505898835797393</t>
+  </si>
+  <si>
+    <t>22 0.6521148589876689</t>
+  </si>
+  <si>
+    <t>23 0.643747873115321</t>
+  </si>
+  <si>
+    <t>24 0.6384257353936403</t>
+  </si>
+  <si>
+    <t>25 0.6358761920102745</t>
+  </si>
+  <si>
+    <t>26 0.6254059861687505</t>
+  </si>
+  <si>
+    <t>27 0.6205928112468339</t>
+  </si>
+  <si>
+    <t>28 0.6169665202217068</t>
+  </si>
+  <si>
+    <t>29 0.6186172397165957</t>
+  </si>
+  <si>
+    <t>30 0.6199914964098251</t>
+  </si>
+  <si>
+    <t>31 0.619035319597225</t>
+  </si>
+  <si>
+    <t>32 0.6099213776525532</t>
+  </si>
+  <si>
+    <t>33 0.6067809082383067</t>
+  </si>
+  <si>
+    <t>34 0.6013722844358659</t>
+  </si>
+  <si>
+    <t>35 0.6066667821875183</t>
+  </si>
+  <si>
+    <t>36 0.6017981370478054</t>
+  </si>
+  <si>
+    <t>37 0.5990194350816828</t>
+  </si>
+  <si>
+    <t>38 0.5957329562085255</t>
+  </si>
+  <si>
+    <t>39 0.5945429067610194</t>
+  </si>
+  <si>
+    <t>40 0.5937290987341773</t>
+  </si>
+  <si>
+    <t>41 0.5924686339391932</t>
+  </si>
+  <si>
+    <t>42 0.5919607979306803</t>
+  </si>
+  <si>
+    <t>43 0.5928926922137343</t>
+  </si>
+  <si>
+    <t>44 0.5880168966159321</t>
+  </si>
+  <si>
+    <t>45 0.5861580441523648</t>
+  </si>
+  <si>
+    <t>46 0.5810801535771853</t>
+  </si>
+  <si>
+    <t>47 0.5721780079583937</t>
+  </si>
+  <si>
+    <t>48 0.571335344452591</t>
+  </si>
+  <si>
+    <t>49 0.5683832701954683</t>
+  </si>
+  <si>
+    <t>50 0.5684154366519051</t>
+  </si>
+  <si>
+    <t>51 0.5651624141140955</t>
+  </si>
+  <si>
+    <t>52 0.5624042447506735</t>
+  </si>
+  <si>
+    <t>53 0.5622944549126258</t>
+  </si>
+  <si>
+    <t>54 0.5621040306474071</t>
+  </si>
+  <si>
+    <t>55 0.5632085853123532</t>
+  </si>
+  <si>
+    <t>56 0.5591933793524096</t>
+  </si>
+  <si>
+    <t>57 0.5520190638678893</t>
+  </si>
+  <si>
+    <t>58 0.5518903044392609</t>
+  </si>
+  <si>
+    <t>59 0.5523580829226736</t>
+  </si>
+  <si>
+    <t>60 0.55403685691288</t>
+  </si>
+  <si>
+    <t>61 0.5511270806884873</t>
+  </si>
+  <si>
+    <t>62 0.5493814231779771</t>
+  </si>
+  <si>
+    <t>63 0.54790210541945</t>
+  </si>
+  <si>
+    <t>64 0.5452208153099943</t>
+  </si>
+  <si>
+    <t>65 0.5470420000439783</t>
+  </si>
+  <si>
+    <t>66 0.5504313565799258</t>
+  </si>
+  <si>
+    <t>67 0.549644387141993</t>
+  </si>
+  <si>
+    <t>68 0.547212218559148</t>
+  </si>
+  <si>
+    <t>69 0.5448378494937198</t>
+  </si>
+  <si>
+    <t>70 0.5448378494937198</t>
   </si>
 </sst>
 </file>
@@ -424,214 +634,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>721.9</c:v>
+                  <c:v>757.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>715.7</c:v>
+                  <c:v>708.93333333333305</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>631</c:v>
+                  <c:v>646.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>584.4</c:v>
+                  <c:v>603.96666666666601</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>527.79999999999995</c:v>
+                  <c:v>554.93333333333305</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>472.9</c:v>
+                  <c:v>503.7</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>442</c:v>
+                  <c:v>468.9</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>436.3</c:v>
+                  <c:v>452.33333333333297</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>422.9</c:v>
+                  <c:v>428.06666666666598</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>412</c:v>
+                  <c:v>410.3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>359.2</c:v>
+                  <c:v>371.433333333333</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>349.7</c:v>
+                  <c:v>356.86666666666599</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>330.7</c:v>
+                  <c:v>342.933333333333</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>328.4</c:v>
+                  <c:v>324.86666666666599</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>298.8</c:v>
+                  <c:v>308.03333333333302</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>279.39999999999998</c:v>
+                  <c:v>279.60000000000002</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>279.39999999999998</c:v>
+                  <c:v>275.26666666666603</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>274.8</c:v>
+                  <c:v>260.96666666666601</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>271.7</c:v>
+                  <c:v>254</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>269.7</c:v>
+                  <c:v>244.166666666666</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>260.39999999999998</c:v>
+                  <c:v>236.06666666666601</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>242.3</c:v>
+                  <c:v>226.73333333333301</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>229.1</c:v>
+                  <c:v>221.1</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>215.8</c:v>
+                  <c:v>212.766666666666</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>215</c:v>
+                  <c:v>199.2</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>209.1</c:v>
+                  <c:v>195.7</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>194.3</c:v>
+                  <c:v>187.06666666666601</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>188.2</c:v>
+                  <c:v>178.5</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>183.9</c:v>
+                  <c:v>176.56666666666601</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>182.7</c:v>
+                  <c:v>174.23333333333301</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>179.1</c:v>
+                  <c:v>166.63333333333301</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>179.1</c:v>
+                  <c:v>166.433333333333</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>171.3</c:v>
+                  <c:v>163.266666666666</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>164.8</c:v>
+                  <c:v>159.86666666666599</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>161.30000000000001</c:v>
+                  <c:v>156.9</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>156.30000000000001</c:v>
+                  <c:v>148.6</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>156.30000000000001</c:v>
+                  <c:v>146.86666666666599</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>151.30000000000001</c:v>
+                  <c:v>138.6</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>149.19999999999999</c:v>
+                  <c:v>134.03333333333299</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>145.19999999999999</c:v>
+                  <c:v>127.533333333333</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>145</c:v>
+                  <c:v>125.5</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>143.5</c:v>
+                  <c:v>122.9</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>123.7</c:v>
+                  <c:v>115.666666666666</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>121</c:v>
+                  <c:v>108.966666666666</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>118.9</c:v>
+                  <c:v>106.533333333333</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>111.2</c:v>
+                  <c:v>98</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>109.5</c:v>
+                  <c:v>95.533333333333303</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>108.5</c:v>
+                  <c:v>94.866666666666603</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>106.7</c:v>
+                  <c:v>91.133333333333297</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>103</c:v>
+                  <c:v>88.233333333333306</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>101.1</c:v>
+                  <c:v>87</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>76.099999999999994</c:v>
+                  <c:v>75.5</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>73.8</c:v>
+                  <c:v>74.066666666666606</c:v>
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>73.7</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>73.3</c:v>
+                  <c:v>72.966666666666598</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>72.2</c:v>
+                  <c:v>71.733333333333306</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>71.5</c:v>
+                  <c:v>68.066666666666606</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>68.2</c:v>
+                  <c:v>66.266666666666595</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>68.099999999999994</c:v>
+                  <c:v>65.266666666666595</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>64.8</c:v>
+                  <c:v>64</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>55.6</c:v>
+                  <c:v>60.933333333333302</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>54.7</c:v>
+                  <c:v>59.9</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>52.7</c:v>
+                  <c:v>58</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>52.5</c:v>
+                  <c:v>56.733333333333299</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>51</c:v>
+                  <c:v>55.8333333333333</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>50.1</c:v>
+                  <c:v>54.233333333333299</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>44.1</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>44.1</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>44</c:v>
+                  <c:v>49.7</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>44</c:v>
+                  <c:v>49.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -675,214 +885,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>438.3</c:v>
+                  <c:v>366.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>375.7</c:v>
+                  <c:v>335.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>337.4</c:v>
+                  <c:v>278.7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>266.89999999999998</c:v>
+                  <c:v>252.933333333333</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>227.4</c:v>
+                  <c:v>226.56666666666601</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>216</c:v>
+                  <c:v>195</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>197</c:v>
+                  <c:v>166</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>188.7</c:v>
+                  <c:v>158.833333333333</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>170.9</c:v>
+                  <c:v>145.9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>163.9</c:v>
+                  <c:v>136.433333333333</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>150.1</c:v>
+                  <c:v>134.13333333333301</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>129.80000000000001</c:v>
+                  <c:v>123.766666666666</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>127.9</c:v>
+                  <c:v>120.06666666666599</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>127.8</c:v>
+                  <c:v>114.833333333333</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>123.2</c:v>
+                  <c:v>113.266666666666</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>111.6</c:v>
+                  <c:v>111.56666666666599</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>107.2</c:v>
+                  <c:v>106.2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>106.8</c:v>
+                  <c:v>104.333333333333</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>106.1</c:v>
+                  <c:v>101.23333333333299</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>93.5</c:v>
+                  <c:v>98.033333333333303</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>84.5</c:v>
+                  <c:v>95.633333333333297</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>84.5</c:v>
+                  <c:v>91.966666666666598</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>79.099999999999994</c:v>
+                  <c:v>90.3333333333333</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>79.099999999999994</c:v>
+                  <c:v>83.433333333333294</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>77.400000000000006</c:v>
+                  <c:v>81.066666666666606</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>77.400000000000006</c:v>
+                  <c:v>79.400000000000006</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>72.7</c:v>
+                  <c:v>78</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>71.400000000000006</c:v>
+                  <c:v>77.566666666666606</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>67.599999999999994</c:v>
+                  <c:v>73.433333333333294</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>66.400000000000006</c:v>
+                  <c:v>72.233333333333306</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>58.9</c:v>
+                  <c:v>70.400000000000006</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>57.2</c:v>
+                  <c:v>68.566666666666606</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>56.7</c:v>
+                  <c:v>67.5</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>55.7</c:v>
+                  <c:v>64.400000000000006</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>55.3</c:v>
+                  <c:v>63.2</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>54.9</c:v>
+                  <c:v>60.266666666666602</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>54.9</c:v>
+                  <c:v>57.1666666666666</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>54.9</c:v>
+                  <c:v>57</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>50.4</c:v>
+                  <c:v>55.4</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>43.9</c:v>
+                  <c:v>53.366666666666603</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>43.2</c:v>
+                  <c:v>50.5</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>42.6</c:v>
+                  <c:v>49.466666666666598</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>42.3</c:v>
+                  <c:v>45.733333333333299</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>42.3</c:v>
+                  <c:v>43.966666666666598</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>39.1</c:v>
+                  <c:v>43.733333333333299</c:v>
                 </c:pt>
                 <c:pt idx="45">
+                  <c:v>43.133333333333297</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>42.1666666666666</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>41.433333333333302</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>40.566666666666599</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>40.5</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>40.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>39.466666666666598</c:v>
+                </c:pt>
+                <c:pt idx="52">
                   <c:v>38.700000000000003</c:v>
                 </c:pt>
-                <c:pt idx="46">
-                  <c:v>38.299999999999997</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>38.1</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>38</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>37</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>36.4</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>36.299999999999997</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>35.6</c:v>
-                </c:pt>
                 <c:pt idx="53">
-                  <c:v>35.4</c:v>
+                  <c:v>38.700000000000003</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>34.200000000000003</c:v>
+                  <c:v>37.933333333333302</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>34.200000000000003</c:v>
+                  <c:v>36.533333333333303</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>34.200000000000003</c:v>
+                  <c:v>34.3333333333333</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>34.200000000000003</c:v>
+                  <c:v>33.966666666666598</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>33.799999999999997</c:v>
+                  <c:v>33.5</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>31.8</c:v>
+                  <c:v>32.6666666666666</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>30.6</c:v>
+                  <c:v>31.1666666666666</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>29.7</c:v>
+                  <c:v>30.1</c:v>
                 </c:pt>
                 <c:pt idx="62">
+                  <c:v>29.8</c:v>
+                </c:pt>
+                <c:pt idx="63">
                   <c:v>29.3</c:v>
                 </c:pt>
-                <c:pt idx="63">
-                  <c:v>28.9</c:v>
-                </c:pt>
                 <c:pt idx="64">
-                  <c:v>28.9</c:v>
+                  <c:v>29.1666666666666</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>28.1</c:v>
+                  <c:v>29.066666666666599</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>28.1</c:v>
+                  <c:v>27.3</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>28</c:v>
+                  <c:v>26.8666666666666</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>28</c:v>
+                  <c:v>26.3333333333333</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>28</c:v>
+                  <c:v>26.3333333333333</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -897,11 +1107,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="343719704"/>
-        <c:axId val="346466048"/>
+        <c:axId val="364411552"/>
+        <c:axId val="364411944"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="343719704"/>
+        <c:axId val="364411552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1014,12 +1224,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="346466048"/>
+        <c:crossAx val="364411944"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="346466048"/>
+        <c:axId val="364411944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1076,7 +1286,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="343719704"/>
+        <c:crossAx val="364411552"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1489,214 +1699,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>1.06383523139125E-2</c:v>
+                  <c:v>1.04146754726555E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.5810539785954702E-3</c:v>
+                  <c:v>8.0076639865018003E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.2869038803537204E-3</c:v>
+                  <c:v>6.5962787772507704E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.1250426202196402E-3</c:v>
+                  <c:v>5.3797199845398297E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.5059768851830901E-3</c:v>
+                  <c:v>4.6458918099082699E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.4832735193812002E-3</c:v>
+                  <c:v>3.75063604676287E-3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.87457600733278E-3</c:v>
+                  <c:v>3.1679456088083702E-3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.5010040884948801E-3</c:v>
+                  <c:v>2.6980196969778E-3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.1536991348774198E-3</c:v>
+                  <c:v>2.2424378073924601E-3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.7999949864495901E-3</c:v>
+                  <c:v>1.86947651610022E-3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.6782209008272E-3</c:v>
+                  <c:v>1.64681563198507E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.41802598362938E-3</c:v>
+                  <c:v>1.44664542601287E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.20121949107636E-3</c:v>
+                  <c:v>1.27377801939478E-3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.11484019260655E-3</c:v>
+                  <c:v>1.1647472184426E-3</c:v>
                 </c:pt>
                 <c:pt idx="14" formatCode="0.00E+00">
-                  <c:v>9.5723548459934E-4</c:v>
+                  <c:v>1.05473615874447E-3</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00E+00">
-                  <c:v>9.0294871873444402E-4</c:v>
+                  <c:v>9.4777766504134601E-4</c:v>
                 </c:pt>
                 <c:pt idx="16" formatCode="0.00E+00">
-                  <c:v>8.3926885306566802E-4</c:v>
+                  <c:v>8.8060617981324397E-4</c:v>
                 </c:pt>
                 <c:pt idx="17" formatCode="0.00E+00">
-                  <c:v>7.4997845979743699E-4</c:v>
+                  <c:v>8.2126508645216699E-4</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00E+00">
-                  <c:v>7.3177891081085598E-4</c:v>
+                  <c:v>7.7045134651684605E-4</c:v>
                 </c:pt>
                 <c:pt idx="19" formatCode="0.00E+00">
-                  <c:v>7.04195703866309E-4</c:v>
+                  <c:v>7.2775895857640305E-4</c:v>
                 </c:pt>
                 <c:pt idx="20" formatCode="0.00E+00">
-                  <c:v>6.7935852139595497E-4</c:v>
+                  <c:v>6.9115023501205102E-4</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00E+00">
-                  <c:v>6.6737580397042799E-4</c:v>
+                  <c:v>6.7538366421427505E-4</c:v>
                 </c:pt>
                 <c:pt idx="22" formatCode="0.00E+00">
-                  <c:v>6.4437470837393597E-4</c:v>
+                  <c:v>6.5132020217662499E-4</c:v>
                 </c:pt>
                 <c:pt idx="23" formatCode="0.00E+00">
-                  <c:v>6.1737335842525904E-4</c:v>
+                  <c:v>6.2909518521640198E-4</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00E+00">
-                  <c:v>5.8332341370480399E-4</c:v>
+                  <c:v>5.9135634597828305E-4</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="0.00E+00">
-                  <c:v>5.6668102385006296E-4</c:v>
+                  <c:v>5.5355106421415201E-4</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="0.00E+00">
-                  <c:v>5.5714372536035302E-4</c:v>
+                  <c:v>5.3912597463276902E-4</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00E+00">
-                  <c:v>5.4061174476971398E-4</c:v>
+                  <c:v>5.2009832919238698E-4</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="0.00E+00">
-                  <c:v>5.3013223536924905E-4</c:v>
+                  <c:v>5.1330600144477198E-4</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="0.00E+00">
-                  <c:v>5.0993600629680195E-4</c:v>
+                  <c:v>4.9774352522451105E-4</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00E+00">
-                  <c:v>4.7889329939988399E-4</c:v>
+                  <c:v>4.7659553261708901E-4</c:v>
                 </c:pt>
                 <c:pt idx="31" formatCode="0.00E+00">
-                  <c:v>4.6504341579952898E-4</c:v>
+                  <c:v>4.5677708278977298E-4</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="0.00E+00">
-                  <c:v>4.5707094722044998E-4</c:v>
+                  <c:v>4.4360034765033901E-4</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00E+00">
-                  <c:v>4.4372899727806601E-4</c:v>
+                  <c:v>4.3376210842222798E-4</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="0.00E+00">
-                  <c:v>4.3632795608312898E-4</c:v>
+                  <c:v>4.2811783980542501E-4</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="0.00E+00">
-                  <c:v>4.46962550879127E-4</c:v>
+                  <c:v>4.2521028960767403E-4</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00E+00">
-                  <c:v>4.3345505970351998E-4</c:v>
+                  <c:v>4.1562417559770903E-4</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="0.00E+00">
-                  <c:v>4.3111628003847803E-4</c:v>
+                  <c:v>4.0967264583203101E-4</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="0.00E+00">
-                  <c:v>4.1353249983020298E-4</c:v>
+                  <c:v>4.0434279411852698E-4</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="0.00E+00">
-                  <c:v>4.0872445589815702E-4</c:v>
+                  <c:v>4.0381413389985302E-4</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="0.00E+00">
-                  <c:v>4.0146132370063502E-4</c:v>
+                  <c:v>3.9839724110683902E-4</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="0.00E+00">
-                  <c:v>3.8761300124531302E-4</c:v>
+                  <c:v>3.8692930846641598E-4</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00E+00">
-                  <c:v>3.7493819419275103E-4</c:v>
+                  <c:v>3.8546700473082198E-4</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="0.00E+00">
-                  <c:v>3.6665950189994801E-4</c:v>
+                  <c:v>3.79620691588214E-4</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="0.00E+00">
-                  <c:v>3.6733870067678399E-4</c:v>
+                  <c:v>3.7697438704909598E-4</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00E+00">
-                  <c:v>3.4827981707836699E-4</c:v>
+                  <c:v>3.6549298714095299E-4</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="0.00E+00">
-                  <c:v>3.4345794781199998E-4</c:v>
+                  <c:v>3.6433006767189901E-4</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="0.00E+00">
-                  <c:v>3.4229131937222798E-4</c:v>
+                  <c:v>3.5493646996606599E-4</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00E+00">
-                  <c:v>3.4546140721874899E-4</c:v>
+                  <c:v>3.5596997491511297E-4</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="0.00E+00">
-                  <c:v>3.4471096962063202E-4</c:v>
+                  <c:v>3.54573946754829E-4</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="0.00E+00">
-                  <c:v>3.4531297199252799E-4</c:v>
+                  <c:v>3.5592631511453397E-4</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00E+00">
-                  <c:v>3.4998657382968298E-4</c:v>
+                  <c:v>3.5523829209910702E-4</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="0.00E+00">
-                  <c:v>3.5101251010564202E-4</c:v>
+                  <c:v>3.5513749224393599E-4</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="0.00E+00">
-                  <c:v>3.4101093831140702E-4</c:v>
+                  <c:v>3.57386877703124E-4</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00E+00">
-                  <c:v>3.3151175073857102E-4</c:v>
+                  <c:v>3.53616915445156E-4</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00E+00">
-                  <c:v>3.1925096472942599E-4</c:v>
+                  <c:v>3.4919265363781999E-4</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00E+00">
-                  <c:v>3.1761089153413299E-4</c:v>
+                  <c:v>3.4885281607527498E-4</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00E+00">
-                  <c:v>3.16854934871136E-4</c:v>
+                  <c:v>3.4804544366309298E-4</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="0.00E+00">
-                  <c:v>3.1767748020337201E-4</c:v>
+                  <c:v>3.4594624353098799E-4</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="0.00E+00">
-                  <c:v>3.1232163065188998E-4</c:v>
+                  <c:v>3.3816676949701498E-4</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="0.00E+00">
-                  <c:v>3.1639879080852399E-4</c:v>
+                  <c:v>3.3953262234193198E-4</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="0.00E+00">
-                  <c:v>3.1211756715020901E-4</c:v>
+                  <c:v>3.4396927697661901E-4</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="0.00E+00">
-                  <c:v>3.1034440173116401E-4</c:v>
+                  <c:v>3.41333721461545E-4</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="0.00E+00">
-                  <c:v>3.0606112048333701E-4</c:v>
+                  <c:v>3.4006746208164698E-4</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="0.00E+00">
-                  <c:v>3.0265676087775598E-4</c:v>
+                  <c:v>3.3760083903140801E-4</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="0.00E+00">
-                  <c:v>2.9961387722659898E-4</c:v>
+                  <c:v>3.3683225686062301E-4</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="0.00E+00">
-                  <c:v>2.9217166176705899E-4</c:v>
+                  <c:v>3.33555875900424E-4</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="0.00E+00">
-                  <c:v>2.8864145059779098E-4</c:v>
+                  <c:v>3.3163383101576598E-4</c:v>
                 </c:pt>
                 <c:pt idx="68" formatCode="0.00E+00">
-                  <c:v>2.8955412195869398E-4</c:v>
+                  <c:v>3.3218948292219999E-4</c:v>
                 </c:pt>
                 <c:pt idx="69" formatCode="0.00E+00">
-                  <c:v>2.8955412195869398E-4</c:v>
+                  <c:v>3.3218948292219999E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1740,214 +1950,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>1.0922005258687899E-2</c:v>
+                  <c:v>1.1160219798206E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.0870889854810207E-3</c:v>
+                  <c:v>8.2216887993449596E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.3536332778655899E-3</c:v>
+                  <c:v>5.7309982239340104E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.5626268386532703E-3</c:v>
+                  <c:v>4.29906043263304E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.4088873750394099E-3</c:v>
+                  <c:v>3.2842768942501601E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.82323478039429E-3</c:v>
+                  <c:v>2.5561964997723001E-3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.2822973171864902E-3</c:v>
+                  <c:v>2.0479240244974501E-3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.91130874129758E-3</c:v>
+                  <c:v>1.6864033182758501E-3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.56063567460619E-3</c:v>
+                  <c:v>1.4179918376485501E-3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.37017979641644E-3</c:v>
+                  <c:v>1.23800837385637E-3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.16922732111627E-3</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1.03575950156211E-3</c:v>
+                  <c:v>1.0817484427115701E-3</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="0.00E+00">
+                  <c:v>9.6757001222246995E-4</c:v>
                 </c:pt>
                 <c:pt idx="12" formatCode="0.00E+00">
-                  <c:v>9.7026855783229103E-4</c:v>
+                  <c:v>8.7507665939443903E-4</c:v>
                 </c:pt>
                 <c:pt idx="13" formatCode="0.00E+00">
-                  <c:v>9.0182313150035396E-4</c:v>
+                  <c:v>7.8849333922230999E-4</c:v>
                 </c:pt>
                 <c:pt idx="14" formatCode="0.00E+00">
-                  <c:v>8.4284057047047801E-4</c:v>
+                  <c:v>7.24614586522773E-4</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00E+00">
-                  <c:v>8.0849268787772295E-4</c:v>
+                  <c:v>6.8840541458690203E-4</c:v>
                 </c:pt>
                 <c:pt idx="16" formatCode="0.00E+00">
-                  <c:v>7.6646872313275796E-4</c:v>
+                  <c:v>6.5296824339923303E-4</c:v>
                 </c:pt>
                 <c:pt idx="17" formatCode="0.00E+00">
-                  <c:v>7.40578425652974E-4</c:v>
+                  <c:v>6.1658638553614903E-4</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00E+00">
-                  <c:v>7.1458306061550998E-4</c:v>
+                  <c:v>5.8903816628338296E-4</c:v>
                 </c:pt>
                 <c:pt idx="19" formatCode="0.00E+00">
-                  <c:v>6.9821868185286E-4</c:v>
+                  <c:v>5.6793528092820603E-4</c:v>
                 </c:pt>
                 <c:pt idx="20" formatCode="0.00E+00">
-                  <c:v>6.6646549987467798E-4</c:v>
+                  <c:v>5.5223677759925897E-4</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00E+00">
-                  <c:v>6.4680385897619404E-4</c:v>
+                  <c:v>5.2869694813629695E-4</c:v>
                 </c:pt>
                 <c:pt idx="22" formatCode="0.00E+00">
-                  <c:v>6.1812803158358201E-4</c:v>
+                  <c:v>5.0914001296105502E-4</c:v>
                 </c:pt>
                 <c:pt idx="23" formatCode="0.00E+00">
-                  <c:v>5.9525635907166905E-4</c:v>
+                  <c:v>4.89989829958158E-4</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00E+00">
-                  <c:v>5.8159001371037398E-4</c:v>
+                  <c:v>4.6717118843020102E-4</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="0.00E+00">
-                  <c:v>5.6020073221486498E-4</c:v>
+                  <c:v>4.5772606205040799E-4</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="0.00E+00">
-                  <c:v>5.3868931951656595E-4</c:v>
+                  <c:v>4.4828608551544802E-4</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00E+00">
-                  <c:v>5.2855522554097999E-4</c:v>
+                  <c:v>4.3411752436227097E-4</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="0.00E+00">
-                  <c:v>5.1616230201372004E-4</c:v>
+                  <c:v>4.2279679683340001E-4</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="0.00E+00">
-                  <c:v>5.0006729246403095E-4</c:v>
+                  <c:v>4.0672944419178501E-4</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00E+00">
-                  <c:v>4.8719786797702801E-4</c:v>
+                  <c:v>3.99319699942204E-4</c:v>
                 </c:pt>
                 <c:pt idx="31" formatCode="0.00E+00">
-                  <c:v>4.7143359059263198E-4</c:v>
+                  <c:v>3.9353951123557502E-4</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="0.00E+00">
-                  <c:v>3.8057015153041798E-4</c:v>
+                  <c:v>3.9180259351326898E-4</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00E+00">
-                  <c:v>3.7369445028088798E-4</c:v>
+                  <c:v>3.7945811694362801E-4</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="0.00E+00">
-                  <c:v>3.6844290072597598E-4</c:v>
+                  <c:v>3.6915514124951499E-4</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="0.00E+00">
-                  <c:v>3.6820191319592602E-4</c:v>
+                  <c:v>3.6681257520363797E-4</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00E+00">
-                  <c:v>3.6779144520681002E-4</c:v>
+                  <c:v>3.6222054326156899E-4</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="0.00E+00">
-                  <c:v>3.6795697023902401E-4</c:v>
+                  <c:v>3.5895964741454998E-4</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="0.00E+00">
-                  <c:v>3.6697157192033602E-4</c:v>
+                  <c:v>3.5213504536005301E-4</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="0.00E+00">
-                  <c:v>3.5964089930351202E-4</c:v>
+                  <c:v>3.44035010877063E-4</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="0.00E+00">
-                  <c:v>3.5248017675008003E-4</c:v>
+                  <c:v>3.3900046969914801E-4</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="0.00E+00">
-                  <c:v>3.4820992340059003E-4</c:v>
+                  <c:v>3.3496578216205198E-4</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00E+00">
-                  <c:v>3.4408588864611399E-4</c:v>
+                  <c:v>3.32704053507927E-4</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="0.00E+00">
-                  <c:v>3.4064144432624402E-4</c:v>
+                  <c:v>3.3021306688383299E-4</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="0.00E+00">
-                  <c:v>3.3922988482544899E-4</c:v>
+                  <c:v>3.24618311138663E-4</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00E+00">
-                  <c:v>3.2792017884209E-4</c:v>
+                  <c:v>3.2171115458442899E-4</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="0.00E+00">
-                  <c:v>3.2778187583548001E-4</c:v>
+                  <c:v>3.2124140628867002E-4</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="0.00E+00">
-                  <c:v>3.27853566781995E-4</c:v>
+                  <c:v>3.20864222975467E-4</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00E+00">
-                  <c:v>3.3059523947906097E-4</c:v>
+                  <c:v>3.2095168635226E-4</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="0.00E+00">
-                  <c:v>3.1666884658662099E-4</c:v>
+                  <c:v>3.1534714404608702E-4</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="0.00E+00">
-                  <c:v>3.1079372213412899E-4</c:v>
+                  <c:v>3.1369835302852E-4</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00E+00">
-                  <c:v>3.1294027433858797E-4</c:v>
+                  <c:v>3.1354000024706898E-4</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="0.00E+00">
-                  <c:v>3.1133532772313101E-4</c:v>
+                  <c:v>3.1744750990404601E-4</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="0.00E+00">
-                  <c:v>3.1650291388515302E-4</c:v>
+                  <c:v>3.1435461850710299E-4</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00E+00">
-                  <c:v>3.1520524222449501E-4</c:v>
+                  <c:v>3.1265339788549498E-4</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00E+00">
-                  <c:v>3.1704801362872001E-4</c:v>
+                  <c:v>3.0958483238244803E-4</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00E+00">
-                  <c:v>3.1606769777886698E-4</c:v>
+                  <c:v>3.0747490234269901E-4</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00E+00">
-                  <c:v>3.1582121565974601E-4</c:v>
+                  <c:v>3.0646136229955299E-4</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="0.00E+00">
-                  <c:v>3.11569460307142E-4</c:v>
+                  <c:v>3.0226373092919802E-4</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="0.00E+00">
-                  <c:v>3.0277785548266502E-4</c:v>
+                  <c:v>2.99278133744498E-4</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="0.00E+00">
-                  <c:v>3.0864410596062798E-4</c:v>
+                  <c:v>3.0135757356330501E-4</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="0.00E+00">
-                  <c:v>3.0721391337254299E-4</c:v>
+                  <c:v>3.0409732263618299E-4</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="0.00E+00">
-                  <c:v>3.0793946533693898E-4</c:v>
+                  <c:v>3.0327662113568098E-4</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="0.00E+00">
-                  <c:v>3.0629558161670802E-4</c:v>
+                  <c:v>3.0065802806271299E-4</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="0.00E+00">
-                  <c:v>3.0854584300282002E-4</c:v>
+                  <c:v>3.0070362727937703E-4</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="0.00E+00">
-                  <c:v>3.0825622966724201E-4</c:v>
+                  <c:v>3.0128313522629198E-4</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="0.00E+00">
-                  <c:v>3.1048046448416198E-4</c:v>
+                  <c:v>3.0089573524966798E-4</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="0.00E+00">
-                  <c:v>3.1209820508750402E-4</c:v>
+                  <c:v>3.0286855011583502E-4</c:v>
                 </c:pt>
                 <c:pt idx="68" formatCode="0.00E+00">
-                  <c:v>3.1497390436151701E-4</c:v>
+                  <c:v>3.0317335678730403E-4</c:v>
                 </c:pt>
                 <c:pt idx="69" formatCode="0.00E+00">
-                  <c:v>3.1497390436151701E-4</c:v>
+                  <c:v>3.0317335678730403E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1962,11 +2172,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="346471536"/>
-        <c:axId val="346474672"/>
+        <c:axId val="364413904"/>
+        <c:axId val="364412336"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="346471536"/>
+        <c:axId val="364413904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2079,12 +2289,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="346474672"/>
+        <c:crossAx val="364412336"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="346474672"/>
+        <c:axId val="364412336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2141,7 +2351,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="346471536"/>
+        <c:crossAx val="364413904"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2554,214 +2764,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>0.69425629338408201</c:v>
+                  <c:v>0.68884288448075603</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.70141418729654004</c:v>
+                  <c:v>0.70314472428445796</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.72091290943217901</c:v>
+                  <c:v>0.71986048987838902</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.73686820114812002</c:v>
+                  <c:v>0.73356026085486203</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.74902749170497596</c:v>
+                  <c:v>0.74487886485935095</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.76212710247193005</c:v>
+                  <c:v>0.75615098121000901</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.771461098885034</c:v>
+                  <c:v>0.76574801368551804</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.77549909805487904</c:v>
+                  <c:v>0.77178283252776803</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.78049096619076297</c:v>
+                  <c:v>0.77817696783470003</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.78497928528354499</c:v>
+                  <c:v>0.78325327465915395</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.79298986323327103</c:v>
+                  <c:v>0.789628746784378</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.79669637472882904</c:v>
+                  <c:v>0.79348987699242701</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.800457812202234</c:v>
+                  <c:v>0.79695635557753997</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.80279777894382298</c:v>
+                  <c:v>0.80026903103066105</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.80695427099078199</c:v>
+                  <c:v>0.803299557952454</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.80983874630933395</c:v>
+                  <c:v>0.80729497224190105</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.81060953738438501</c:v>
+                  <c:v>0.80871178458094495</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.81187163402173501</c:v>
+                  <c:v>0.81094378583295901</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.81263931854195504</c:v>
+                  <c:v>0.81264051969756002</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.81322306368959496</c:v>
+                  <c:v>0.81417664714586901</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.81496328261034101</c:v>
+                  <c:v>0.81553098105630295</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.81668256491785896</c:v>
+                  <c:v>0.81682080166618398</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.81880368922965296</c:v>
+                  <c:v>0.81811677929202498</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.82013710610059498</c:v>
+                  <c:v>0.819071745567297</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.82079791469243801</c:v>
+                  <c:v>0.82057292212501398</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.82150033545571099</c:v>
+                  <c:v>0.82133555370175504</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.82268578633690204</c:v>
+                  <c:v>0.82206040478056897</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.82336228433591496</c:v>
+                  <c:v>0.82307323827250001</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.82373501870459198</c:v>
+                  <c:v>0.82339367383640205</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.82417366946778703</c:v>
+                  <c:v>0.82387204340966902</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.82475130592777601</c:v>
+                  <c:v>0.82464370527648401</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.82486439496581399</c:v>
+                  <c:v>0.82487748848245002</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.82537021518765896</c:v>
+                  <c:v>0.82528001759247205</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.82636705381127196</c:v>
+                  <c:v>0.82580955589836902</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.82677106257227995</c:v>
+                  <c:v>0.82609773044531698</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.82727406339982401</c:v>
+                  <c:v>0.826434837985766</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.82743403792085302</c:v>
+                  <c:v>0.82666695312074201</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.82784044838811599</c:v>
+                  <c:v>0.82731439173223598</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.82808602285275701</c:v>
+                  <c:v>0.82782725806158597</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.82838527023111197</c:v>
+                  <c:v>0.82825522743754898</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.82855049195819996</c:v>
+                  <c:v>0.82855214407382405</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.82881551502241102</c:v>
+                  <c:v>0.82875297632771405</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.829726127170346</c:v>
+                  <c:v>0.82916370605899203</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.82994859826502798</c:v>
+                  <c:v>0.82944491138787702</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.83014833146679001</c:v>
+                  <c:v>0.82972256224088103</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.83086171654122898</c:v>
+                  <c:v>0.83030089380658301</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.83102957492409801</c:v>
+                  <c:v>0.83046756990527404</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.83108084613155597</c:v>
+                  <c:v>0.83060876207124401</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.83128188460845698</c:v>
+                  <c:v>0.83083917420180597</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.83147342068234498</c:v>
+                  <c:v>0.83109091318764605</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.83160112880194004</c:v>
+                  <c:v>0.83117102426196199</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.832208760484622</c:v>
+                  <c:v>0.83154242769130604</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.83231297365171597</c:v>
+                  <c:v>0.83161246047283099</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.83244757362404398</c:v>
+                  <c:v>0.83168864153695798</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.83258943092614501</c:v>
+                  <c:v>0.831793153607854</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.83280955252557698</c:v>
+                  <c:v>0.83189143879594196</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.83298712215547899</c:v>
+                  <c:v>0.83228256214306695</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.83323126081746701</c:v>
+                  <c:v>0.83239659357197004</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.83328759649246398</c:v>
+                  <c:v>0.83247404097271405</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.83349871169343703</c:v>
+                  <c:v>0.83261602787407696</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.833800491305562</c:v>
+                  <c:v>0.832739168193257</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.83389071192316599</c:v>
+                  <c:v>0.83275938591232801</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.834081125460435</c:v>
+                  <c:v>0.832899748409481</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.83418651337515404</c:v>
+                  <c:v>0.83297343173380201</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.83431907711826503</c:v>
+                  <c:v>0.83307887827378602</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.83444887367808196</c:v>
+                  <c:v>0.83316967024245103</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.83468066443725597</c:v>
+                  <c:v>0.83329008575456898</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.83471833467776702</c:v>
+                  <c:v>0.83333733321036696</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.83481696126726501</c:v>
+                  <c:v>0.83340637912266802</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.83481696126726501</c:v>
+                  <c:v>0.83340637912266802</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2805,214 +3015,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>0.74241248782830904</c:v>
+                  <c:v>0.74643435415784498</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.75927961865081495</c:v>
+                  <c:v>0.75931399314186998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.77059329976165603</c:v>
+                  <c:v>0.77501245376561301</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.78319868114999902</c:v>
+                  <c:v>0.78491030668751505</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.79420635355726599</c:v>
+                  <c:v>0.79369378338761998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.799583538914167</c:v>
+                  <c:v>0.80046780221254299</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.80443430680753103</c:v>
+                  <c:v>0.80671418660317096</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.80824025416317502</c:v>
+                  <c:v>0.81065807409239399</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.81290032135873902</c:v>
+                  <c:v>0.81460987400212603</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.81581541843205096</c:v>
+                  <c:v>0.81743322825359399</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.81890001853490701</c:v>
+                  <c:v>0.81965974495805904</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.82123656545563195</c:v>
+                  <c:v>0.82182871758003595</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.82255886138238998</c:v>
+                  <c:v>0.82322835140788697</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.82392449244376198</c:v>
+                  <c:v>0.82444137961872299</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.82493062462636502</c:v>
+                  <c:v>0.82533250506185296</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.82622785927045495</c:v>
+                  <c:v>0.82594094923894001</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.82689135672908498</c:v>
+                  <c:v>0.82669980800590204</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.82753258619384396</c:v>
+                  <c:v>0.82725116223501205</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.82801044742221197</c:v>
+                  <c:v>0.82772129625360003</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.82844455582792198</c:v>
+                  <c:v>0.82829726981318996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.82915530424658201</c:v>
+                  <c:v>0.82874028676149003</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.82939576203267895</c:v>
+                  <c:v>0.82912818750026196</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.82992385024839299</c:v>
+                  <c:v>0.82951138096016597</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.83014193561860805</c:v>
+                  <c:v>0.82998467645361496</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.83054114096710396</c:v>
+                  <c:v>0.83030682375528697</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.83087675331083</c:v>
+                  <c:v>0.83061500642076302</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.83138244300516095</c:v>
+                  <c:v>0.83086354026496301</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.83161204090210195</c:v>
+                  <c:v>0.83104494080182001</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.83192188711458503</c:v>
+                  <c:v>0.83136824963983602</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.83214464536979704</c:v>
+                  <c:v>0.83157100323204003</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.83241676913076501</c:v>
+                  <c:v>0.83179488281233604</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.83268777035511299</c:v>
+                  <c:v>0.83195484296028599</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.83282811353805197</c:v>
+                  <c:v>0.83210599115206196</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.83289405603807198</c:v>
+                  <c:v>0.83229159243313999</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.83316552716146997</c:v>
+                  <c:v>0.83238044559678204</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.83317249733071197</c:v>
+                  <c:v>0.83254586409221298</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.83335714155186702</c:v>
+                  <c:v>0.83271850507303102</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.83346083260890502</c:v>
+                  <c:v>0.83280352429340199</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.83367941398367296</c:v>
+                  <c:v>0.83294113578342399</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.83386157818206497</c:v>
+                  <c:v>0.833089436901154</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.83401317283670195</c:v>
+                  <c:v>0.83321780850055904</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.834177533082198</c:v>
+                  <c:v>0.83327315177734196</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.83429088317526401</c:v>
+                  <c:v>0.83338489506698099</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.83427634241021598</c:v>
+                  <c:v>0.83347724157300995</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.83438186085244903</c:v>
+                  <c:v>0.83356081978964403</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.83448260198767299</c:v>
+                  <c:v>0.83365713997264002</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.834503512495399</c:v>
+                  <c:v>0.83373079709689202</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.83455050240040096</c:v>
+                  <c:v>0.83379931027447896</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.834554731491851</c:v>
+                  <c:v>0.83387454813616202</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.83461406929966697</c:v>
+                  <c:v>0.83399286764284597</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.83473452008948901</c:v>
+                  <c:v>0.83408932755953602</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.83481667410673499</c:v>
+                  <c:v>0.83415639100003203</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.83487394957983196</c:v>
+                  <c:v>0.83416208514812396</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.83492958040625298</c:v>
+                  <c:v>0.83422113136783804</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.83499212919091204</c:v>
+                  <c:v>0.83425073744457801</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.83508480372577698</c:v>
+                  <c:v>0.83431475294383906</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.83518118524203699</c:v>
+                  <c:v>0.83441267133097696</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.83520063384160703</c:v>
+                  <c:v>0.83444036480275896</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.83523407499066704</c:v>
+                  <c:v>0.834482520712027</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.835346067597589</c:v>
+                  <c:v>0.83451293899087098</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.83533499886440998</c:v>
+                  <c:v>0.83456176718410002</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.83529229026186402</c:v>
+                  <c:v>0.83457872736139405</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.83528158700572497</c:v>
+                  <c:v>0.83461091851150104</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.83522650439486101</c:v>
+                  <c:v>0.83465841050126599</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.83527665306569998</c:v>
+                  <c:v>0.83467005206477496</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.83533988059343001</c:v>
+                  <c:v>0.83466167677639902</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.83534995731750294</c:v>
+                  <c:v>0.83467927448867896</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.83539282255306602</c:v>
+                  <c:v>0.83468283769791496</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.83534799940479398</c:v>
+                  <c:v>0.83473400643054396</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.83534799940479398</c:v>
+                  <c:v>0.83473400643054396</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3027,11 +3237,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="346472320"/>
-        <c:axId val="346466832"/>
+        <c:axId val="364414688"/>
+        <c:axId val="364413512"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="346472320"/>
+        <c:axId val="364414688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3144,12 +3354,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="346466832"/>
+        <c:crossAx val="364413512"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="346466832"/>
+        <c:axId val="364413512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0.65000000000000013"/>
@@ -3207,7 +3417,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="346472320"/>
+        <c:crossAx val="364414688"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3620,214 +3830,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>0.20689670811171099</c:v>
+                  <c:v>0.26070199936674299</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.21150055103502</c:v>
+                  <c:v>0.24569335427127501</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.184356912631786</c:v>
+                  <c:v>0.21862555087809299</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.184238732988981</c:v>
+                  <c:v>0.20741124922750201</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.171947391045396</c:v>
+                  <c:v>0.199080648969579</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.15008252837397501</c:v>
+                  <c:v>0.17663795023315901</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.13934777445180699</c:v>
+                  <c:v>0.176118040566489</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.135293462500226</c:v>
+                  <c:v>0.17294063125426301</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.13225062366019999</c:v>
+                  <c:v>0.17127953041896701</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.14287431528126401</c:v>
+                  <c:v>0.16703731551889101</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.113534608659102</c:v>
+                  <c:v>0.14737615503968399</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.112653039370742</c:v>
+                  <c:v>0.139370501662094</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.107266967844664</c:v>
+                  <c:v>0.134198949147457</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.105081440969646</c:v>
+                  <c:v>0.12848419495073399</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>9.5692205881676207E-2</c:v>
+                  <c:v>0.124335792509762</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>8.94335803147112E-2</c:v>
+                  <c:v>0.112277800907381</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>8.9210131841901005E-2</c:v>
+                  <c:v>0.111203285059739</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>8.7510674506344296E-2</c:v>
+                  <c:v>0.10299640475463701</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>8.5705867646785797E-2</c:v>
+                  <c:v>0.100019155921117</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>8.5140029293306801E-2</c:v>
+                  <c:v>9.7091598652251795E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>8.0236298839995904E-2</c:v>
+                  <c:v>9.3586669734792793E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>7.2378565466757805E-2</c:v>
+                  <c:v>8.9667037502854E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>7.0068228089801607E-2</c:v>
+                  <c:v>8.7411760850928305E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>6.3238193289494801E-2</c:v>
+                  <c:v>8.3103209200931602E-2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>6.2863364551558096E-2</c:v>
+                  <c:v>7.5380475411144496E-2</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>6.02806564643645E-2</c:v>
+                  <c:v>7.2831769628116896E-2</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>5.7045943611740701E-2</c:v>
+                  <c:v>6.9804344280290004E-2</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>5.5229037692836297E-2</c:v>
+                  <c:v>6.5863900094645794E-2</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>5.3524914720911899E-2</c:v>
+                  <c:v>6.4905166309931595E-2</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>5.3021046470156701E-2</c:v>
+                  <c:v>6.3663639343299494E-2</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>5.2557143621047901E-2</c:v>
+                  <c:v>6.1062337134811101E-2</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>5.2467228642085202E-2</c:v>
+                  <c:v>6.0974153083806201E-2</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>5.0435500444749197E-2</c:v>
+                  <c:v>5.9697188375601701E-2</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>4.6996193581275103E-2</c:v>
+                  <c:v>5.8235627647746702E-2</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>4.6576635875247699E-2</c:v>
+                  <c:v>5.7523394060693199E-2</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>4.05625402342027E-2</c:v>
+                  <c:v>5.3070164930587797E-2</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>4.0475999363821999E-2</c:v>
+                  <c:v>5.2148403946328997E-2</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>3.7546501047758703E-2</c:v>
+                  <c:v>4.7935878989361698E-2</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>3.6654382590880899E-2</c:v>
+                  <c:v>4.5717478012335201E-2</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>3.5859342632056E-2</c:v>
+                  <c:v>4.2880229859735101E-2</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>3.5841697297351302E-2</c:v>
+                  <c:v>4.23775604470732E-2</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>3.7290335481191102E-2</c:v>
+                  <c:v>4.2565971503969298E-2</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>3.3820711211019601E-2</c:v>
+                  <c:v>4.0802560182957803E-2</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>3.3248005341182801E-2</c:v>
+                  <c:v>3.8901584759120603E-2</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>3.22048557546614E-2</c:v>
+                  <c:v>3.7614529315325197E-2</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>3.1233314658641102E-2</c:v>
+                  <c:v>3.5281791151543902E-2</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>3.10310454193077E-2</c:v>
+                  <c:v>3.4466552881035901E-2</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>3.0286599823272201E-2</c:v>
+                  <c:v>3.3966376027798603E-2</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>2.8607938875435699E-2</c:v>
+                  <c:v>3.2108879977000203E-2</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>2.8111089714841501E-2</c:v>
+                  <c:v>3.1206307745831701E-2</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>2.77310851253387E-2</c:v>
+                  <c:v>3.0832354784116899E-2</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>2.1687810160028E-2</c:v>
+                  <c:v>2.6932382254637899E-2</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>2.1340779399450699E-2</c:v>
+                  <c:v>2.6607946964281599E-2</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>2.1423073122327101E-2</c:v>
+                  <c:v>2.6603271204905601E-2</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>2.1471044193833801E-2</c:v>
+                  <c:v>2.6353743317352601E-2</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>2.1180421965927301E-2</c:v>
+                  <c:v>2.58008703583094E-2</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>1.9908333879016599E-2</c:v>
+                  <c:v>2.3430680760085899E-2</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>1.9799130552775601E-2</c:v>
+                  <c:v>2.3147045866607499E-2</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>1.9789685995265101E-2</c:v>
+                  <c:v>2.2737615191229299E-2</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>1.91214658959321E-2</c:v>
+                  <c:v>2.2375714118101901E-2</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>1.535015886913E-2</c:v>
+                  <c:v>2.06754057482436E-2</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>1.5269924438015401E-2</c:v>
+                  <c:v>2.0422532142128198E-2</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>1.4761033838664899E-2</c:v>
+                  <c:v>1.9951577105645699E-2</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>1.4738941472839899E-2</c:v>
+                  <c:v>1.9839470893254101E-2</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>1.45491297266364E-2</c:v>
+                  <c:v>1.9473258059402001E-2</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>1.4592903529605201E-2</c:v>
+                  <c:v>1.90500853175011E-2</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>1.35755395924946E-2</c:v>
+                  <c:v>1.80244992193348E-2</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>1.36649998054532E-2</c:v>
+                  <c:v>1.80719191284298E-2</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>1.34901695137603E-2</c:v>
+                  <c:v>1.7957824332433502E-2</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>1.34901695137603E-2</c:v>
+                  <c:v>1.7957824332433502E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3871,214 +4081,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>0.119373200482033</c:v>
+                  <c:v>0.12488100860519601</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.9465607145709303E-2</c:v>
+                  <c:v>0.114352284307533</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.2098726189586005E-2</c:v>
+                  <c:v>9.39288119990946E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.9296180558503501E-2</c:v>
+                  <c:v>8.4781818453746202E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.3678988309036802E-2</c:v>
+                  <c:v>7.2137447445350306E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.5052706064113499E-2</c:v>
+                  <c:v>6.2838439544546695E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.8166642965889399E-2</c:v>
+                  <c:v>5.5685630485540698E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.4853545276119802E-2</c:v>
+                  <c:v>5.1725776191935802E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.0424528282248601E-2</c:v>
+                  <c:v>4.6420094853518098E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.7298704605417198E-2</c:v>
+                  <c:v>4.2840286682438902E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.4776877990154997E-2</c:v>
+                  <c:v>4.1567348868420499E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.9723095521513698E-2</c:v>
+                  <c:v>3.95898280000039E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.8884922180892399E-2</c:v>
+                  <c:v>3.8296349145494103E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.8518443845116499E-2</c:v>
+                  <c:v>3.5921620049663101E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.7257517732615099E-2</c:v>
+                  <c:v>3.5019330534999803E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.5166806272539501E-2</c:v>
+                  <c:v>3.4483123674123102E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2.3018710234849499E-2</c:v>
+                  <c:v>3.3479557379548101E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2.2765438837354799E-2</c:v>
+                  <c:v>3.3276569864292102E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2.2840550038611299E-2</c:v>
+                  <c:v>3.1870215221005999E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2.1341426244348E-2</c:v>
+                  <c:v>3.0563786365766701E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.89123461686195E-2</c:v>
+                  <c:v>2.9963802381725399E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.8948521865011999E-2</c:v>
+                  <c:v>2.8359916294929399E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.8136346038928702E-2</c:v>
+                  <c:v>2.8174266071330299E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.8242102354701899E-2</c:v>
+                  <c:v>2.5930126523408099E-2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.8308204378322899E-2</c:v>
+                  <c:v>2.5148921525704301E-2</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.81374360462991E-2</c:v>
+                  <c:v>2.43580490858449E-2</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.69724196494585E-2</c:v>
+                  <c:v>2.39200192322373E-2</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.6529589011411602E-2</c:v>
+                  <c:v>2.38549444972334E-2</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.6529660604745599E-2</c:v>
+                  <c:v>2.19312872326431E-2</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.6904971045586199E-2</c:v>
+                  <c:v>2.1594455293049802E-2</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.5486833928566601E-2</c:v>
+                  <c:v>2.10413824630626E-2</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1.52972810114376E-2</c:v>
+                  <c:v>2.0514102597500399E-2</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1.5095387273163599E-2</c:v>
+                  <c:v>2.02481156285493E-2</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1.5031602059784399E-2</c:v>
+                  <c:v>1.9312676687198899E-2</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1.48089462634176E-2</c:v>
+                  <c:v>1.90694781455286E-2</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1.4112874129750401E-2</c:v>
+                  <c:v>1.8689364112695499E-2</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1.3976971131468599E-2</c:v>
+                  <c:v>1.7678810341686502E-2</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1.3821676415756001E-2</c:v>
+                  <c:v>1.7586942160676199E-2</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1.3291493908073901E-2</c:v>
+                  <c:v>1.72203223041947E-2</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1.2006102307381E-2</c:v>
+                  <c:v>1.6482968705710699E-2</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1.19108353772023E-2</c:v>
+                  <c:v>1.5700469331038899E-2</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1.1717671395947499E-2</c:v>
+                  <c:v>1.53200867184663E-2</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>1.16755750676809E-2</c:v>
+                  <c:v>1.4356114620424699E-2</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>1.1760922035034699E-2</c:v>
+                  <c:v>1.4019312615009299E-2</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>1.1527255363824099E-2</c:v>
+                  <c:v>1.38872225507841E-2</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>1.1456327252177699E-2</c:v>
+                  <c:v>1.37061346806392E-2</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>1.1111932175548201E-2</c:v>
+                  <c:v>1.3428926441428899E-2</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>1.0899726319140201E-2</c:v>
+                  <c:v>1.3172627966171101E-2</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>1.1146585841051399E-2</c:v>
+                  <c:v>1.2673635248618901E-2</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>1.09315415812936E-2</c:v>
+                  <c:v>1.2600264350854699E-2</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>1.07899784362556E-2</c:v>
+                  <c:v>1.25343739732538E-2</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>1.06861998500122E-2</c:v>
+                  <c:v>1.24396342929151E-2</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>1.0553808619354999E-2</c:v>
+                  <c:v>1.22661371115567E-2</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>1.0687394497913E-2</c:v>
+                  <c:v>1.2211386046059E-2</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>1.0354702478019799E-2</c:v>
+                  <c:v>1.22470248796145E-2</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>1.03281977748609E-2</c:v>
+                  <c:v>1.19322102775377E-2</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>1.01957206141788E-2</c:v>
+                  <c:v>1.1278553370128E-2</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>1.01976375570285E-2</c:v>
+                  <c:v>1.1234938197526899E-2</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>1.0217414336975201E-2</c:v>
+                  <c:v>1.1207669931559E-2</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>1.0067593494196199E-2</c:v>
+                  <c:v>1.11214860857934E-2</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>9.9146375854633796E-3</c:v>
+                  <c:v>1.08408385522512E-2</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>9.9637900078251903E-3</c:v>
+                  <c:v>1.0761187520518901E-2</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>1.00110463918555E-2</c:v>
+                  <c:v>1.06864347009179E-2</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>1.0005148925731301E-2</c:v>
+                  <c:v>1.0582557118743501E-2</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>9.9184793972403994E-3</c:v>
+                  <c:v>1.06353399980451E-2</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>9.59099997414521E-3</c:v>
+                  <c:v>1.0642553813495E-2</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>9.6041204877854499E-3</c:v>
+                  <c:v>1.03163331230575E-2</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>9.4792808436466505E-3</c:v>
+                  <c:v>1.0170418752764599E-2</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>9.5163058430269305E-3</c:v>
+                  <c:v>1.0049070616387001E-2</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>9.5163058430269305E-3</c:v>
+                  <c:v>1.0049070616387001E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4093,11 +4303,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="346469576"/>
-        <c:axId val="346473496"/>
+        <c:axId val="364415472"/>
+        <c:axId val="364416256"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="346469576"/>
+        <c:axId val="364415472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4210,12 +4420,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="346473496"/>
+        <c:crossAx val="364416256"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="346473496"/>
+        <c:axId val="364416256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4272,7 +4482,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="346469576"/>
+        <c:crossAx val="364415472"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -4685,214 +4895,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>0.76771750755111101</c:v>
+                  <c:v>0.766327328951392</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.84029172078523195</c:v>
+                  <c:v>0.81028008950052399</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.83200283543641895</c:v>
+                  <c:v>0.82334868823943097</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.81446152776780401</c:v>
+                  <c:v>0.83177270166272699</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.82262943424466295</c:v>
+                  <c:v>0.83462490203242601</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.82779661007531502</c:v>
+                  <c:v>0.85029133127237899</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.84650471551143402</c:v>
+                  <c:v>0.85302560474017097</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.83167634795045098</c:v>
+                  <c:v>0.85489516763487405</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.86220569509672995</c:v>
+                  <c:v>0.87489784121783898</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.85342214911288306</c:v>
+                  <c:v>0.87315759285928796</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.85238662777469199</c:v>
+                  <c:v>0.87854885324290199</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.87946137473936603</c:v>
+                  <c:v>0.89383434590856503</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.87153611095483996</c:v>
+                  <c:v>0.87751344808780096</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.82930273579021596</c:v>
+                  <c:v>0.84461262772019896</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.81676503511639997</c:v>
+                  <c:v>0.82511048118899399</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.798290686931456</c:v>
+                  <c:v>0.81221615539852599</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.780651124365491</c:v>
+                  <c:v>0.80125635003364204</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.77604232124692596</c:v>
+                  <c:v>0.79037244782224803</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.75644501057044899</c:v>
+                  <c:v>0.77868012774593098</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.74920197795838195</c:v>
+                  <c:v>0.76376931486520105</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.72877685964977801</c:v>
+                  <c:v>0.75265977772009596</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.71355221829691295</c:v>
+                  <c:v>0.73639902090263898</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.71203387995664902</c:v>
+                  <c:v>0.72735402655937997</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.70641271681094298</c:v>
+                  <c:v>0.72298202648197096</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.70603720778679502</c:v>
+                  <c:v>0.72048916237364102</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.701714199626982</c:v>
+                  <c:v>0.71743209919367501</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.70009356265797695</c:v>
+                  <c:v>0.71099587521481999</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.69057527120504802</c:v>
+                  <c:v>0.70323181416706104</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.68572314436945503</c:v>
+                  <c:v>0.69503470929871403</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.68461025632928696</c:v>
+                  <c:v>0.68906973129747895</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.68439613911465802</c:v>
+                  <c:v>0.68477729271847698</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.68373615810402899</c:v>
+                  <c:v>0.67884544887061504</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.67839887634306495</c:v>
+                  <c:v>0.67226918092824095</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.67093876190771395</c:v>
+                  <c:v>0.66651065380779495</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.66060469284326395</c:v>
+                  <c:v>0.65983022103404199</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.65499780072176295</c:v>
+                  <c:v>0.65960200845087402</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.65582900628761298</c:v>
+                  <c:v>0.66029389869948496</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.65913284413578599</c:v>
+                  <c:v>0.66043748103364397</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.65807038538162799</c:v>
+                  <c:v>0.65410736450821005</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.65026188996391099</c:v>
+                  <c:v>0.64995627790920696</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.64781523725415702</c:v>
+                  <c:v>0.644044497560191</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.64682072027791604</c:v>
+                  <c:v>0.640681368796576</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.64890026185244298</c:v>
+                  <c:v>0.63750494020191495</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.64520800386561805</c:v>
+                  <c:v>0.63198466526347996</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.64570769635700898</c:v>
+                  <c:v>0.63054092663786498</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.64736271607277096</c:v>
+                  <c:v>0.62997831697649098</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.64490592890669296</c:v>
+                  <c:v>0.62615828724044498</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.64259863031019704</c:v>
+                  <c:v>0.62734237468041298</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.64395496402260999</c:v>
+                  <c:v>0.62414815142538005</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.63823855763806503</c:v>
+                  <c:v>0.61887902899456004</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.63175320892431197</c:v>
+                  <c:v>0.61278252378585596</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.63095600450072198</c:v>
+                  <c:v>0.61126520231954695</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.62499638716074402</c:v>
+                  <c:v>0.60928406811964597</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.61949692429891601</c:v>
+                  <c:v>0.60615338415291198</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.61528336269322004</c:v>
+                  <c:v>0.60342455516900795</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.61743388561663204</c:v>
+                  <c:v>0.60255006745098805</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.61134705954841795</c:v>
+                  <c:v>0.59902987081057002</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.608456464240691</c:v>
+                  <c:v>0.59621234806785195</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.60771758140620102</c:v>
+                  <c:v>0.59379821765230101</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.59994233117439</c:v>
+                  <c:v>0.590989217035776</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.60220976584931896</c:v>
+                  <c:v>0.59087769919958799</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.60074733808977099</c:v>
+                  <c:v>0.58865451722088302</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.59111840449851705</c:v>
+                  <c:v>0.58208297535624598</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.59064203856828601</c:v>
+                  <c:v>0.58584005692535002</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.587024337256005</c:v>
+                  <c:v>0.58307570775395201</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.58379151659845396</c:v>
+                  <c:v>0.57981293783868104</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.57982089190990305</c:v>
+                  <c:v>0.57713306137931397</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.58140130410654001</c:v>
+                  <c:v>0.57899113104956001</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.57696909372309102</c:v>
+                  <c:v>0.57599198680548103</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.57696909372309102</c:v>
+                  <c:v>0.57599198680548103</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4936,214 +5146,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>0.66701421116973103</c:v>
+                  <c:v>0.65785967184468397</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.73899085096005901</c:v>
+                  <c:v>0.76878519026251202</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.77538745348101101</c:v>
+                  <c:v>0.79585710269721699</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.78516183876153001</c:v>
+                  <c:v>0.79560272586738701</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.80308959846161199</c:v>
+                  <c:v>0.79034724970395498</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.82596452057717495</c:v>
+                  <c:v>0.83887158288117103</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.83893596972796503</c:v>
+                  <c:v>0.84812795711163103</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.85364362187459697</c:v>
+                  <c:v>0.85768402597443205</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.84044337634338995</c:v>
+                  <c:v>0.84805252868182102</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.81840478060594601</c:v>
+                  <c:v>0.81129981934165796</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.78536684283249802</c:v>
+                  <c:v>0.77821256913167003</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.76371007240125599</c:v>
+                  <c:v>0.74389195325088298</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.74275277961987296</c:v>
+                  <c:v>0.72641497036548097</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.72823873838502495</c:v>
+                  <c:v>0.70378202490046005</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.70417912025706397</c:v>
+                  <c:v>0.68977105070322897</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.68789709766645302</c:v>
+                  <c:v>0.67927305549972905</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.69231984599127405</c:v>
+                  <c:v>0.67031192566827902</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.68383636681303195</c:v>
+                  <c:v>0.668494426648095</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.676594662878655</c:v>
+                  <c:v>0.66440811429056401</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.66062550751193105</c:v>
+                  <c:v>0.65519974043786</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.65661803374213101</c:v>
+                  <c:v>0.65058988357973901</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.66589933984816896</c:v>
+                  <c:v>0.65211485898766797</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.67363447739359905</c:v>
+                  <c:v>0.643747873115321</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.67903158689402898</c:v>
+                  <c:v>0.63842573539364</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.66383082571386298</c:v>
+                  <c:v>0.63587619201027401</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.65501035002130004</c:v>
+                  <c:v>0.62540598616874998</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.66103629440308997</c:v>
+                  <c:v>0.62059281124683296</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.65196850773374004</c:v>
+                  <c:v>0.61696652022170595</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.65204646995820303</c:v>
+                  <c:v>0.61861723971659499</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.64431509987807301</c:v>
+                  <c:v>0.61999149640982498</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.63609799676098699</c:v>
+                  <c:v>0.61903531959722502</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.63355567206997598</c:v>
+                  <c:v>0.60992137765255305</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.62869424318627798</c:v>
+                  <c:v>0.60678090823830599</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.62622291462129598</c:v>
+                  <c:v>0.60137228443586499</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.61040180973718206</c:v>
+                  <c:v>0.60666678218751802</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.61409591904022398</c:v>
+                  <c:v>0.60179813704780505</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.61179686845173598</c:v>
+                  <c:v>0.59901943508168198</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.61511033251131098</c:v>
+                  <c:v>0.59573295620852496</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.60664776257425701</c:v>
+                  <c:v>0.59454290676101895</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.60802014054188402</c:v>
+                  <c:v>0.59372909873417701</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.60306642974028701</c:v>
+                  <c:v>0.59246863393919302</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.60006292540463702</c:v>
+                  <c:v>0.59196079793068002</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.59770364964266098</c:v>
+                  <c:v>0.59289269221373397</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.60382099947779799</c:v>
+                  <c:v>0.58801689661593204</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.60525583688915396</c:v>
+                  <c:v>0.58615804415236406</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.60219727701604397</c:v>
+                  <c:v>0.58108015357718501</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.597454574095028</c:v>
+                  <c:v>0.57217800795839302</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.591069846853432</c:v>
+                  <c:v>0.57133534445259104</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.59238385066855104</c:v>
+                  <c:v>0.56838327019546797</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.58524359838634699</c:v>
+                  <c:v>0.56841543665190497</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.58159434954741196</c:v>
+                  <c:v>0.56516241411409496</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.57845712991113496</c:v>
+                  <c:v>0.56240424475067297</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.582732557220208</c:v>
+                  <c:v>0.56229445491262497</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.58277815622320495</c:v>
+                  <c:v>0.56210403064740699</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.57599098937774595</c:v>
+                  <c:v>0.56320858531235296</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.57538057710219703</c:v>
+                  <c:v>0.55919337935240898</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.56602151291208502</c:v>
+                  <c:v>0.55201906386788901</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.56472236270056897</c:v>
+                  <c:v>0.55189030443926002</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.56648774670616397</c:v>
+                  <c:v>0.55235808292267297</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.56734714163703204</c:v>
+                  <c:v>0.55403685691287996</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.56398337275302801</c:v>
+                  <c:v>0.55112708068848704</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.56256926684067199</c:v>
+                  <c:v>0.549381423177977</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.56904980042366904</c:v>
+                  <c:v>0.54790210541944995</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.57706727927472801</c:v>
+                  <c:v>0.545220815309994</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.57620998077638896</c:v>
+                  <c:v>0.54704200004397796</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.57349459106536205</c:v>
+                  <c:v>0.55043135657992504</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.57194400301579595</c:v>
+                  <c:v>0.54964438714199304</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.56372406312326095</c:v>
+                  <c:v>0.54721221855914803</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.56885973039349103</c:v>
+                  <c:v>0.54483784949371905</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.56885973039349103</c:v>
+                  <c:v>0.54483784949371905</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5158,11 +5368,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="346474280"/>
-        <c:axId val="346464872"/>
+        <c:axId val="364406848"/>
+        <c:axId val="364407240"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="346474280"/>
+        <c:axId val="364406848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5275,12 +5485,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="346464872"/>
+        <c:crossAx val="364407240"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="346464872"/>
+        <c:axId val="364407240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5337,7 +5547,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="346474280"/>
+        <c:crossAx val="364406848"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -9369,13 +9579,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>721.9</v>
+        <v>757.1</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>438.3</v>
+        <v>366.1</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -9383,13 +9593,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>715.7</v>
+        <v>708.93333333333305</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>375.7</v>
+        <v>335.3</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -9397,13 +9607,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>631</v>
+        <v>646.6</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4">
-        <v>337.4</v>
+        <v>278.7</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -9411,13 +9621,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>584.4</v>
+        <v>603.96666666666601</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>266.89999999999998</v>
+        <v>252.933333333333</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -9425,13 +9635,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>527.79999999999995</v>
+        <v>554.93333333333305</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6">
-        <v>227.4</v>
+        <v>226.56666666666601</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -9439,13 +9649,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>472.9</v>
+        <v>503.7</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7">
-        <v>216</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -9453,13 +9663,13 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>442</v>
+        <v>468.9</v>
       </c>
       <c r="C8">
         <v>7</v>
       </c>
       <c r="D8">
-        <v>197</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -9467,13 +9677,13 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>436.3</v>
+        <v>452.33333333333297</v>
       </c>
       <c r="C9">
         <v>8</v>
       </c>
       <c r="D9">
-        <v>188.7</v>
+        <v>158.833333333333</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -9481,13 +9691,13 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>422.9</v>
+        <v>428.06666666666598</v>
       </c>
       <c r="C10">
         <v>9</v>
       </c>
       <c r="D10">
-        <v>170.9</v>
+        <v>145.9</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -9495,13 +9705,13 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>412</v>
+        <v>410.3</v>
       </c>
       <c r="C11">
         <v>10</v>
       </c>
       <c r="D11">
-        <v>163.9</v>
+        <v>136.433333333333</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -9509,13 +9719,13 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>359.2</v>
+        <v>371.433333333333</v>
       </c>
       <c r="C12">
         <v>11</v>
       </c>
       <c r="D12">
-        <v>150.1</v>
+        <v>134.13333333333301</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -9523,13 +9733,13 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>349.7</v>
+        <v>356.86666666666599</v>
       </c>
       <c r="C13">
         <v>12</v>
       </c>
       <c r="D13">
-        <v>129.80000000000001</v>
+        <v>123.766666666666</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -9537,13 +9747,13 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>330.7</v>
+        <v>342.933333333333</v>
       </c>
       <c r="C14">
         <v>13</v>
       </c>
       <c r="D14">
-        <v>127.9</v>
+        <v>120.06666666666599</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -9551,13 +9761,13 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>328.4</v>
+        <v>324.86666666666599</v>
       </c>
       <c r="C15">
         <v>14</v>
       </c>
       <c r="D15">
-        <v>127.8</v>
+        <v>114.833333333333</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -9565,13 +9775,13 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>298.8</v>
+        <v>308.03333333333302</v>
       </c>
       <c r="C16">
         <v>15</v>
       </c>
       <c r="D16">
-        <v>123.2</v>
+        <v>113.266666666666</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -9579,13 +9789,13 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>279.39999999999998</v>
+        <v>279.60000000000002</v>
       </c>
       <c r="C17">
         <v>16</v>
       </c>
       <c r="D17">
-        <v>111.6</v>
+        <v>111.56666666666599</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -9593,13 +9803,13 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>279.39999999999998</v>
+        <v>275.26666666666603</v>
       </c>
       <c r="C18">
         <v>17</v>
       </c>
       <c r="D18">
-        <v>107.2</v>
+        <v>106.2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -9607,13 +9817,13 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>274.8</v>
+        <v>260.96666666666601</v>
       </c>
       <c r="C19">
         <v>18</v>
       </c>
       <c r="D19">
-        <v>106.8</v>
+        <v>104.333333333333</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -9621,13 +9831,13 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>271.7</v>
+        <v>254</v>
       </c>
       <c r="C20">
         <v>19</v>
       </c>
       <c r="D20">
-        <v>106.1</v>
+        <v>101.23333333333299</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -9635,13 +9845,13 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>269.7</v>
+        <v>244.166666666666</v>
       </c>
       <c r="C21">
         <v>20</v>
       </c>
       <c r="D21">
-        <v>93.5</v>
+        <v>98.033333333333303</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -9649,13 +9859,13 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>260.39999999999998</v>
+        <v>236.06666666666601</v>
       </c>
       <c r="C22">
         <v>21</v>
       </c>
       <c r="D22">
-        <v>84.5</v>
+        <v>95.633333333333297</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -9663,13 +9873,13 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>242.3</v>
+        <v>226.73333333333301</v>
       </c>
       <c r="C23">
         <v>22</v>
       </c>
       <c r="D23">
-        <v>84.5</v>
+        <v>91.966666666666598</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -9677,13 +9887,13 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>229.1</v>
+        <v>221.1</v>
       </c>
       <c r="C24">
         <v>23</v>
       </c>
       <c r="D24">
-        <v>79.099999999999994</v>
+        <v>90.3333333333333</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -9691,13 +9901,13 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>215.8</v>
+        <v>212.766666666666</v>
       </c>
       <c r="C25">
         <v>24</v>
       </c>
       <c r="D25">
-        <v>79.099999999999994</v>
+        <v>83.433333333333294</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -9705,13 +9915,13 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>215</v>
+        <v>199.2</v>
       </c>
       <c r="C26">
         <v>25</v>
       </c>
       <c r="D26">
-        <v>77.400000000000006</v>
+        <v>81.066666666666606</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -9719,13 +9929,13 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>209.1</v>
+        <v>195.7</v>
       </c>
       <c r="C27">
         <v>26</v>
       </c>
       <c r="D27">
-        <v>77.400000000000006</v>
+        <v>79.400000000000006</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -9733,13 +9943,13 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>194.3</v>
+        <v>187.06666666666601</v>
       </c>
       <c r="C28">
         <v>27</v>
       </c>
       <c r="D28">
-        <v>72.7</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -9747,13 +9957,13 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>188.2</v>
+        <v>178.5</v>
       </c>
       <c r="C29">
         <v>28</v>
       </c>
       <c r="D29">
-        <v>71.400000000000006</v>
+        <v>77.566666666666606</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -9761,13 +9971,13 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>183.9</v>
+        <v>176.56666666666601</v>
       </c>
       <c r="C30">
         <v>29</v>
       </c>
       <c r="D30">
-        <v>67.599999999999994</v>
+        <v>73.433333333333294</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -9775,13 +9985,13 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>182.7</v>
+        <v>174.23333333333301</v>
       </c>
       <c r="C31">
         <v>30</v>
       </c>
       <c r="D31">
-        <v>66.400000000000006</v>
+        <v>72.233333333333306</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -9789,13 +9999,13 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>179.1</v>
+        <v>166.63333333333301</v>
       </c>
       <c r="C32">
         <v>31</v>
       </c>
       <c r="D32">
-        <v>58.9</v>
+        <v>70.400000000000006</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -9803,13 +10013,13 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>179.1</v>
+        <v>166.433333333333</v>
       </c>
       <c r="C33">
         <v>32</v>
       </c>
       <c r="D33">
-        <v>57.2</v>
+        <v>68.566666666666606</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -9817,13 +10027,13 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>171.3</v>
+        <v>163.266666666666</v>
       </c>
       <c r="C34">
         <v>33</v>
       </c>
       <c r="D34">
-        <v>56.7</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -9831,13 +10041,13 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>164.8</v>
+        <v>159.86666666666599</v>
       </c>
       <c r="C35">
         <v>34</v>
       </c>
       <c r="D35">
-        <v>55.7</v>
+        <v>64.400000000000006</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -9845,13 +10055,13 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>161.30000000000001</v>
+        <v>156.9</v>
       </c>
       <c r="C36">
         <v>35</v>
       </c>
       <c r="D36">
-        <v>55.3</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -9859,13 +10069,13 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>156.30000000000001</v>
+        <v>148.6</v>
       </c>
       <c r="C37">
         <v>36</v>
       </c>
       <c r="D37">
-        <v>54.9</v>
+        <v>60.266666666666602</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -9873,13 +10083,13 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>156.30000000000001</v>
+        <v>146.86666666666599</v>
       </c>
       <c r="C38">
         <v>37</v>
       </c>
       <c r="D38">
-        <v>54.9</v>
+        <v>57.1666666666666</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -9887,13 +10097,13 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>151.30000000000001</v>
+        <v>138.6</v>
       </c>
       <c r="C39">
         <v>38</v>
       </c>
       <c r="D39">
-        <v>54.9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -9901,13 +10111,13 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>149.19999999999999</v>
+        <v>134.03333333333299</v>
       </c>
       <c r="C40">
         <v>39</v>
       </c>
       <c r="D40">
-        <v>50.4</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -9915,13 +10125,13 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>145.19999999999999</v>
+        <v>127.533333333333</v>
       </c>
       <c r="C41">
         <v>40</v>
       </c>
       <c r="D41">
-        <v>43.9</v>
+        <v>53.366666666666603</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -9929,13 +10139,13 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>145</v>
+        <v>125.5</v>
       </c>
       <c r="C42">
         <v>41</v>
       </c>
       <c r="D42">
-        <v>43.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -9943,13 +10153,13 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>143.5</v>
+        <v>122.9</v>
       </c>
       <c r="C43">
         <v>42</v>
       </c>
       <c r="D43">
-        <v>42.6</v>
+        <v>49.466666666666598</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -9957,13 +10167,13 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>123.7</v>
+        <v>115.666666666666</v>
       </c>
       <c r="C44">
         <v>43</v>
       </c>
       <c r="D44">
-        <v>42.3</v>
+        <v>45.733333333333299</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -9971,13 +10181,13 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>121</v>
+        <v>108.966666666666</v>
       </c>
       <c r="C45">
         <v>44</v>
       </c>
       <c r="D45">
-        <v>42.3</v>
+        <v>43.966666666666598</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -9985,13 +10195,13 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>118.9</v>
+        <v>106.533333333333</v>
       </c>
       <c r="C46">
         <v>45</v>
       </c>
       <c r="D46">
-        <v>39.1</v>
+        <v>43.733333333333299</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -9999,13 +10209,13 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>111.2</v>
+        <v>98</v>
       </c>
       <c r="C47">
         <v>46</v>
       </c>
       <c r="D47">
-        <v>38.700000000000003</v>
+        <v>43.133333333333297</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -10013,13 +10223,13 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>109.5</v>
+        <v>95.533333333333303</v>
       </c>
       <c r="C48">
         <v>47</v>
       </c>
       <c r="D48">
-        <v>38.299999999999997</v>
+        <v>42.1666666666666</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -10027,13 +10237,13 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>108.5</v>
+        <v>94.866666666666603</v>
       </c>
       <c r="C49">
         <v>48</v>
       </c>
       <c r="D49">
-        <v>38.1</v>
+        <v>41.433333333333302</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -10041,13 +10251,13 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>106.7</v>
+        <v>91.133333333333297</v>
       </c>
       <c r="C50">
         <v>49</v>
       </c>
       <c r="D50">
-        <v>38</v>
+        <v>40.566666666666599</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -10055,13 +10265,13 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>103</v>
+        <v>88.233333333333306</v>
       </c>
       <c r="C51">
         <v>50</v>
       </c>
       <c r="D51">
-        <v>37</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -10069,13 +10279,13 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>101.1</v>
+        <v>87</v>
       </c>
       <c r="C52">
         <v>51</v>
       </c>
       <c r="D52">
-        <v>36.4</v>
+        <v>40.299999999999997</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -10083,13 +10293,13 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>76.099999999999994</v>
+        <v>75.5</v>
       </c>
       <c r="C53">
         <v>52</v>
       </c>
       <c r="D53">
-        <v>36.299999999999997</v>
+        <v>39.466666666666598</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -10097,13 +10307,13 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>73.8</v>
+        <v>74.066666666666606</v>
       </c>
       <c r="C54">
         <v>53</v>
       </c>
       <c r="D54">
-        <v>35.6</v>
+        <v>38.700000000000003</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -10117,7 +10327,7 @@
         <v>54</v>
       </c>
       <c r="D55">
-        <v>35.4</v>
+        <v>38.700000000000003</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -10125,13 +10335,13 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>73.3</v>
+        <v>72.966666666666598</v>
       </c>
       <c r="C56">
         <v>55</v>
       </c>
       <c r="D56">
-        <v>34.200000000000003</v>
+        <v>37.933333333333302</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -10139,13 +10349,13 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>72.2</v>
+        <v>71.733333333333306</v>
       </c>
       <c r="C57">
         <v>56</v>
       </c>
       <c r="D57">
-        <v>34.200000000000003</v>
+        <v>36.533333333333303</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -10153,13 +10363,13 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>71.5</v>
+        <v>68.066666666666606</v>
       </c>
       <c r="C58">
         <v>57</v>
       </c>
       <c r="D58">
-        <v>34.200000000000003</v>
+        <v>34.3333333333333</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -10167,13 +10377,13 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>68.2</v>
+        <v>66.266666666666595</v>
       </c>
       <c r="C59">
         <v>58</v>
       </c>
       <c r="D59">
-        <v>34.200000000000003</v>
+        <v>33.966666666666598</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -10181,13 +10391,13 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>68.099999999999994</v>
+        <v>65.266666666666595</v>
       </c>
       <c r="C60">
         <v>59</v>
       </c>
       <c r="D60">
-        <v>33.799999999999997</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -10195,13 +10405,13 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>64.8</v>
+        <v>64</v>
       </c>
       <c r="C61">
         <v>60</v>
       </c>
       <c r="D61">
-        <v>31.8</v>
+        <v>32.6666666666666</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -10209,13 +10419,13 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>55.6</v>
+        <v>60.933333333333302</v>
       </c>
       <c r="C62">
         <v>61</v>
       </c>
       <c r="D62">
-        <v>30.6</v>
+        <v>31.1666666666666</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -10223,13 +10433,13 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>54.7</v>
+        <v>59.9</v>
       </c>
       <c r="C63">
         <v>62</v>
       </c>
       <c r="D63">
-        <v>29.7</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -10237,13 +10447,13 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>52.7</v>
+        <v>58</v>
       </c>
       <c r="C64">
         <v>63</v>
       </c>
       <c r="D64">
-        <v>29.3</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -10251,13 +10461,13 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>52.5</v>
+        <v>56.733333333333299</v>
       </c>
       <c r="C65">
         <v>64</v>
       </c>
       <c r="D65">
-        <v>28.9</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -10265,13 +10475,13 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>51</v>
+        <v>55.8333333333333</v>
       </c>
       <c r="C66">
         <v>65</v>
       </c>
       <c r="D66">
-        <v>28.9</v>
+        <v>29.1666666666666</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -10279,13 +10489,13 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>50.1</v>
+        <v>54.233333333333299</v>
       </c>
       <c r="C67">
         <v>66</v>
       </c>
       <c r="D67">
-        <v>28.1</v>
+        <v>29.066666666666599</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -10293,13 +10503,13 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>44.1</v>
+        <v>50</v>
       </c>
       <c r="C68">
         <v>67</v>
       </c>
       <c r="D68">
-        <v>28.1</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -10307,13 +10517,13 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>44.1</v>
+        <v>50</v>
       </c>
       <c r="C69">
         <v>68</v>
       </c>
       <c r="D69">
-        <v>28</v>
+        <v>26.8666666666666</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -10321,13 +10531,13 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>44</v>
+        <v>49.7</v>
       </c>
       <c r="C70">
         <v>69</v>
       </c>
       <c r="D70">
-        <v>28</v>
+        <v>26.3333333333333</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -10335,13 +10545,13 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>44</v>
+        <v>49.7</v>
       </c>
       <c r="C71">
         <v>70</v>
       </c>
       <c r="D71">
-        <v>28</v>
+        <v>26.3333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -10374,13 +10584,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.06383523139125E-2</v>
+        <v>1.04146754726555E-2</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>1.0922005258687899E-2</v>
+        <v>1.1160219798206E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -10388,13 +10598,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>7.5810539785954702E-3</v>
+        <v>8.0076639865018003E-3</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>8.0870889854810207E-3</v>
+        <v>8.2216887993449596E-3</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -10402,13 +10612,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>6.2869038803537204E-3</v>
+        <v>6.5962787772507704E-3</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4">
-        <v>6.3536332778655899E-3</v>
+        <v>5.7309982239340104E-3</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -10416,13 +10626,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>5.1250426202196402E-3</v>
+        <v>5.3797199845398297E-3</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>4.5626268386532703E-3</v>
+        <v>4.29906043263304E-3</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -10430,13 +10640,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>4.5059768851830901E-3</v>
+        <v>4.6458918099082699E-3</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6">
-        <v>3.4088873750394099E-3</v>
+        <v>3.2842768942501601E-3</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -10444,13 +10654,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>3.4832735193812002E-3</v>
+        <v>3.75063604676287E-3</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7">
-        <v>2.82323478039429E-3</v>
+        <v>2.5561964997723001E-3</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -10458,13 +10668,13 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2.87457600733278E-3</v>
+        <v>3.1679456088083702E-3</v>
       </c>
       <c r="C8">
         <v>7</v>
       </c>
       <c r="D8">
-        <v>2.2822973171864902E-3</v>
+        <v>2.0479240244974501E-3</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -10472,13 +10682,13 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>2.5010040884948801E-3</v>
+        <v>2.6980196969778E-3</v>
       </c>
       <c r="C9">
         <v>8</v>
       </c>
       <c r="D9">
-        <v>1.91130874129758E-3</v>
+        <v>1.6864033182758501E-3</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -10486,13 +10696,13 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>2.1536991348774198E-3</v>
+        <v>2.2424378073924601E-3</v>
       </c>
       <c r="C10">
         <v>9</v>
       </c>
       <c r="D10">
-        <v>1.56063567460619E-3</v>
+        <v>1.4179918376485501E-3</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -10500,13 +10710,13 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1.7999949864495901E-3</v>
+        <v>1.86947651610022E-3</v>
       </c>
       <c r="C11">
         <v>10</v>
       </c>
       <c r="D11">
-        <v>1.37017979641644E-3</v>
+        <v>1.23800837385637E-3</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -10514,13 +10724,13 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>1.6782209008272E-3</v>
+        <v>1.64681563198507E-3</v>
       </c>
       <c r="C12">
         <v>11</v>
       </c>
       <c r="D12">
-        <v>1.16922732111627E-3</v>
+        <v>1.0817484427115701E-3</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -10528,13 +10738,13 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1.41802598362938E-3</v>
+        <v>1.44664542601287E-3</v>
       </c>
       <c r="C13">
         <v>12</v>
       </c>
-      <c r="D13">
-        <v>1.03575950156211E-3</v>
+      <c r="D13" s="1">
+        <v>9.6757001222246995E-4</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -10542,13 +10752,13 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>1.20121949107636E-3</v>
+        <v>1.27377801939478E-3</v>
       </c>
       <c r="C14">
         <v>13</v>
       </c>
       <c r="D14" s="1">
-        <v>9.7026855783229103E-4</v>
+        <v>8.7507665939443903E-4</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -10556,13 +10766,13 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>1.11484019260655E-3</v>
+        <v>1.1647472184426E-3</v>
       </c>
       <c r="C15">
         <v>14</v>
       </c>
       <c r="D15" s="1">
-        <v>9.0182313150035396E-4</v>
+        <v>7.8849333922230999E-4</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -10570,13 +10780,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>9.5723548459934E-4</v>
+        <v>1.05473615874447E-3</v>
       </c>
       <c r="C16">
         <v>15</v>
       </c>
       <c r="D16" s="1">
-        <v>8.4284057047047801E-4</v>
+        <v>7.24614586522773E-4</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -10584,13 +10794,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>9.0294871873444402E-4</v>
+        <v>9.4777766504134601E-4</v>
       </c>
       <c r="C17">
         <v>16</v>
       </c>
       <c r="D17" s="1">
-        <v>8.0849268787772295E-4</v>
+        <v>6.8840541458690203E-4</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -10598,13 +10808,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <v>8.3926885306566802E-4</v>
+        <v>8.8060617981324397E-4</v>
       </c>
       <c r="C18">
         <v>17</v>
       </c>
       <c r="D18" s="1">
-        <v>7.6646872313275796E-4</v>
+        <v>6.5296824339923303E-4</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -10612,13 +10822,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>7.4997845979743699E-4</v>
+        <v>8.2126508645216699E-4</v>
       </c>
       <c r="C19">
         <v>18</v>
       </c>
       <c r="D19" s="1">
-        <v>7.40578425652974E-4</v>
+        <v>6.1658638553614903E-4</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -10626,13 +10836,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="1">
-        <v>7.3177891081085598E-4</v>
+        <v>7.7045134651684605E-4</v>
       </c>
       <c r="C20">
         <v>19</v>
       </c>
       <c r="D20" s="1">
-        <v>7.1458306061550998E-4</v>
+        <v>5.8903816628338296E-4</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -10640,13 +10850,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="1">
-        <v>7.04195703866309E-4</v>
+        <v>7.2775895857640305E-4</v>
       </c>
       <c r="C21">
         <v>20</v>
       </c>
       <c r="D21" s="1">
-        <v>6.9821868185286E-4</v>
+        <v>5.6793528092820603E-4</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -10654,13 +10864,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="1">
-        <v>6.7935852139595497E-4</v>
+        <v>6.9115023501205102E-4</v>
       </c>
       <c r="C22">
         <v>21</v>
       </c>
       <c r="D22" s="1">
-        <v>6.6646549987467798E-4</v>
+        <v>5.5223677759925897E-4</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -10668,13 +10878,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="1">
-        <v>6.6737580397042799E-4</v>
+        <v>6.7538366421427505E-4</v>
       </c>
       <c r="C23">
         <v>22</v>
       </c>
       <c r="D23" s="1">
-        <v>6.4680385897619404E-4</v>
+        <v>5.2869694813629695E-4</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -10682,13 +10892,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="1">
-        <v>6.4437470837393597E-4</v>
+        <v>6.5132020217662499E-4</v>
       </c>
       <c r="C24">
         <v>23</v>
       </c>
       <c r="D24" s="1">
-        <v>6.1812803158358201E-4</v>
+        <v>5.0914001296105502E-4</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -10696,13 +10906,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="1">
-        <v>6.1737335842525904E-4</v>
+        <v>6.2909518521640198E-4</v>
       </c>
       <c r="C25">
         <v>24</v>
       </c>
       <c r="D25" s="1">
-        <v>5.9525635907166905E-4</v>
+        <v>4.89989829958158E-4</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -10710,13 +10920,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="1">
-        <v>5.8332341370480399E-4</v>
+        <v>5.9135634597828305E-4</v>
       </c>
       <c r="C26">
         <v>25</v>
       </c>
       <c r="D26" s="1">
-        <v>5.8159001371037398E-4</v>
+        <v>4.6717118843020102E-4</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -10724,13 +10934,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <v>5.6668102385006296E-4</v>
+        <v>5.5355106421415201E-4</v>
       </c>
       <c r="C27">
         <v>26</v>
       </c>
       <c r="D27" s="1">
-        <v>5.6020073221486498E-4</v>
+        <v>4.5772606205040799E-4</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -10738,13 +10948,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <v>5.5714372536035302E-4</v>
+        <v>5.3912597463276902E-4</v>
       </c>
       <c r="C28">
         <v>27</v>
       </c>
       <c r="D28" s="1">
-        <v>5.3868931951656595E-4</v>
+        <v>4.4828608551544802E-4</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -10752,13 +10962,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="1">
-        <v>5.4061174476971398E-4</v>
+        <v>5.2009832919238698E-4</v>
       </c>
       <c r="C29">
         <v>28</v>
       </c>
       <c r="D29" s="1">
-        <v>5.2855522554097999E-4</v>
+        <v>4.3411752436227097E-4</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -10766,13 +10976,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="1">
-        <v>5.3013223536924905E-4</v>
+        <v>5.1330600144477198E-4</v>
       </c>
       <c r="C30">
         <v>29</v>
       </c>
       <c r="D30" s="1">
-        <v>5.1616230201372004E-4</v>
+        <v>4.2279679683340001E-4</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -10780,13 +10990,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="1">
-        <v>5.0993600629680195E-4</v>
+        <v>4.9774352522451105E-4</v>
       </c>
       <c r="C31">
         <v>30</v>
       </c>
       <c r="D31" s="1">
-        <v>5.0006729246403095E-4</v>
+        <v>4.0672944419178501E-4</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -10794,13 +11004,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="1">
-        <v>4.7889329939988399E-4</v>
+        <v>4.7659553261708901E-4</v>
       </c>
       <c r="C32">
         <v>31</v>
       </c>
       <c r="D32" s="1">
-        <v>4.8719786797702801E-4</v>
+        <v>3.99319699942204E-4</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -10808,13 +11018,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="1">
-        <v>4.6504341579952898E-4</v>
+        <v>4.5677708278977298E-4</v>
       </c>
       <c r="C33">
         <v>32</v>
       </c>
       <c r="D33" s="1">
-        <v>4.7143359059263198E-4</v>
+        <v>3.9353951123557502E-4</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -10822,13 +11032,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="1">
-        <v>4.5707094722044998E-4</v>
+        <v>4.4360034765033901E-4</v>
       </c>
       <c r="C34">
         <v>33</v>
       </c>
       <c r="D34" s="1">
-        <v>3.8057015153041798E-4</v>
+        <v>3.9180259351326898E-4</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -10836,13 +11046,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="1">
-        <v>4.4372899727806601E-4</v>
+        <v>4.3376210842222798E-4</v>
       </c>
       <c r="C35">
         <v>34</v>
       </c>
       <c r="D35" s="1">
-        <v>3.7369445028088798E-4</v>
+        <v>3.7945811694362801E-4</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -10850,13 +11060,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="1">
-        <v>4.3632795608312898E-4</v>
+        <v>4.2811783980542501E-4</v>
       </c>
       <c r="C36">
         <v>35</v>
       </c>
       <c r="D36" s="1">
-        <v>3.6844290072597598E-4</v>
+        <v>3.6915514124951499E-4</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -10864,13 +11074,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="1">
-        <v>4.46962550879127E-4</v>
+        <v>4.2521028960767403E-4</v>
       </c>
       <c r="C37">
         <v>36</v>
       </c>
       <c r="D37" s="1">
-        <v>3.6820191319592602E-4</v>
+        <v>3.6681257520363797E-4</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -10878,13 +11088,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="1">
-        <v>4.3345505970351998E-4</v>
+        <v>4.1562417559770903E-4</v>
       </c>
       <c r="C38">
         <v>37</v>
       </c>
       <c r="D38" s="1">
-        <v>3.6779144520681002E-4</v>
+        <v>3.6222054326156899E-4</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -10892,13 +11102,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="1">
-        <v>4.3111628003847803E-4</v>
+        <v>4.0967264583203101E-4</v>
       </c>
       <c r="C39">
         <v>38</v>
       </c>
       <c r="D39" s="1">
-        <v>3.6795697023902401E-4</v>
+        <v>3.5895964741454998E-4</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -10906,13 +11116,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="1">
-        <v>4.1353249983020298E-4</v>
+        <v>4.0434279411852698E-4</v>
       </c>
       <c r="C40">
         <v>39</v>
       </c>
       <c r="D40" s="1">
-        <v>3.6697157192033602E-4</v>
+        <v>3.5213504536005301E-4</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -10920,13 +11130,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="1">
-        <v>4.0872445589815702E-4</v>
+        <v>4.0381413389985302E-4</v>
       </c>
       <c r="C41">
         <v>40</v>
       </c>
       <c r="D41" s="1">
-        <v>3.5964089930351202E-4</v>
+        <v>3.44035010877063E-4</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -10934,13 +11144,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="1">
-        <v>4.0146132370063502E-4</v>
+        <v>3.9839724110683902E-4</v>
       </c>
       <c r="C42">
         <v>41</v>
       </c>
       <c r="D42" s="1">
-        <v>3.5248017675008003E-4</v>
+        <v>3.3900046969914801E-4</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -10948,13 +11158,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="1">
-        <v>3.8761300124531302E-4</v>
+        <v>3.8692930846641598E-4</v>
       </c>
       <c r="C43">
         <v>42</v>
       </c>
       <c r="D43" s="1">
-        <v>3.4820992340059003E-4</v>
+        <v>3.3496578216205198E-4</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -10962,13 +11172,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="1">
-        <v>3.7493819419275103E-4</v>
+        <v>3.8546700473082198E-4</v>
       </c>
       <c r="C44">
         <v>43</v>
       </c>
       <c r="D44" s="1">
-        <v>3.4408588864611399E-4</v>
+        <v>3.32704053507927E-4</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -10976,13 +11186,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="1">
-        <v>3.6665950189994801E-4</v>
+        <v>3.79620691588214E-4</v>
       </c>
       <c r="C45">
         <v>44</v>
       </c>
       <c r="D45" s="1">
-        <v>3.4064144432624402E-4</v>
+        <v>3.3021306688383299E-4</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -10990,13 +11200,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="1">
-        <v>3.6733870067678399E-4</v>
+        <v>3.7697438704909598E-4</v>
       </c>
       <c r="C46">
         <v>45</v>
       </c>
       <c r="D46" s="1">
-        <v>3.3922988482544899E-4</v>
+        <v>3.24618311138663E-4</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -11004,13 +11214,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="1">
-        <v>3.4827981707836699E-4</v>
+        <v>3.6549298714095299E-4</v>
       </c>
       <c r="C47">
         <v>46</v>
       </c>
       <c r="D47" s="1">
-        <v>3.2792017884209E-4</v>
+        <v>3.2171115458442899E-4</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -11018,13 +11228,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="1">
-        <v>3.4345794781199998E-4</v>
+        <v>3.6433006767189901E-4</v>
       </c>
       <c r="C48">
         <v>47</v>
       </c>
       <c r="D48" s="1">
-        <v>3.2778187583548001E-4</v>
+        <v>3.2124140628867002E-4</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -11032,13 +11242,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="1">
-        <v>3.4229131937222798E-4</v>
+        <v>3.5493646996606599E-4</v>
       </c>
       <c r="C49">
         <v>48</v>
       </c>
       <c r="D49" s="1">
-        <v>3.27853566781995E-4</v>
+        <v>3.20864222975467E-4</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -11046,13 +11256,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="1">
-        <v>3.4546140721874899E-4</v>
+        <v>3.5596997491511297E-4</v>
       </c>
       <c r="C50">
         <v>49</v>
       </c>
       <c r="D50" s="1">
-        <v>3.3059523947906097E-4</v>
+        <v>3.2095168635226E-4</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -11060,13 +11270,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="1">
-        <v>3.4471096962063202E-4</v>
+        <v>3.54573946754829E-4</v>
       </c>
       <c r="C51">
         <v>50</v>
       </c>
       <c r="D51" s="1">
-        <v>3.1666884658662099E-4</v>
+        <v>3.1534714404608702E-4</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -11074,13 +11284,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="1">
-        <v>3.4531297199252799E-4</v>
+        <v>3.5592631511453397E-4</v>
       </c>
       <c r="C52">
         <v>51</v>
       </c>
       <c r="D52" s="1">
-        <v>3.1079372213412899E-4</v>
+        <v>3.1369835302852E-4</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -11088,13 +11298,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="1">
-        <v>3.4998657382968298E-4</v>
+        <v>3.5523829209910702E-4</v>
       </c>
       <c r="C53">
         <v>52</v>
       </c>
       <c r="D53" s="1">
-        <v>3.1294027433858797E-4</v>
+        <v>3.1354000024706898E-4</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -11102,13 +11312,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="1">
-        <v>3.5101251010564202E-4</v>
+        <v>3.5513749224393599E-4</v>
       </c>
       <c r="C54">
         <v>53</v>
       </c>
       <c r="D54" s="1">
-        <v>3.1133532772313101E-4</v>
+        <v>3.1744750990404601E-4</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -11116,13 +11326,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="1">
-        <v>3.4101093831140702E-4</v>
+        <v>3.57386877703124E-4</v>
       </c>
       <c r="C55">
         <v>54</v>
       </c>
       <c r="D55" s="1">
-        <v>3.1650291388515302E-4</v>
+        <v>3.1435461850710299E-4</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -11130,13 +11340,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="1">
-        <v>3.3151175073857102E-4</v>
+        <v>3.53616915445156E-4</v>
       </c>
       <c r="C56">
         <v>55</v>
       </c>
       <c r="D56" s="1">
-        <v>3.1520524222449501E-4</v>
+        <v>3.1265339788549498E-4</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -11144,13 +11354,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="1">
-        <v>3.1925096472942599E-4</v>
+        <v>3.4919265363781999E-4</v>
       </c>
       <c r="C57">
         <v>56</v>
       </c>
       <c r="D57" s="1">
-        <v>3.1704801362872001E-4</v>
+        <v>3.0958483238244803E-4</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -11158,13 +11368,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="1">
-        <v>3.1761089153413299E-4</v>
+        <v>3.4885281607527498E-4</v>
       </c>
       <c r="C58">
         <v>57</v>
       </c>
       <c r="D58" s="1">
-        <v>3.1606769777886698E-4</v>
+        <v>3.0747490234269901E-4</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -11172,13 +11382,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="1">
-        <v>3.16854934871136E-4</v>
+        <v>3.4804544366309298E-4</v>
       </c>
       <c r="C59">
         <v>58</v>
       </c>
       <c r="D59" s="1">
-        <v>3.1582121565974601E-4</v>
+        <v>3.0646136229955299E-4</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -11186,13 +11396,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="1">
-        <v>3.1767748020337201E-4</v>
+        <v>3.4594624353098799E-4</v>
       </c>
       <c r="C60">
         <v>59</v>
       </c>
       <c r="D60" s="1">
-        <v>3.11569460307142E-4</v>
+        <v>3.0226373092919802E-4</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -11200,13 +11410,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="1">
-        <v>3.1232163065188998E-4</v>
+        <v>3.3816676949701498E-4</v>
       </c>
       <c r="C61">
         <v>60</v>
       </c>
       <c r="D61" s="1">
-        <v>3.0277785548266502E-4</v>
+        <v>2.99278133744498E-4</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -11214,13 +11424,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="1">
-        <v>3.1639879080852399E-4</v>
+        <v>3.3953262234193198E-4</v>
       </c>
       <c r="C62">
         <v>61</v>
       </c>
       <c r="D62" s="1">
-        <v>3.0864410596062798E-4</v>
+        <v>3.0135757356330501E-4</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -11228,13 +11438,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="1">
-        <v>3.1211756715020901E-4</v>
+        <v>3.4396927697661901E-4</v>
       </c>
       <c r="C63">
         <v>62</v>
       </c>
       <c r="D63" s="1">
-        <v>3.0721391337254299E-4</v>
+        <v>3.0409732263618299E-4</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -11242,13 +11452,13 @@
         <v>63</v>
       </c>
       <c r="B64" s="1">
-        <v>3.1034440173116401E-4</v>
+        <v>3.41333721461545E-4</v>
       </c>
       <c r="C64">
         <v>63</v>
       </c>
       <c r="D64" s="1">
-        <v>3.0793946533693898E-4</v>
+        <v>3.0327662113568098E-4</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -11256,13 +11466,13 @@
         <v>64</v>
       </c>
       <c r="B65" s="1">
-        <v>3.0606112048333701E-4</v>
+        <v>3.4006746208164698E-4</v>
       </c>
       <c r="C65">
         <v>64</v>
       </c>
       <c r="D65" s="1">
-        <v>3.0629558161670802E-4</v>
+        <v>3.0065802806271299E-4</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -11270,13 +11480,13 @@
         <v>65</v>
       </c>
       <c r="B66" s="1">
-        <v>3.0265676087775598E-4</v>
+        <v>3.3760083903140801E-4</v>
       </c>
       <c r="C66">
         <v>65</v>
       </c>
       <c r="D66" s="1">
-        <v>3.0854584300282002E-4</v>
+        <v>3.0070362727937703E-4</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -11284,13 +11494,13 @@
         <v>66</v>
       </c>
       <c r="B67" s="1">
-        <v>2.9961387722659898E-4</v>
+        <v>3.3683225686062301E-4</v>
       </c>
       <c r="C67">
         <v>66</v>
       </c>
       <c r="D67" s="1">
-        <v>3.0825622966724201E-4</v>
+        <v>3.0128313522629198E-4</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -11298,13 +11508,13 @@
         <v>67</v>
       </c>
       <c r="B68" s="1">
-        <v>2.9217166176705899E-4</v>
+        <v>3.33555875900424E-4</v>
       </c>
       <c r="C68">
         <v>67</v>
       </c>
       <c r="D68" s="1">
-        <v>3.1048046448416198E-4</v>
+        <v>3.0089573524966798E-4</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -11312,13 +11522,13 @@
         <v>68</v>
       </c>
       <c r="B69" s="1">
-        <v>2.8864145059779098E-4</v>
+        <v>3.3163383101576598E-4</v>
       </c>
       <c r="C69">
         <v>68</v>
       </c>
       <c r="D69" s="1">
-        <v>3.1209820508750402E-4</v>
+        <v>3.0286855011583502E-4</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -11326,13 +11536,13 @@
         <v>69</v>
       </c>
       <c r="B70" s="1">
-        <v>2.8955412195869398E-4</v>
+        <v>3.3218948292219999E-4</v>
       </c>
       <c r="C70">
         <v>69</v>
       </c>
       <c r="D70" s="1">
-        <v>3.1497390436151701E-4</v>
+        <v>3.0317335678730403E-4</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -11340,13 +11550,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="1">
-        <v>2.8955412195869398E-4</v>
+        <v>3.3218948292219999E-4</v>
       </c>
       <c r="C71">
         <v>70</v>
       </c>
       <c r="D71" s="1">
-        <v>3.1497390436151701E-4</v>
+        <v>3.0317335678730403E-4</v>
       </c>
     </row>
   </sheetData>
@@ -11379,13 +11589,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.69425629338408201</v>
+        <v>0.68884288448075603</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0.74241248782830904</v>
+        <v>0.74643435415784498</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -11393,13 +11603,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.70141418729654004</v>
+        <v>0.70314472428445796</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>0.75927961865081495</v>
+        <v>0.75931399314186998</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -11407,13 +11617,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.72091290943217901</v>
+        <v>0.71986048987838902</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4">
-        <v>0.77059329976165603</v>
+        <v>0.77501245376561301</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -11421,13 +11631,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.73686820114812002</v>
+        <v>0.73356026085486203</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>0.78319868114999902</v>
+        <v>0.78491030668751505</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -11435,13 +11645,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.74902749170497596</v>
+        <v>0.74487886485935095</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6">
-        <v>0.79420635355726599</v>
+        <v>0.79369378338761998</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -11449,13 +11659,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.76212710247193005</v>
+        <v>0.75615098121000901</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7">
-        <v>0.799583538914167</v>
+        <v>0.80046780221254299</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -11463,13 +11673,13 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.771461098885034</v>
+        <v>0.76574801368551804</v>
       </c>
       <c r="C8">
         <v>7</v>
       </c>
       <c r="D8">
-        <v>0.80443430680753103</v>
+        <v>0.80671418660317096</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -11477,13 +11687,13 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.77549909805487904</v>
+        <v>0.77178283252776803</v>
       </c>
       <c r="C9">
         <v>8</v>
       </c>
       <c r="D9">
-        <v>0.80824025416317502</v>
+        <v>0.81065807409239399</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -11491,13 +11701,13 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.78049096619076297</v>
+        <v>0.77817696783470003</v>
       </c>
       <c r="C10">
         <v>9</v>
       </c>
       <c r="D10">
-        <v>0.81290032135873902</v>
+        <v>0.81460987400212603</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -11505,13 +11715,13 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.78497928528354499</v>
+        <v>0.78325327465915395</v>
       </c>
       <c r="C11">
         <v>10</v>
       </c>
       <c r="D11">
-        <v>0.81581541843205096</v>
+        <v>0.81743322825359399</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -11519,13 +11729,13 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.79298986323327103</v>
+        <v>0.789628746784378</v>
       </c>
       <c r="C12">
         <v>11</v>
       </c>
       <c r="D12">
-        <v>0.81890001853490701</v>
+        <v>0.81965974495805904</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -11533,13 +11743,13 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.79669637472882904</v>
+        <v>0.79348987699242701</v>
       </c>
       <c r="C13">
         <v>12</v>
       </c>
       <c r="D13">
-        <v>0.82123656545563195</v>
+        <v>0.82182871758003595</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -11547,13 +11757,13 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.800457812202234</v>
+        <v>0.79695635557753997</v>
       </c>
       <c r="C14">
         <v>13</v>
       </c>
       <c r="D14">
-        <v>0.82255886138238998</v>
+        <v>0.82322835140788697</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -11561,13 +11771,13 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0.80279777894382298</v>
+        <v>0.80026903103066105</v>
       </c>
       <c r="C15">
         <v>14</v>
       </c>
       <c r="D15">
-        <v>0.82392449244376198</v>
+        <v>0.82444137961872299</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -11575,13 +11785,13 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0.80695427099078199</v>
+        <v>0.803299557952454</v>
       </c>
       <c r="C16">
         <v>15</v>
       </c>
       <c r="D16">
-        <v>0.82493062462636502</v>
+        <v>0.82533250506185296</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -11589,13 +11799,13 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.80983874630933395</v>
+        <v>0.80729497224190105</v>
       </c>
       <c r="C17">
         <v>16</v>
       </c>
       <c r="D17">
-        <v>0.82622785927045495</v>
+        <v>0.82594094923894001</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -11603,13 +11813,13 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.81060953738438501</v>
+        <v>0.80871178458094495</v>
       </c>
       <c r="C18">
         <v>17</v>
       </c>
       <c r="D18">
-        <v>0.82689135672908498</v>
+        <v>0.82669980800590204</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -11617,13 +11827,13 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.81187163402173501</v>
+        <v>0.81094378583295901</v>
       </c>
       <c r="C19">
         <v>18</v>
       </c>
       <c r="D19">
-        <v>0.82753258619384396</v>
+        <v>0.82725116223501205</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -11631,13 +11841,13 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.81263931854195504</v>
+        <v>0.81264051969756002</v>
       </c>
       <c r="C20">
         <v>19</v>
       </c>
       <c r="D20">
-        <v>0.82801044742221197</v>
+        <v>0.82772129625360003</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -11645,13 +11855,13 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.81322306368959496</v>
+        <v>0.81417664714586901</v>
       </c>
       <c r="C21">
         <v>20</v>
       </c>
       <c r="D21">
-        <v>0.82844455582792198</v>
+        <v>0.82829726981318996</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -11659,13 +11869,13 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>0.81496328261034101</v>
+        <v>0.81553098105630295</v>
       </c>
       <c r="C22">
         <v>21</v>
       </c>
       <c r="D22">
-        <v>0.82915530424658201</v>
+        <v>0.82874028676149003</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -11673,13 +11883,13 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.81668256491785896</v>
+        <v>0.81682080166618398</v>
       </c>
       <c r="C23">
         <v>22</v>
       </c>
       <c r="D23">
-        <v>0.82939576203267895</v>
+        <v>0.82912818750026196</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -11687,13 +11897,13 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>0.81880368922965296</v>
+        <v>0.81811677929202498</v>
       </c>
       <c r="C24">
         <v>23</v>
       </c>
       <c r="D24">
-        <v>0.82992385024839299</v>
+        <v>0.82951138096016597</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -11701,13 +11911,13 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0.82013710610059498</v>
+        <v>0.819071745567297</v>
       </c>
       <c r="C25">
         <v>24</v>
       </c>
       <c r="D25">
-        <v>0.83014193561860805</v>
+        <v>0.82998467645361496</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -11715,13 +11925,13 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>0.82079791469243801</v>
+        <v>0.82057292212501398</v>
       </c>
       <c r="C26">
         <v>25</v>
       </c>
       <c r="D26">
-        <v>0.83054114096710396</v>
+        <v>0.83030682375528697</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -11729,13 +11939,13 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>0.82150033545571099</v>
+        <v>0.82133555370175504</v>
       </c>
       <c r="C27">
         <v>26</v>
       </c>
       <c r="D27">
-        <v>0.83087675331083</v>
+        <v>0.83061500642076302</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -11743,13 +11953,13 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>0.82268578633690204</v>
+        <v>0.82206040478056897</v>
       </c>
       <c r="C28">
         <v>27</v>
       </c>
       <c r="D28">
-        <v>0.83138244300516095</v>
+        <v>0.83086354026496301</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -11757,13 +11967,13 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>0.82336228433591496</v>
+        <v>0.82307323827250001</v>
       </c>
       <c r="C29">
         <v>28</v>
       </c>
       <c r="D29">
-        <v>0.83161204090210195</v>
+        <v>0.83104494080182001</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -11771,13 +11981,13 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>0.82373501870459198</v>
+        <v>0.82339367383640205</v>
       </c>
       <c r="C30">
         <v>29</v>
       </c>
       <c r="D30">
-        <v>0.83192188711458503</v>
+        <v>0.83136824963983602</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -11785,13 +11995,13 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.82417366946778703</v>
+        <v>0.82387204340966902</v>
       </c>
       <c r="C31">
         <v>30</v>
       </c>
       <c r="D31">
-        <v>0.83214464536979704</v>
+        <v>0.83157100323204003</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -11799,13 +12009,13 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>0.82475130592777601</v>
+        <v>0.82464370527648401</v>
       </c>
       <c r="C32">
         <v>31</v>
       </c>
       <c r="D32">
-        <v>0.83241676913076501</v>
+        <v>0.83179488281233604</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -11813,13 +12023,13 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.82486439496581399</v>
+        <v>0.82487748848245002</v>
       </c>
       <c r="C33">
         <v>32</v>
       </c>
       <c r="D33">
-        <v>0.83268777035511299</v>
+        <v>0.83195484296028599</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -11827,13 +12037,13 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>0.82537021518765896</v>
+        <v>0.82528001759247205</v>
       </c>
       <c r="C34">
         <v>33</v>
       </c>
       <c r="D34">
-        <v>0.83282811353805197</v>
+        <v>0.83210599115206196</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -11841,13 +12051,13 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>0.82636705381127196</v>
+        <v>0.82580955589836902</v>
       </c>
       <c r="C35">
         <v>34</v>
       </c>
       <c r="D35">
-        <v>0.83289405603807198</v>
+        <v>0.83229159243313999</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -11855,13 +12065,13 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>0.82677106257227995</v>
+        <v>0.82609773044531698</v>
       </c>
       <c r="C36">
         <v>35</v>
       </c>
       <c r="D36">
-        <v>0.83316552716146997</v>
+        <v>0.83238044559678204</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -11869,13 +12079,13 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>0.82727406339982401</v>
+        <v>0.826434837985766</v>
       </c>
       <c r="C37">
         <v>36</v>
       </c>
       <c r="D37">
-        <v>0.83317249733071197</v>
+        <v>0.83254586409221298</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -11883,13 +12093,13 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>0.82743403792085302</v>
+        <v>0.82666695312074201</v>
       </c>
       <c r="C38">
         <v>37</v>
       </c>
       <c r="D38">
-        <v>0.83335714155186702</v>
+        <v>0.83271850507303102</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -11897,13 +12107,13 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>0.82784044838811599</v>
+        <v>0.82731439173223598</v>
       </c>
       <c r="C39">
         <v>38</v>
       </c>
       <c r="D39">
-        <v>0.83346083260890502</v>
+        <v>0.83280352429340199</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -11911,13 +12121,13 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>0.82808602285275701</v>
+        <v>0.82782725806158597</v>
       </c>
       <c r="C40">
         <v>39</v>
       </c>
       <c r="D40">
-        <v>0.83367941398367296</v>
+        <v>0.83294113578342399</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -11925,13 +12135,13 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>0.82838527023111197</v>
+        <v>0.82825522743754898</v>
       </c>
       <c r="C41">
         <v>40</v>
       </c>
       <c r="D41">
-        <v>0.83386157818206497</v>
+        <v>0.833089436901154</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -11939,13 +12149,13 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>0.82855049195819996</v>
+        <v>0.82855214407382405</v>
       </c>
       <c r="C42">
         <v>41</v>
       </c>
       <c r="D42">
-        <v>0.83401317283670195</v>
+        <v>0.83321780850055904</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -11953,13 +12163,13 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>0.82881551502241102</v>
+        <v>0.82875297632771405</v>
       </c>
       <c r="C43">
         <v>42</v>
       </c>
       <c r="D43">
-        <v>0.834177533082198</v>
+        <v>0.83327315177734196</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -11967,13 +12177,13 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>0.829726127170346</v>
+        <v>0.82916370605899203</v>
       </c>
       <c r="C44">
         <v>43</v>
       </c>
       <c r="D44">
-        <v>0.83429088317526401</v>
+        <v>0.83338489506698099</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -11981,13 +12191,13 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>0.82994859826502798</v>
+        <v>0.82944491138787702</v>
       </c>
       <c r="C45">
         <v>44</v>
       </c>
       <c r="D45">
-        <v>0.83427634241021598</v>
+        <v>0.83347724157300995</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -11995,13 +12205,13 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>0.83014833146679001</v>
+        <v>0.82972256224088103</v>
       </c>
       <c r="C46">
         <v>45</v>
       </c>
       <c r="D46">
-        <v>0.83438186085244903</v>
+        <v>0.83356081978964403</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -12009,13 +12219,13 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>0.83086171654122898</v>
+        <v>0.83030089380658301</v>
       </c>
       <c r="C47">
         <v>46</v>
       </c>
       <c r="D47">
-        <v>0.83448260198767299</v>
+        <v>0.83365713997264002</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -12023,13 +12233,13 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>0.83102957492409801</v>
+        <v>0.83046756990527404</v>
       </c>
       <c r="C48">
         <v>47</v>
       </c>
       <c r="D48">
-        <v>0.834503512495399</v>
+        <v>0.83373079709689202</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -12037,13 +12247,13 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>0.83108084613155597</v>
+        <v>0.83060876207124401</v>
       </c>
       <c r="C49">
         <v>48</v>
       </c>
       <c r="D49">
-        <v>0.83455050240040096</v>
+        <v>0.83379931027447896</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -12051,13 +12261,13 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>0.83128188460845698</v>
+        <v>0.83083917420180597</v>
       </c>
       <c r="C50">
         <v>49</v>
       </c>
       <c r="D50">
-        <v>0.834554731491851</v>
+        <v>0.83387454813616202</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -12065,13 +12275,13 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>0.83147342068234498</v>
+        <v>0.83109091318764605</v>
       </c>
       <c r="C51">
         <v>50</v>
       </c>
       <c r="D51">
-        <v>0.83461406929966697</v>
+        <v>0.83399286764284597</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -12079,13 +12289,13 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>0.83160112880194004</v>
+        <v>0.83117102426196199</v>
       </c>
       <c r="C52">
         <v>51</v>
       </c>
       <c r="D52">
-        <v>0.83473452008948901</v>
+        <v>0.83408932755953602</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -12093,13 +12303,13 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>0.832208760484622</v>
+        <v>0.83154242769130604</v>
       </c>
       <c r="C53">
         <v>52</v>
       </c>
       <c r="D53">
-        <v>0.83481667410673499</v>
+        <v>0.83415639100003203</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -12107,13 +12317,13 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>0.83231297365171597</v>
+        <v>0.83161246047283099</v>
       </c>
       <c r="C54">
         <v>53</v>
       </c>
       <c r="D54">
-        <v>0.83487394957983196</v>
+        <v>0.83416208514812396</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -12121,13 +12331,13 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>0.83244757362404398</v>
+        <v>0.83168864153695798</v>
       </c>
       <c r="C55">
         <v>54</v>
       </c>
       <c r="D55">
-        <v>0.83492958040625298</v>
+        <v>0.83422113136783804</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -12135,13 +12345,13 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>0.83258943092614501</v>
+        <v>0.831793153607854</v>
       </c>
       <c r="C56">
         <v>55</v>
       </c>
       <c r="D56">
-        <v>0.83499212919091204</v>
+        <v>0.83425073744457801</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -12149,13 +12359,13 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>0.83280955252557698</v>
+        <v>0.83189143879594196</v>
       </c>
       <c r="C57">
         <v>56</v>
       </c>
       <c r="D57">
-        <v>0.83508480372577698</v>
+        <v>0.83431475294383906</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -12163,13 +12373,13 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>0.83298712215547899</v>
+        <v>0.83228256214306695</v>
       </c>
       <c r="C58">
         <v>57</v>
       </c>
       <c r="D58">
-        <v>0.83518118524203699</v>
+        <v>0.83441267133097696</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -12177,13 +12387,13 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>0.83323126081746701</v>
+        <v>0.83239659357197004</v>
       </c>
       <c r="C59">
         <v>58</v>
       </c>
       <c r="D59">
-        <v>0.83520063384160703</v>
+        <v>0.83444036480275896</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -12191,13 +12401,13 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>0.83328759649246398</v>
+        <v>0.83247404097271405</v>
       </c>
       <c r="C60">
         <v>59</v>
       </c>
       <c r="D60">
-        <v>0.83523407499066704</v>
+        <v>0.834482520712027</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -12205,13 +12415,13 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>0.83349871169343703</v>
+        <v>0.83261602787407696</v>
       </c>
       <c r="C61">
         <v>60</v>
       </c>
       <c r="D61">
-        <v>0.835346067597589</v>
+        <v>0.83451293899087098</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -12219,13 +12429,13 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>0.833800491305562</v>
+        <v>0.832739168193257</v>
       </c>
       <c r="C62">
         <v>61</v>
       </c>
       <c r="D62">
-        <v>0.83533499886440998</v>
+        <v>0.83456176718410002</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -12233,13 +12443,13 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>0.83389071192316599</v>
+        <v>0.83275938591232801</v>
       </c>
       <c r="C63">
         <v>62</v>
       </c>
       <c r="D63">
-        <v>0.83529229026186402</v>
+        <v>0.83457872736139405</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -12247,13 +12457,13 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>0.834081125460435</v>
+        <v>0.832899748409481</v>
       </c>
       <c r="C64">
         <v>63</v>
       </c>
       <c r="D64">
-        <v>0.83528158700572497</v>
+        <v>0.83461091851150104</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -12261,13 +12471,13 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>0.83418651337515404</v>
+        <v>0.83297343173380201</v>
       </c>
       <c r="C65">
         <v>64</v>
       </c>
       <c r="D65">
-        <v>0.83522650439486101</v>
+        <v>0.83465841050126599</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -12275,13 +12485,13 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>0.83431907711826503</v>
+        <v>0.83307887827378602</v>
       </c>
       <c r="C66">
         <v>65</v>
       </c>
       <c r="D66">
-        <v>0.83527665306569998</v>
+        <v>0.83467005206477496</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -12289,13 +12499,13 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>0.83444887367808196</v>
+        <v>0.83316967024245103</v>
       </c>
       <c r="C67">
         <v>66</v>
       </c>
       <c r="D67">
-        <v>0.83533988059343001</v>
+        <v>0.83466167677639902</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -12303,13 +12513,13 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>0.83468066443725597</v>
+        <v>0.83329008575456898</v>
       </c>
       <c r="C68">
         <v>67</v>
       </c>
       <c r="D68">
-        <v>0.83534995731750294</v>
+        <v>0.83467927448867896</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -12317,13 +12527,13 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>0.83471833467776702</v>
+        <v>0.83333733321036696</v>
       </c>
       <c r="C69">
         <v>68</v>
       </c>
       <c r="D69">
-        <v>0.83539282255306602</v>
+        <v>0.83468283769791496</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -12331,13 +12541,13 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>0.83481696126726501</v>
+        <v>0.83340637912266802</v>
       </c>
       <c r="C70">
         <v>69</v>
       </c>
       <c r="D70">
-        <v>0.83534799940479398</v>
+        <v>0.83473400643054396</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -12345,13 +12555,13 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>0.83481696126726501</v>
+        <v>0.83340637912266802</v>
       </c>
       <c r="C71">
         <v>70</v>
       </c>
       <c r="D71">
-        <v>0.83534799940479398</v>
+        <v>0.83473400643054396</v>
       </c>
     </row>
   </sheetData>
@@ -12384,13 +12594,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.20689670811171099</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
+        <v>0.26070199936674299</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>0.119373200482033</v>
+        <v>0.12488100860519601</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -12398,13 +12608,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.21150055103502</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
+        <v>0.24569335427127501</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>9.9465607145709303E-2</v>
+        <v>0.114352284307533</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -12412,13 +12622,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.184356912631786</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
+        <v>0.21862555087809299</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
       </c>
       <c r="D4">
-        <v>9.2098726189586005E-2</v>
+        <v>9.39288119990946E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -12426,13 +12636,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.184238732988981</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
+        <v>0.20741124922750201</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>7.9296180558503501E-2</v>
+        <v>8.4781818453746202E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -12440,13 +12650,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.171947391045396</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
+        <v>0.199080648969579</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>6.3678988309036802E-2</v>
+        <v>7.2137447445350306E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -12454,13 +12664,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.15008252837397501</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
+        <v>0.17663795023315901</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>5.5052706064113499E-2</v>
+        <v>6.2838439544546695E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -12468,13 +12678,13 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.13934777445180699</v>
-      </c>
-      <c r="C8">
-        <v>7</v>
+        <v>0.176118040566489</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
       </c>
       <c r="D8">
-        <v>4.8166642965889399E-2</v>
+        <v>5.5685630485540698E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -12482,13 +12692,13 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.135293462500226</v>
-      </c>
-      <c r="C9">
-        <v>8</v>
+        <v>0.17294063125426301</v>
+      </c>
+      <c r="C9" t="s">
+        <v>9</v>
       </c>
       <c r="D9">
-        <v>4.4853545276119802E-2</v>
+        <v>5.1725776191935802E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -12496,13 +12706,13 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.13225062366019999</v>
-      </c>
-      <c r="C10">
-        <v>9</v>
+        <v>0.17127953041896701</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
       </c>
       <c r="D10">
-        <v>4.0424528282248601E-2</v>
+        <v>4.6420094853518098E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -12510,13 +12720,13 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.14287431528126401</v>
-      </c>
-      <c r="C11">
-        <v>10</v>
+        <v>0.16703731551889101</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
       </c>
       <c r="D11">
-        <v>3.7298704605417198E-2</v>
+        <v>4.2840286682438902E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -12524,13 +12734,13 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.113534608659102</v>
-      </c>
-      <c r="C12">
-        <v>11</v>
+        <v>0.14737615503968399</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
       </c>
       <c r="D12">
-        <v>3.4776877990154997E-2</v>
+        <v>4.1567348868420499E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -12538,13 +12748,13 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.112653039370742</v>
-      </c>
-      <c r="C13">
-        <v>12</v>
+        <v>0.139370501662094</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
       </c>
       <c r="D13">
-        <v>2.9723095521513698E-2</v>
+        <v>3.95898280000039E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -12552,13 +12762,13 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.107266967844664</v>
-      </c>
-      <c r="C14">
-        <v>13</v>
+        <v>0.134198949147457</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
       </c>
       <c r="D14">
-        <v>2.8884922180892399E-2</v>
+        <v>3.8296349145494103E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -12566,13 +12776,13 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0.105081440969646</v>
-      </c>
-      <c r="C15">
-        <v>14</v>
+        <v>0.12848419495073399</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
       </c>
       <c r="D15">
-        <v>2.8518443845116499E-2</v>
+        <v>3.5921620049663101E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -12580,13 +12790,13 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>9.5692205881676207E-2</v>
-      </c>
-      <c r="C16">
-        <v>15</v>
+        <v>0.124335792509762</v>
+      </c>
+      <c r="C16" t="s">
+        <v>16</v>
       </c>
       <c r="D16">
-        <v>2.7257517732615099E-2</v>
+        <v>3.5019330534999803E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -12594,13 +12804,13 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>8.94335803147112E-2</v>
-      </c>
-      <c r="C17">
-        <v>16</v>
+        <v>0.112277800907381</v>
+      </c>
+      <c r="C17" t="s">
+        <v>17</v>
       </c>
       <c r="D17">
-        <v>2.5166806272539501E-2</v>
+        <v>3.4483123674123102E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -12608,13 +12818,13 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>8.9210131841901005E-2</v>
-      </c>
-      <c r="C18">
-        <v>17</v>
+        <v>0.111203285059739</v>
+      </c>
+      <c r="C18" t="s">
+        <v>18</v>
       </c>
       <c r="D18">
-        <v>2.3018710234849499E-2</v>
+        <v>3.3479557379548101E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -12622,13 +12832,13 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>8.7510674506344296E-2</v>
-      </c>
-      <c r="C19">
-        <v>18</v>
+        <v>0.10299640475463701</v>
+      </c>
+      <c r="C19" t="s">
+        <v>19</v>
       </c>
       <c r="D19">
-        <v>2.2765438837354799E-2</v>
+        <v>3.3276569864292102E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -12636,13 +12846,13 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>8.5705867646785797E-2</v>
-      </c>
-      <c r="C20">
-        <v>19</v>
+        <v>0.100019155921117</v>
+      </c>
+      <c r="C20" t="s">
+        <v>20</v>
       </c>
       <c r="D20">
-        <v>2.2840550038611299E-2</v>
+        <v>3.1870215221005999E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -12650,13 +12860,13 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>8.5140029293306801E-2</v>
-      </c>
-      <c r="C21">
-        <v>20</v>
+        <v>9.7091598652251795E-2</v>
+      </c>
+      <c r="C21" t="s">
+        <v>21</v>
       </c>
       <c r="D21">
-        <v>2.1341426244348E-2</v>
+        <v>3.0563786365766701E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -12664,13 +12874,13 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>8.0236298839995904E-2</v>
-      </c>
-      <c r="C22">
-        <v>21</v>
+        <v>9.3586669734792793E-2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>22</v>
       </c>
       <c r="D22">
-        <v>1.89123461686195E-2</v>
+        <v>2.9963802381725399E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -12678,13 +12888,13 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>7.2378565466757805E-2</v>
-      </c>
-      <c r="C23">
-        <v>22</v>
+        <v>8.9667037502854E-2</v>
+      </c>
+      <c r="C23" t="s">
+        <v>23</v>
       </c>
       <c r="D23">
-        <v>1.8948521865011999E-2</v>
+        <v>2.8359916294929399E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -12692,13 +12902,13 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>7.0068228089801607E-2</v>
-      </c>
-      <c r="C24">
-        <v>23</v>
+        <v>8.7411760850928305E-2</v>
+      </c>
+      <c r="C24" t="s">
+        <v>24</v>
       </c>
       <c r="D24">
-        <v>1.8136346038928702E-2</v>
+        <v>2.8174266071330299E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -12706,13 +12916,13 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>6.3238193289494801E-2</v>
-      </c>
-      <c r="C25">
-        <v>24</v>
+        <v>8.3103209200931602E-2</v>
+      </c>
+      <c r="C25" t="s">
+        <v>25</v>
       </c>
       <c r="D25">
-        <v>1.8242102354701899E-2</v>
+        <v>2.5930126523408099E-2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -12720,13 +12930,13 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>6.2863364551558096E-2</v>
-      </c>
-      <c r="C26">
-        <v>25</v>
+        <v>7.5380475411144496E-2</v>
+      </c>
+      <c r="C26" t="s">
+        <v>26</v>
       </c>
       <c r="D26">
-        <v>1.8308204378322899E-2</v>
+        <v>2.5148921525704301E-2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -12734,13 +12944,13 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>6.02806564643645E-2</v>
-      </c>
-      <c r="C27">
-        <v>26</v>
+        <v>7.2831769628116896E-2</v>
+      </c>
+      <c r="C27" t="s">
+        <v>27</v>
       </c>
       <c r="D27">
-        <v>1.81374360462991E-2</v>
+        <v>2.43580490858449E-2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -12748,13 +12958,13 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>5.7045943611740701E-2</v>
-      </c>
-      <c r="C28">
-        <v>27</v>
+        <v>6.9804344280290004E-2</v>
+      </c>
+      <c r="C28" t="s">
+        <v>28</v>
       </c>
       <c r="D28">
-        <v>1.69724196494585E-2</v>
+        <v>2.39200192322373E-2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -12762,13 +12972,13 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>5.5229037692836297E-2</v>
-      </c>
-      <c r="C29">
-        <v>28</v>
+        <v>6.5863900094645794E-2</v>
+      </c>
+      <c r="C29" t="s">
+        <v>29</v>
       </c>
       <c r="D29">
-        <v>1.6529589011411602E-2</v>
+        <v>2.38549444972334E-2</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -12776,13 +12986,13 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>5.3524914720911899E-2</v>
-      </c>
-      <c r="C30">
-        <v>29</v>
+        <v>6.4905166309931595E-2</v>
+      </c>
+      <c r="C30" t="s">
+        <v>30</v>
       </c>
       <c r="D30">
-        <v>1.6529660604745599E-2</v>
+        <v>2.19312872326431E-2</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -12790,13 +13000,13 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>5.3021046470156701E-2</v>
-      </c>
-      <c r="C31">
-        <v>30</v>
+        <v>6.3663639343299494E-2</v>
+      </c>
+      <c r="C31" t="s">
+        <v>31</v>
       </c>
       <c r="D31">
-        <v>1.6904971045586199E-2</v>
+        <v>2.1594455293049802E-2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -12804,13 +13014,13 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>5.2557143621047901E-2</v>
-      </c>
-      <c r="C32">
-        <v>31</v>
+        <v>6.1062337134811101E-2</v>
+      </c>
+      <c r="C32" t="s">
+        <v>32</v>
       </c>
       <c r="D32">
-        <v>1.5486833928566601E-2</v>
+        <v>2.10413824630626E-2</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -12818,13 +13028,13 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>5.2467228642085202E-2</v>
-      </c>
-      <c r="C33">
-        <v>32</v>
+        <v>6.0974153083806201E-2</v>
+      </c>
+      <c r="C33" t="s">
+        <v>33</v>
       </c>
       <c r="D33">
-        <v>1.52972810114376E-2</v>
+        <v>2.0514102597500399E-2</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -12832,13 +13042,13 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>5.0435500444749197E-2</v>
-      </c>
-      <c r="C34">
-        <v>33</v>
+        <v>5.9697188375601701E-2</v>
+      </c>
+      <c r="C34" t="s">
+        <v>34</v>
       </c>
       <c r="D34">
-        <v>1.5095387273163599E-2</v>
+        <v>2.02481156285493E-2</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -12846,13 +13056,13 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>4.6996193581275103E-2</v>
-      </c>
-      <c r="C35">
-        <v>34</v>
+        <v>5.8235627647746702E-2</v>
+      </c>
+      <c r="C35" t="s">
+        <v>35</v>
       </c>
       <c r="D35">
-        <v>1.5031602059784399E-2</v>
+        <v>1.9312676687198899E-2</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -12860,13 +13070,13 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>4.6576635875247699E-2</v>
-      </c>
-      <c r="C36">
-        <v>35</v>
+        <v>5.7523394060693199E-2</v>
+      </c>
+      <c r="C36" t="s">
+        <v>36</v>
       </c>
       <c r="D36">
-        <v>1.48089462634176E-2</v>
+        <v>1.90694781455286E-2</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -12874,13 +13084,13 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>4.05625402342027E-2</v>
-      </c>
-      <c r="C37">
-        <v>36</v>
+        <v>5.3070164930587797E-2</v>
+      </c>
+      <c r="C37" t="s">
+        <v>37</v>
       </c>
       <c r="D37">
-        <v>1.4112874129750401E-2</v>
+        <v>1.8689364112695499E-2</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -12888,13 +13098,13 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>4.0475999363821999E-2</v>
-      </c>
-      <c r="C38">
-        <v>37</v>
+        <v>5.2148403946328997E-2</v>
+      </c>
+      <c r="C38" t="s">
+        <v>38</v>
       </c>
       <c r="D38">
-        <v>1.3976971131468599E-2</v>
+        <v>1.7678810341686502E-2</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -12902,13 +13112,13 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>3.7546501047758703E-2</v>
-      </c>
-      <c r="C39">
-        <v>38</v>
+        <v>4.7935878989361698E-2</v>
+      </c>
+      <c r="C39" t="s">
+        <v>39</v>
       </c>
       <c r="D39">
-        <v>1.3821676415756001E-2</v>
+        <v>1.7586942160676199E-2</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -12916,13 +13126,13 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>3.6654382590880899E-2</v>
-      </c>
-      <c r="C40">
-        <v>39</v>
+        <v>4.5717478012335201E-2</v>
+      </c>
+      <c r="C40" t="s">
+        <v>40</v>
       </c>
       <c r="D40">
-        <v>1.3291493908073901E-2</v>
+        <v>1.72203223041947E-2</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -12930,13 +13140,13 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>3.5859342632056E-2</v>
-      </c>
-      <c r="C41">
-        <v>40</v>
+        <v>4.2880229859735101E-2</v>
+      </c>
+      <c r="C41" t="s">
+        <v>41</v>
       </c>
       <c r="D41">
-        <v>1.2006102307381E-2</v>
+        <v>1.6482968705710699E-2</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -12944,13 +13154,13 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>3.5841697297351302E-2</v>
-      </c>
-      <c r="C42">
-        <v>41</v>
+        <v>4.23775604470732E-2</v>
+      </c>
+      <c r="C42" t="s">
+        <v>42</v>
       </c>
       <c r="D42">
-        <v>1.19108353772023E-2</v>
+        <v>1.5700469331038899E-2</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -12958,13 +13168,13 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>3.7290335481191102E-2</v>
-      </c>
-      <c r="C43">
-        <v>42</v>
+        <v>4.2565971503969298E-2</v>
+      </c>
+      <c r="C43" t="s">
+        <v>43</v>
       </c>
       <c r="D43">
-        <v>1.1717671395947499E-2</v>
+        <v>1.53200867184663E-2</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -12972,13 +13182,13 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>3.3820711211019601E-2</v>
-      </c>
-      <c r="C44">
-        <v>43</v>
+        <v>4.0802560182957803E-2</v>
+      </c>
+      <c r="C44" t="s">
+        <v>44</v>
       </c>
       <c r="D44">
-        <v>1.16755750676809E-2</v>
+        <v>1.4356114620424699E-2</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -12986,13 +13196,13 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>3.3248005341182801E-2</v>
-      </c>
-      <c r="C45">
-        <v>44</v>
+        <v>3.8901584759120603E-2</v>
+      </c>
+      <c r="C45" t="s">
+        <v>45</v>
       </c>
       <c r="D45">
-        <v>1.1760922035034699E-2</v>
+        <v>1.4019312615009299E-2</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -13000,13 +13210,13 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>3.22048557546614E-2</v>
-      </c>
-      <c r="C46">
-        <v>45</v>
+        <v>3.7614529315325197E-2</v>
+      </c>
+      <c r="C46" t="s">
+        <v>46</v>
       </c>
       <c r="D46">
-        <v>1.1527255363824099E-2</v>
+        <v>1.38872225507841E-2</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -13014,13 +13224,13 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>3.1233314658641102E-2</v>
-      </c>
-      <c r="C47">
-        <v>46</v>
+        <v>3.5281791151543902E-2</v>
+      </c>
+      <c r="C47" t="s">
+        <v>47</v>
       </c>
       <c r="D47">
-        <v>1.1456327252177699E-2</v>
+        <v>1.37061346806392E-2</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -13028,13 +13238,13 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>3.10310454193077E-2</v>
-      </c>
-      <c r="C48">
-        <v>47</v>
+        <v>3.4466552881035901E-2</v>
+      </c>
+      <c r="C48" t="s">
+        <v>48</v>
       </c>
       <c r="D48">
-        <v>1.1111932175548201E-2</v>
+        <v>1.3428926441428899E-2</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -13042,13 +13252,13 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>3.0286599823272201E-2</v>
-      </c>
-      <c r="C49">
-        <v>48</v>
+        <v>3.3966376027798603E-2</v>
+      </c>
+      <c r="C49" t="s">
+        <v>49</v>
       </c>
       <c r="D49">
-        <v>1.0899726319140201E-2</v>
+        <v>1.3172627966171101E-2</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -13056,13 +13266,13 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>2.8607938875435699E-2</v>
-      </c>
-      <c r="C50">
-        <v>49</v>
+        <v>3.2108879977000203E-2</v>
+      </c>
+      <c r="C50" t="s">
+        <v>50</v>
       </c>
       <c r="D50">
-        <v>1.1146585841051399E-2</v>
+        <v>1.2673635248618901E-2</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -13070,13 +13280,13 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>2.8111089714841501E-2</v>
-      </c>
-      <c r="C51">
-        <v>50</v>
+        <v>3.1206307745831701E-2</v>
+      </c>
+      <c r="C51" t="s">
+        <v>51</v>
       </c>
       <c r="D51">
-        <v>1.09315415812936E-2</v>
+        <v>1.2600264350854699E-2</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -13084,13 +13294,13 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>2.77310851253387E-2</v>
-      </c>
-      <c r="C52">
-        <v>51</v>
+        <v>3.0832354784116899E-2</v>
+      </c>
+      <c r="C52" t="s">
+        <v>52</v>
       </c>
       <c r="D52">
-        <v>1.07899784362556E-2</v>
+        <v>1.25343739732538E-2</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -13098,13 +13308,13 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>2.1687810160028E-2</v>
-      </c>
-      <c r="C53">
-        <v>52</v>
+        <v>2.6932382254637899E-2</v>
+      </c>
+      <c r="C53" t="s">
+        <v>53</v>
       </c>
       <c r="D53">
-        <v>1.06861998500122E-2</v>
+        <v>1.24396342929151E-2</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -13112,13 +13322,13 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>2.1340779399450699E-2</v>
-      </c>
-      <c r="C54">
-        <v>53</v>
+        <v>2.6607946964281599E-2</v>
+      </c>
+      <c r="C54" t="s">
+        <v>54</v>
       </c>
       <c r="D54">
-        <v>1.0553808619354999E-2</v>
+        <v>1.22661371115567E-2</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -13126,13 +13336,13 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>2.1423073122327101E-2</v>
-      </c>
-      <c r="C55">
-        <v>54</v>
+        <v>2.6603271204905601E-2</v>
+      </c>
+      <c r="C55" t="s">
+        <v>55</v>
       </c>
       <c r="D55">
-        <v>1.0687394497913E-2</v>
+        <v>1.2211386046059E-2</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -13140,13 +13350,13 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>2.1471044193833801E-2</v>
-      </c>
-      <c r="C56">
-        <v>55</v>
+        <v>2.6353743317352601E-2</v>
+      </c>
+      <c r="C56" t="s">
+        <v>56</v>
       </c>
       <c r="D56">
-        <v>1.0354702478019799E-2</v>
+        <v>1.22470248796145E-2</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -13154,13 +13364,13 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>2.1180421965927301E-2</v>
-      </c>
-      <c r="C57">
-        <v>56</v>
+        <v>2.58008703583094E-2</v>
+      </c>
+      <c r="C57" t="s">
+        <v>57</v>
       </c>
       <c r="D57">
-        <v>1.03281977748609E-2</v>
+        <v>1.19322102775377E-2</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -13168,13 +13378,13 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>1.9908333879016599E-2</v>
-      </c>
-      <c r="C58">
-        <v>57</v>
+        <v>2.3430680760085899E-2</v>
+      </c>
+      <c r="C58" t="s">
+        <v>58</v>
       </c>
       <c r="D58">
-        <v>1.01957206141788E-2</v>
+        <v>1.1278553370128E-2</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -13182,13 +13392,13 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>1.9799130552775601E-2</v>
-      </c>
-      <c r="C59">
-        <v>58</v>
+        <v>2.3147045866607499E-2</v>
+      </c>
+      <c r="C59" t="s">
+        <v>59</v>
       </c>
       <c r="D59">
-        <v>1.01976375570285E-2</v>
+        <v>1.1234938197526899E-2</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -13196,13 +13406,13 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>1.9789685995265101E-2</v>
-      </c>
-      <c r="C60">
-        <v>59</v>
+        <v>2.2737615191229299E-2</v>
+      </c>
+      <c r="C60" t="s">
+        <v>60</v>
       </c>
       <c r="D60">
-        <v>1.0217414336975201E-2</v>
+        <v>1.1207669931559E-2</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -13210,13 +13420,13 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>1.91214658959321E-2</v>
-      </c>
-      <c r="C61">
-        <v>60</v>
+        <v>2.2375714118101901E-2</v>
+      </c>
+      <c r="C61" t="s">
+        <v>61</v>
       </c>
       <c r="D61">
-        <v>1.0067593494196199E-2</v>
+        <v>1.11214860857934E-2</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -13224,13 +13434,13 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>1.535015886913E-2</v>
-      </c>
-      <c r="C62">
-        <v>61</v>
+        <v>2.06754057482436E-2</v>
+      </c>
+      <c r="C62" t="s">
+        <v>62</v>
       </c>
       <c r="D62">
-        <v>9.9146375854633796E-3</v>
+        <v>1.08408385522512E-2</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -13238,13 +13448,13 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>1.5269924438015401E-2</v>
-      </c>
-      <c r="C63">
-        <v>62</v>
+        <v>2.0422532142128198E-2</v>
+      </c>
+      <c r="C63" t="s">
+        <v>63</v>
       </c>
       <c r="D63">
-        <v>9.9637900078251903E-3</v>
+        <v>1.0761187520518901E-2</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -13252,13 +13462,13 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>1.4761033838664899E-2</v>
-      </c>
-      <c r="C64">
-        <v>63</v>
+        <v>1.9951577105645699E-2</v>
+      </c>
+      <c r="C64" t="s">
+        <v>64</v>
       </c>
       <c r="D64">
-        <v>1.00110463918555E-2</v>
+        <v>1.06864347009179E-2</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -13266,13 +13476,13 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>1.4738941472839899E-2</v>
-      </c>
-      <c r="C65">
-        <v>64</v>
+        <v>1.9839470893254101E-2</v>
+      </c>
+      <c r="C65" t="s">
+        <v>65</v>
       </c>
       <c r="D65">
-        <v>1.0005148925731301E-2</v>
+        <v>1.0582557118743501E-2</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -13280,13 +13490,13 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>1.45491297266364E-2</v>
-      </c>
-      <c r="C66">
-        <v>65</v>
+        <v>1.9473258059402001E-2</v>
+      </c>
+      <c r="C66" t="s">
+        <v>66</v>
       </c>
       <c r="D66">
-        <v>9.9184793972403994E-3</v>
+        <v>1.06353399980451E-2</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -13294,13 +13504,13 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>1.4592903529605201E-2</v>
-      </c>
-      <c r="C67">
-        <v>66</v>
+        <v>1.90500853175011E-2</v>
+      </c>
+      <c r="C67" t="s">
+        <v>67</v>
       </c>
       <c r="D67">
-        <v>9.59099997414521E-3</v>
+        <v>1.0642553813495E-2</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -13308,13 +13518,13 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>1.35755395924946E-2</v>
-      </c>
-      <c r="C68">
-        <v>67</v>
+        <v>1.80244992193348E-2</v>
+      </c>
+      <c r="C68" t="s">
+        <v>68</v>
       </c>
       <c r="D68">
-        <v>9.6041204877854499E-3</v>
+        <v>1.03163331230575E-2</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -13322,13 +13532,13 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>1.36649998054532E-2</v>
-      </c>
-      <c r="C69">
-        <v>68</v>
+        <v>1.80719191284298E-2</v>
+      </c>
+      <c r="C69" t="s">
+        <v>69</v>
       </c>
       <c r="D69">
-        <v>9.4792808436466505E-3</v>
+        <v>1.0170418752764599E-2</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -13336,13 +13546,13 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>1.34901695137603E-2</v>
-      </c>
-      <c r="C70">
-        <v>69</v>
+        <v>1.7957824332433502E-2</v>
+      </c>
+      <c r="C70" t="s">
+        <v>70</v>
       </c>
       <c r="D70">
-        <v>9.5163058430269305E-3</v>
+        <v>1.0049070616387001E-2</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -13350,13 +13560,13 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>1.34901695137603E-2</v>
-      </c>
-      <c r="C71">
-        <v>70</v>
+        <v>1.7957824332433502E-2</v>
+      </c>
+      <c r="C71" t="s">
+        <v>71</v>
       </c>
       <c r="D71">
-        <v>9.5163058430269305E-3</v>
+        <v>1.0049070616387001E-2</v>
       </c>
     </row>
   </sheetData>
@@ -13389,13 +13599,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.76771750755111101</v>
+        <v>0.766327328951392</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0.66701421116973103</v>
+        <v>0.65785967184468397</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -13403,13 +13613,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.84029172078523195</v>
+        <v>0.81028008950052399</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>0.73899085096005901</v>
+        <v>0.76878519026251202</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -13417,13 +13627,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.83200283543641895</v>
+        <v>0.82334868823943097</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4">
-        <v>0.77538745348101101</v>
+        <v>0.79585710269721699</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -13431,13 +13641,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.81446152776780401</v>
+        <v>0.83177270166272699</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>0.78516183876153001</v>
+        <v>0.79560272586738701</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -13445,13 +13655,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.82262943424466295</v>
+        <v>0.83462490203242601</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6">
-        <v>0.80308959846161199</v>
+        <v>0.79034724970395498</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -13459,13 +13669,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.82779661007531502</v>
+        <v>0.85029133127237899</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7">
-        <v>0.82596452057717495</v>
+        <v>0.83887158288117103</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -13473,13 +13683,13 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.84650471551143402</v>
+        <v>0.85302560474017097</v>
       </c>
       <c r="C8">
         <v>7</v>
       </c>
       <c r="D8">
-        <v>0.83893596972796503</v>
+        <v>0.84812795711163103</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -13487,13 +13697,13 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.83167634795045098</v>
+        <v>0.85489516763487405</v>
       </c>
       <c r="C9">
         <v>8</v>
       </c>
       <c r="D9">
-        <v>0.85364362187459697</v>
+        <v>0.85768402597443205</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -13501,13 +13711,13 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.86220569509672995</v>
+        <v>0.87489784121783898</v>
       </c>
       <c r="C10">
         <v>9</v>
       </c>
       <c r="D10">
-        <v>0.84044337634338995</v>
+        <v>0.84805252868182102</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -13515,13 +13725,13 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.85342214911288306</v>
+        <v>0.87315759285928796</v>
       </c>
       <c r="C11">
         <v>10</v>
       </c>
       <c r="D11">
-        <v>0.81840478060594601</v>
+        <v>0.81129981934165796</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -13529,13 +13739,13 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.85238662777469199</v>
+        <v>0.87854885324290199</v>
       </c>
       <c r="C12">
         <v>11</v>
       </c>
       <c r="D12">
-        <v>0.78536684283249802</v>
+        <v>0.77821256913167003</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -13543,13 +13753,13 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.87946137473936603</v>
+        <v>0.89383434590856503</v>
       </c>
       <c r="C13">
         <v>12</v>
       </c>
       <c r="D13">
-        <v>0.76371007240125599</v>
+        <v>0.74389195325088298</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -13557,13 +13767,13 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.87153611095483996</v>
+        <v>0.87751344808780096</v>
       </c>
       <c r="C14">
         <v>13</v>
       </c>
       <c r="D14">
-        <v>0.74275277961987296</v>
+        <v>0.72641497036548097</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -13571,13 +13781,13 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0.82930273579021596</v>
+        <v>0.84461262772019896</v>
       </c>
       <c r="C15">
         <v>14</v>
       </c>
       <c r="D15">
-        <v>0.72823873838502495</v>
+        <v>0.70378202490046005</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -13585,13 +13795,13 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0.81676503511639997</v>
+        <v>0.82511048118899399</v>
       </c>
       <c r="C16">
         <v>15</v>
       </c>
       <c r="D16">
-        <v>0.70417912025706397</v>
+        <v>0.68977105070322897</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -13599,13 +13809,13 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.798290686931456</v>
+        <v>0.81221615539852599</v>
       </c>
       <c r="C17">
         <v>16</v>
       </c>
       <c r="D17">
-        <v>0.68789709766645302</v>
+        <v>0.67927305549972905</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -13613,13 +13823,13 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.780651124365491</v>
+        <v>0.80125635003364204</v>
       </c>
       <c r="C18">
         <v>17</v>
       </c>
       <c r="D18">
-        <v>0.69231984599127405</v>
+        <v>0.67031192566827902</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -13627,13 +13837,13 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.77604232124692596</v>
+        <v>0.79037244782224803</v>
       </c>
       <c r="C19">
         <v>18</v>
       </c>
       <c r="D19">
-        <v>0.68383636681303195</v>
+        <v>0.668494426648095</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -13641,13 +13851,13 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.75644501057044899</v>
+        <v>0.77868012774593098</v>
       </c>
       <c r="C20">
         <v>19</v>
       </c>
       <c r="D20">
-        <v>0.676594662878655</v>
+        <v>0.66440811429056401</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -13655,13 +13865,13 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.74920197795838195</v>
+        <v>0.76376931486520105</v>
       </c>
       <c r="C21">
         <v>20</v>
       </c>
       <c r="D21">
-        <v>0.66062550751193105</v>
+        <v>0.65519974043786</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -13669,13 +13879,13 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>0.72877685964977801</v>
+        <v>0.75265977772009596</v>
       </c>
       <c r="C22">
         <v>21</v>
       </c>
       <c r="D22">
-        <v>0.65661803374213101</v>
+        <v>0.65058988357973901</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -13683,13 +13893,13 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.71355221829691295</v>
+        <v>0.73639902090263898</v>
       </c>
       <c r="C23">
         <v>22</v>
       </c>
       <c r="D23">
-        <v>0.66589933984816896</v>
+        <v>0.65211485898766797</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -13697,13 +13907,13 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>0.71203387995664902</v>
+        <v>0.72735402655937997</v>
       </c>
       <c r="C24">
         <v>23</v>
       </c>
       <c r="D24">
-        <v>0.67363447739359905</v>
+        <v>0.643747873115321</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -13711,13 +13921,13 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0.70641271681094298</v>
+        <v>0.72298202648197096</v>
       </c>
       <c r="C25">
         <v>24</v>
       </c>
       <c r="D25">
-        <v>0.67903158689402898</v>
+        <v>0.63842573539364</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -13725,13 +13935,13 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>0.70603720778679502</v>
+        <v>0.72048916237364102</v>
       </c>
       <c r="C26">
         <v>25</v>
       </c>
       <c r="D26">
-        <v>0.66383082571386298</v>
+        <v>0.63587619201027401</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -13739,13 +13949,13 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>0.701714199626982</v>
+        <v>0.71743209919367501</v>
       </c>
       <c r="C27">
         <v>26</v>
       </c>
       <c r="D27">
-        <v>0.65501035002130004</v>
+        <v>0.62540598616874998</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -13753,13 +13963,13 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>0.70009356265797695</v>
+        <v>0.71099587521481999</v>
       </c>
       <c r="C28">
         <v>27</v>
       </c>
       <c r="D28">
-        <v>0.66103629440308997</v>
+        <v>0.62059281124683296</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -13767,13 +13977,13 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>0.69057527120504802</v>
+        <v>0.70323181416706104</v>
       </c>
       <c r="C29">
         <v>28</v>
       </c>
       <c r="D29">
-        <v>0.65196850773374004</v>
+        <v>0.61696652022170595</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -13781,13 +13991,13 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>0.68572314436945503</v>
+        <v>0.69503470929871403</v>
       </c>
       <c r="C30">
         <v>29</v>
       </c>
       <c r="D30">
-        <v>0.65204646995820303</v>
+        <v>0.61861723971659499</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -13795,13 +14005,13 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.68461025632928696</v>
+        <v>0.68906973129747895</v>
       </c>
       <c r="C31">
         <v>30</v>
       </c>
       <c r="D31">
-        <v>0.64431509987807301</v>
+        <v>0.61999149640982498</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -13809,13 +14019,13 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>0.68439613911465802</v>
+        <v>0.68477729271847698</v>
       </c>
       <c r="C32">
         <v>31</v>
       </c>
       <c r="D32">
-        <v>0.63609799676098699</v>
+        <v>0.61903531959722502</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -13823,13 +14033,13 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.68373615810402899</v>
+        <v>0.67884544887061504</v>
       </c>
       <c r="C33">
         <v>32</v>
       </c>
       <c r="D33">
-        <v>0.63355567206997598</v>
+        <v>0.60992137765255305</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -13837,13 +14047,13 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>0.67839887634306495</v>
+        <v>0.67226918092824095</v>
       </c>
       <c r="C34">
         <v>33</v>
       </c>
       <c r="D34">
-        <v>0.62869424318627798</v>
+        <v>0.60678090823830599</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -13851,13 +14061,13 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>0.67093876190771395</v>
+        <v>0.66651065380779495</v>
       </c>
       <c r="C35">
         <v>34</v>
       </c>
       <c r="D35">
-        <v>0.62622291462129598</v>
+        <v>0.60137228443586499</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -13865,13 +14075,13 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>0.66060469284326395</v>
+        <v>0.65983022103404199</v>
       </c>
       <c r="C36">
         <v>35</v>
       </c>
       <c r="D36">
-        <v>0.61040180973718206</v>
+        <v>0.60666678218751802</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -13879,13 +14089,13 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>0.65499780072176295</v>
+        <v>0.65960200845087402</v>
       </c>
       <c r="C37">
         <v>36</v>
       </c>
       <c r="D37">
-        <v>0.61409591904022398</v>
+        <v>0.60179813704780505</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -13893,13 +14103,13 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>0.65582900628761298</v>
+        <v>0.66029389869948496</v>
       </c>
       <c r="C38">
         <v>37</v>
       </c>
       <c r="D38">
-        <v>0.61179686845173598</v>
+        <v>0.59901943508168198</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -13907,13 +14117,13 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>0.65913284413578599</v>
+        <v>0.66043748103364397</v>
       </c>
       <c r="C39">
         <v>38</v>
       </c>
       <c r="D39">
-        <v>0.61511033251131098</v>
+        <v>0.59573295620852496</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -13921,13 +14131,13 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>0.65807038538162799</v>
+        <v>0.65410736450821005</v>
       </c>
       <c r="C40">
         <v>39</v>
       </c>
       <c r="D40">
-        <v>0.60664776257425701</v>
+        <v>0.59454290676101895</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -13935,13 +14145,13 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>0.65026188996391099</v>
+        <v>0.64995627790920696</v>
       </c>
       <c r="C41">
         <v>40</v>
       </c>
       <c r="D41">
-        <v>0.60802014054188402</v>
+        <v>0.59372909873417701</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -13949,13 +14159,13 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>0.64781523725415702</v>
+        <v>0.644044497560191</v>
       </c>
       <c r="C42">
         <v>41</v>
       </c>
       <c r="D42">
-        <v>0.60306642974028701</v>
+        <v>0.59246863393919302</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -13963,13 +14173,13 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>0.64682072027791604</v>
+        <v>0.640681368796576</v>
       </c>
       <c r="C43">
         <v>42</v>
       </c>
       <c r="D43">
-        <v>0.60006292540463702</v>
+        <v>0.59196079793068002</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -13977,13 +14187,13 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>0.64890026185244298</v>
+        <v>0.63750494020191495</v>
       </c>
       <c r="C44">
         <v>43</v>
       </c>
       <c r="D44">
-        <v>0.59770364964266098</v>
+        <v>0.59289269221373397</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -13991,13 +14201,13 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>0.64520800386561805</v>
+        <v>0.63198466526347996</v>
       </c>
       <c r="C45">
         <v>44</v>
       </c>
       <c r="D45">
-        <v>0.60382099947779799</v>
+        <v>0.58801689661593204</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -14005,13 +14215,13 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>0.64570769635700898</v>
+        <v>0.63054092663786498</v>
       </c>
       <c r="C46">
         <v>45</v>
       </c>
       <c r="D46">
-        <v>0.60525583688915396</v>
+        <v>0.58615804415236406</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -14019,13 +14229,13 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>0.64736271607277096</v>
+        <v>0.62997831697649098</v>
       </c>
       <c r="C47">
         <v>46</v>
       </c>
       <c r="D47">
-        <v>0.60219727701604397</v>
+        <v>0.58108015357718501</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -14033,13 +14243,13 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>0.64490592890669296</v>
+        <v>0.62615828724044498</v>
       </c>
       <c r="C48">
         <v>47</v>
       </c>
       <c r="D48">
-        <v>0.597454574095028</v>
+        <v>0.57217800795839302</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -14047,13 +14257,13 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>0.64259863031019704</v>
+        <v>0.62734237468041298</v>
       </c>
       <c r="C49">
         <v>48</v>
       </c>
       <c r="D49">
-        <v>0.591069846853432</v>
+        <v>0.57133534445259104</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -14061,13 +14271,13 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>0.64395496402260999</v>
+        <v>0.62414815142538005</v>
       </c>
       <c r="C50">
         <v>49</v>
       </c>
       <c r="D50">
-        <v>0.59238385066855104</v>
+        <v>0.56838327019546797</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -14075,13 +14285,13 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>0.63823855763806503</v>
+        <v>0.61887902899456004</v>
       </c>
       <c r="C51">
         <v>50</v>
       </c>
       <c r="D51">
-        <v>0.58524359838634699</v>
+        <v>0.56841543665190497</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -14089,13 +14299,13 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>0.63175320892431197</v>
+        <v>0.61278252378585596</v>
       </c>
       <c r="C52">
         <v>51</v>
       </c>
       <c r="D52">
-        <v>0.58159434954741196</v>
+        <v>0.56516241411409496</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -14103,13 +14313,13 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>0.63095600450072198</v>
+        <v>0.61126520231954695</v>
       </c>
       <c r="C53">
         <v>52</v>
       </c>
       <c r="D53">
-        <v>0.57845712991113496</v>
+        <v>0.56240424475067297</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -14117,13 +14327,13 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>0.62499638716074402</v>
+        <v>0.60928406811964597</v>
       </c>
       <c r="C54">
         <v>53</v>
       </c>
       <c r="D54">
-        <v>0.582732557220208</v>
+        <v>0.56229445491262497</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -14131,13 +14341,13 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>0.61949692429891601</v>
+        <v>0.60615338415291198</v>
       </c>
       <c r="C55">
         <v>54</v>
       </c>
       <c r="D55">
-        <v>0.58277815622320495</v>
+        <v>0.56210403064740699</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -14145,13 +14355,13 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>0.61528336269322004</v>
+        <v>0.60342455516900795</v>
       </c>
       <c r="C56">
         <v>55</v>
       </c>
       <c r="D56">
-        <v>0.57599098937774595</v>
+        <v>0.56320858531235296</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -14159,13 +14369,13 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>0.61743388561663204</v>
+        <v>0.60255006745098805</v>
       </c>
       <c r="C57">
         <v>56</v>
       </c>
       <c r="D57">
-        <v>0.57538057710219703</v>
+        <v>0.55919337935240898</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -14173,13 +14383,13 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>0.61134705954841795</v>
+        <v>0.59902987081057002</v>
       </c>
       <c r="C58">
         <v>57</v>
       </c>
       <c r="D58">
-        <v>0.56602151291208502</v>
+        <v>0.55201906386788901</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -14187,13 +14397,13 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>0.608456464240691</v>
+        <v>0.59621234806785195</v>
       </c>
       <c r="C59">
         <v>58</v>
       </c>
       <c r="D59">
-        <v>0.56472236270056897</v>
+        <v>0.55189030443926002</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -14201,13 +14411,13 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>0.60771758140620102</v>
+        <v>0.59379821765230101</v>
       </c>
       <c r="C60">
         <v>59</v>
       </c>
       <c r="D60">
-        <v>0.56648774670616397</v>
+        <v>0.55235808292267297</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -14215,13 +14425,13 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>0.59994233117439</v>
+        <v>0.590989217035776</v>
       </c>
       <c r="C61">
         <v>60</v>
       </c>
       <c r="D61">
-        <v>0.56734714163703204</v>
+        <v>0.55403685691287996</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -14229,13 +14439,13 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>0.60220976584931896</v>
+        <v>0.59087769919958799</v>
       </c>
       <c r="C62">
         <v>61</v>
       </c>
       <c r="D62">
-        <v>0.56398337275302801</v>
+        <v>0.55112708068848704</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -14243,13 +14453,13 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>0.60074733808977099</v>
+        <v>0.58865451722088302</v>
       </c>
       <c r="C63">
         <v>62</v>
       </c>
       <c r="D63">
-        <v>0.56256926684067199</v>
+        <v>0.549381423177977</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -14257,13 +14467,13 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>0.59111840449851705</v>
+        <v>0.58208297535624598</v>
       </c>
       <c r="C64">
         <v>63</v>
       </c>
       <c r="D64">
-        <v>0.56904980042366904</v>
+        <v>0.54790210541944995</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -14271,13 +14481,13 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>0.59064203856828601</v>
+        <v>0.58584005692535002</v>
       </c>
       <c r="C65">
         <v>64</v>
       </c>
       <c r="D65">
-        <v>0.57706727927472801</v>
+        <v>0.545220815309994</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -14285,13 +14495,13 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>0.587024337256005</v>
+        <v>0.58307570775395201</v>
       </c>
       <c r="C66">
         <v>65</v>
       </c>
       <c r="D66">
-        <v>0.57620998077638896</v>
+        <v>0.54704200004397796</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -14299,13 +14509,13 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>0.58379151659845396</v>
+        <v>0.57981293783868104</v>
       </c>
       <c r="C67">
         <v>66</v>
       </c>
       <c r="D67">
-        <v>0.57349459106536205</v>
+        <v>0.55043135657992504</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -14313,13 +14523,13 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>0.57982089190990305</v>
+        <v>0.57713306137931397</v>
       </c>
       <c r="C68">
         <v>67</v>
       </c>
       <c r="D68">
-        <v>0.57194400301579595</v>
+        <v>0.54964438714199304</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -14327,13 +14537,13 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>0.58140130410654001</v>
+        <v>0.57899113104956001</v>
       </c>
       <c r="C69">
         <v>68</v>
       </c>
       <c r="D69">
-        <v>0.56372406312326095</v>
+        <v>0.54721221855914803</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -14341,13 +14551,13 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>0.57696909372309102</v>
+        <v>0.57599198680548103</v>
       </c>
       <c r="C70">
         <v>69</v>
       </c>
       <c r="D70">
-        <v>0.56885973039349103</v>
+        <v>0.54483784949371905</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -14355,13 +14565,13 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>0.57696909372309102</v>
+        <v>0.57599198680548103</v>
       </c>
       <c r="C71">
         <v>70</v>
       </c>
       <c r="D71">
-        <v>0.56885973039349103</v>
+        <v>0.54483784949371905</v>
       </c>
     </row>
   </sheetData>

--- a/InitializationResults/WithTrack/Comparison of SPEA2 with SPEA2_SI for each generation (on average).xlsx
+++ b/InitializationResults/WithTrack/Comparison of SPEA2 with SPEA2_SI for each generation (on average).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="10995" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="10995" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="EPS" sheetId="1" r:id="rId1"/>
@@ -17,6 +17,7 @@
     <sheet name="HV" sheetId="3" r:id="rId3"/>
     <sheet name="IGD" sheetId="4" r:id="rId4"/>
     <sheet name="Spd" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="6">
   <si>
     <t>SPEA2</t>
   </si>
@@ -36,214 +37,16 @@
     <t>SPEA2_SI</t>
   </si>
   <si>
-    <t>1 0.657859671844684</t>
+    <t>SPEA2_SI_Eps</t>
   </si>
   <si>
-    <t>2 0.7687851902625128</t>
+    <t>SPEA2_SI_HV</t>
   </si>
   <si>
-    <t>3 0.7958571026972172</t>
+    <t>SPEA2_SI_IGD</t>
   </si>
   <si>
-    <t>4 0.7956027258673871</t>
-  </si>
-  <si>
-    <t>5 0.7903472497039553</t>
-  </si>
-  <si>
-    <t>6 0.8388715828811718</t>
-  </si>
-  <si>
-    <t>7 0.8481279571116311</t>
-  </si>
-  <si>
-    <t>8 0.8576840259744329</t>
-  </si>
-  <si>
-    <t>9 0.848052528681821</t>
-  </si>
-  <si>
-    <t>10 0.8112998193416588</t>
-  </si>
-  <si>
-    <t>11 0.7782125691316707</t>
-  </si>
-  <si>
-    <t>12 0.743891953250883</t>
-  </si>
-  <si>
-    <t>13 0.7264149703654817</t>
-  </si>
-  <si>
-    <t>14 0.7037820249004605</t>
-  </si>
-  <si>
-    <t>15 0.6897710507032292</t>
-  </si>
-  <si>
-    <t>16 0.6792730554997299</t>
-  </si>
-  <si>
-    <t>17 0.6703119256682791</t>
-  </si>
-  <si>
-    <t>18 0.6684944266480952</t>
-  </si>
-  <si>
-    <t>19 0.6644081142905648</t>
-  </si>
-  <si>
-    <t>20 0.6551997404378601</t>
-  </si>
-  <si>
-    <t>21 0.6505898835797393</t>
-  </si>
-  <si>
-    <t>22 0.6521148589876689</t>
-  </si>
-  <si>
-    <t>23 0.643747873115321</t>
-  </si>
-  <si>
-    <t>24 0.6384257353936403</t>
-  </si>
-  <si>
-    <t>25 0.6358761920102745</t>
-  </si>
-  <si>
-    <t>26 0.6254059861687505</t>
-  </si>
-  <si>
-    <t>27 0.6205928112468339</t>
-  </si>
-  <si>
-    <t>28 0.6169665202217068</t>
-  </si>
-  <si>
-    <t>29 0.6186172397165957</t>
-  </si>
-  <si>
-    <t>30 0.6199914964098251</t>
-  </si>
-  <si>
-    <t>31 0.619035319597225</t>
-  </si>
-  <si>
-    <t>32 0.6099213776525532</t>
-  </si>
-  <si>
-    <t>33 0.6067809082383067</t>
-  </si>
-  <si>
-    <t>34 0.6013722844358659</t>
-  </si>
-  <si>
-    <t>35 0.6066667821875183</t>
-  </si>
-  <si>
-    <t>36 0.6017981370478054</t>
-  </si>
-  <si>
-    <t>37 0.5990194350816828</t>
-  </si>
-  <si>
-    <t>38 0.5957329562085255</t>
-  </si>
-  <si>
-    <t>39 0.5945429067610194</t>
-  </si>
-  <si>
-    <t>40 0.5937290987341773</t>
-  </si>
-  <si>
-    <t>41 0.5924686339391932</t>
-  </si>
-  <si>
-    <t>42 0.5919607979306803</t>
-  </si>
-  <si>
-    <t>43 0.5928926922137343</t>
-  </si>
-  <si>
-    <t>44 0.5880168966159321</t>
-  </si>
-  <si>
-    <t>45 0.5861580441523648</t>
-  </si>
-  <si>
-    <t>46 0.5810801535771853</t>
-  </si>
-  <si>
-    <t>47 0.5721780079583937</t>
-  </si>
-  <si>
-    <t>48 0.571335344452591</t>
-  </si>
-  <si>
-    <t>49 0.5683832701954683</t>
-  </si>
-  <si>
-    <t>50 0.5684154366519051</t>
-  </si>
-  <si>
-    <t>51 0.5651624141140955</t>
-  </si>
-  <si>
-    <t>52 0.5624042447506735</t>
-  </si>
-  <si>
-    <t>53 0.5622944549126258</t>
-  </si>
-  <si>
-    <t>54 0.5621040306474071</t>
-  </si>
-  <si>
-    <t>55 0.5632085853123532</t>
-  </si>
-  <si>
-    <t>56 0.5591933793524096</t>
-  </si>
-  <si>
-    <t>57 0.5520190638678893</t>
-  </si>
-  <si>
-    <t>58 0.5518903044392609</t>
-  </si>
-  <si>
-    <t>59 0.5523580829226736</t>
-  </si>
-  <si>
-    <t>60 0.55403685691288</t>
-  </si>
-  <si>
-    <t>61 0.5511270806884873</t>
-  </si>
-  <si>
-    <t>62 0.5493814231779771</t>
-  </si>
-  <si>
-    <t>63 0.54790210541945</t>
-  </si>
-  <si>
-    <t>64 0.5452208153099943</t>
-  </si>
-  <si>
-    <t>65 0.5470420000439783</t>
-  </si>
-  <si>
-    <t>66 0.5504313565799258</t>
-  </si>
-  <si>
-    <t>67 0.549644387141993</t>
-  </si>
-  <si>
-    <t>68 0.547212218559148</t>
-  </si>
-  <si>
-    <t>69 0.5448378494937198</t>
-  </si>
-  <si>
-    <t>70 0.5448378494937198</t>
+    <t>SPEA2_SI_Spd</t>
   </si>
 </sst>
 </file>
@@ -279,9 +82,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1107,11 +913,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="364411552"/>
-        <c:axId val="364411944"/>
+        <c:axId val="117573368"/>
+        <c:axId val="117570232"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="364411552"/>
+        <c:axId val="117573368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1224,12 +1030,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="364411944"/>
+        <c:crossAx val="117570232"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="364411944"/>
+        <c:axId val="117570232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1286,7 +1092,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="364411552"/>
+        <c:crossAx val="117573368"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2172,11 +1978,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="364413904"/>
-        <c:axId val="364412336"/>
+        <c:axId val="117571016"/>
+        <c:axId val="117571800"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="364413904"/>
+        <c:axId val="117571016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2289,12 +2095,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="364412336"/>
+        <c:crossAx val="117571800"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="364412336"/>
+        <c:axId val="117571800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2351,7 +2157,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="364413904"/>
+        <c:crossAx val="117571016"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3237,11 +3043,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="364414688"/>
-        <c:axId val="364413512"/>
+        <c:axId val="117572192"/>
+        <c:axId val="117572584"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="364414688"/>
+        <c:axId val="117572192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3354,12 +3160,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="364413512"/>
+        <c:crossAx val="117572584"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="364413512"/>
+        <c:axId val="117572584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0.65000000000000013"/>
@@ -3417,7 +3223,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="364414688"/>
+        <c:crossAx val="117572192"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -4303,11 +4109,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="364415472"/>
-        <c:axId val="364416256"/>
+        <c:axId val="120952184"/>
+        <c:axId val="120951792"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="364415472"/>
+        <c:axId val="120952184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4420,12 +4226,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="364416256"/>
+        <c:crossAx val="120951792"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="364416256"/>
+        <c:axId val="120951792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4482,7 +4288,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="364415472"/>
+        <c:crossAx val="120952184"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5368,11 +5174,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="364406848"/>
-        <c:axId val="364407240"/>
+        <c:axId val="120957280"/>
+        <c:axId val="120956104"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="364406848"/>
+        <c:axId val="120957280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5485,12 +5291,12 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="364407240"/>
+        <c:crossAx val="120956104"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="364407240"/>
+        <c:axId val="120956104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5547,7 +5353,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="364406848"/>
+        <c:crossAx val="120957280"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -9565,14 +9371,14 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2"/>
+      <c r="D1" s="3"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
@@ -10570,14 +10376,14 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2"/>
+      <c r="D1" s="3"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
@@ -11575,14 +11381,14 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2"/>
+      <c r="D1" s="3"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
@@ -12580,14 +12386,14 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2"/>
+      <c r="D1" s="3"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
@@ -12596,8 +12402,8 @@
       <c r="B2">
         <v>0.26070199936674299</v>
       </c>
-      <c r="C2" t="s">
-        <v>2</v>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="D2">
         <v>0.12488100860519601</v>
@@ -12610,8 +12416,8 @@
       <c r="B3">
         <v>0.24569335427127501</v>
       </c>
-      <c r="C3" t="s">
-        <v>3</v>
+      <c r="C3">
+        <v>2</v>
       </c>
       <c r="D3">
         <v>0.114352284307533</v>
@@ -12624,8 +12430,8 @@
       <c r="B4">
         <v>0.21862555087809299</v>
       </c>
-      <c r="C4" t="s">
-        <v>4</v>
+      <c r="C4">
+        <v>3</v>
       </c>
       <c r="D4">
         <v>9.39288119990946E-2</v>
@@ -12638,8 +12444,8 @@
       <c r="B5">
         <v>0.20741124922750201</v>
       </c>
-      <c r="C5" t="s">
-        <v>5</v>
+      <c r="C5">
+        <v>4</v>
       </c>
       <c r="D5">
         <v>8.4781818453746202E-2</v>
@@ -12652,8 +12458,8 @@
       <c r="B6">
         <v>0.199080648969579</v>
       </c>
-      <c r="C6" t="s">
-        <v>6</v>
+      <c r="C6">
+        <v>5</v>
       </c>
       <c r="D6">
         <v>7.2137447445350306E-2</v>
@@ -12666,8 +12472,8 @@
       <c r="B7">
         <v>0.17663795023315901</v>
       </c>
-      <c r="C7" t="s">
-        <v>7</v>
+      <c r="C7">
+        <v>6</v>
       </c>
       <c r="D7">
         <v>6.2838439544546695E-2</v>
@@ -12680,8 +12486,8 @@
       <c r="B8">
         <v>0.176118040566489</v>
       </c>
-      <c r="C8" t="s">
-        <v>8</v>
+      <c r="C8">
+        <v>7</v>
       </c>
       <c r="D8">
         <v>5.5685630485540698E-2</v>
@@ -12694,8 +12500,8 @@
       <c r="B9">
         <v>0.17294063125426301</v>
       </c>
-      <c r="C9" t="s">
-        <v>9</v>
+      <c r="C9">
+        <v>8</v>
       </c>
       <c r="D9">
         <v>5.1725776191935802E-2</v>
@@ -12708,8 +12514,8 @@
       <c r="B10">
         <v>0.17127953041896701</v>
       </c>
-      <c r="C10" t="s">
-        <v>10</v>
+      <c r="C10">
+        <v>9</v>
       </c>
       <c r="D10">
         <v>4.6420094853518098E-2</v>
@@ -12722,8 +12528,8 @@
       <c r="B11">
         <v>0.16703731551889101</v>
       </c>
-      <c r="C11" t="s">
-        <v>11</v>
+      <c r="C11">
+        <v>10</v>
       </c>
       <c r="D11">
         <v>4.2840286682438902E-2</v>
@@ -12736,8 +12542,8 @@
       <c r="B12">
         <v>0.14737615503968399</v>
       </c>
-      <c r="C12" t="s">
-        <v>12</v>
+      <c r="C12">
+        <v>11</v>
       </c>
       <c r="D12">
         <v>4.1567348868420499E-2</v>
@@ -12750,8 +12556,8 @@
       <c r="B13">
         <v>0.139370501662094</v>
       </c>
-      <c r="C13" t="s">
-        <v>13</v>
+      <c r="C13">
+        <v>12</v>
       </c>
       <c r="D13">
         <v>3.95898280000039E-2</v>
@@ -12764,8 +12570,8 @@
       <c r="B14">
         <v>0.134198949147457</v>
       </c>
-      <c r="C14" t="s">
-        <v>14</v>
+      <c r="C14">
+        <v>13</v>
       </c>
       <c r="D14">
         <v>3.8296349145494103E-2</v>
@@ -12778,8 +12584,8 @@
       <c r="B15">
         <v>0.12848419495073399</v>
       </c>
-      <c r="C15" t="s">
-        <v>15</v>
+      <c r="C15">
+        <v>14</v>
       </c>
       <c r="D15">
         <v>3.5921620049663101E-2</v>
@@ -12792,8 +12598,8 @@
       <c r="B16">
         <v>0.124335792509762</v>
       </c>
-      <c r="C16" t="s">
-        <v>16</v>
+      <c r="C16">
+        <v>15</v>
       </c>
       <c r="D16">
         <v>3.5019330534999803E-2</v>
@@ -12806,8 +12612,8 @@
       <c r="B17">
         <v>0.112277800907381</v>
       </c>
-      <c r="C17" t="s">
-        <v>17</v>
+      <c r="C17">
+        <v>16</v>
       </c>
       <c r="D17">
         <v>3.4483123674123102E-2</v>
@@ -12820,8 +12626,8 @@
       <c r="B18">
         <v>0.111203285059739</v>
       </c>
-      <c r="C18" t="s">
-        <v>18</v>
+      <c r="C18">
+        <v>17</v>
       </c>
       <c r="D18">
         <v>3.3479557379548101E-2</v>
@@ -12834,8 +12640,8 @@
       <c r="B19">
         <v>0.10299640475463701</v>
       </c>
-      <c r="C19" t="s">
-        <v>19</v>
+      <c r="C19">
+        <v>18</v>
       </c>
       <c r="D19">
         <v>3.3276569864292102E-2</v>
@@ -12848,8 +12654,8 @@
       <c r="B20">
         <v>0.100019155921117</v>
       </c>
-      <c r="C20" t="s">
-        <v>20</v>
+      <c r="C20">
+        <v>19</v>
       </c>
       <c r="D20">
         <v>3.1870215221005999E-2</v>
@@ -12862,8 +12668,8 @@
       <c r="B21">
         <v>9.7091598652251795E-2</v>
       </c>
-      <c r="C21" t="s">
-        <v>21</v>
+      <c r="C21">
+        <v>20</v>
       </c>
       <c r="D21">
         <v>3.0563786365766701E-2</v>
@@ -12876,8 +12682,8 @@
       <c r="B22">
         <v>9.3586669734792793E-2</v>
       </c>
-      <c r="C22" t="s">
-        <v>22</v>
+      <c r="C22">
+        <v>21</v>
       </c>
       <c r="D22">
         <v>2.9963802381725399E-2</v>
@@ -12890,8 +12696,8 @@
       <c r="B23">
         <v>8.9667037502854E-2</v>
       </c>
-      <c r="C23" t="s">
-        <v>23</v>
+      <c r="C23">
+        <v>22</v>
       </c>
       <c r="D23">
         <v>2.8359916294929399E-2</v>
@@ -12904,8 +12710,8 @@
       <c r="B24">
         <v>8.7411760850928305E-2</v>
       </c>
-      <c r="C24" t="s">
-        <v>24</v>
+      <c r="C24">
+        <v>23</v>
       </c>
       <c r="D24">
         <v>2.8174266071330299E-2</v>
@@ -12918,8 +12724,8 @@
       <c r="B25">
         <v>8.3103209200931602E-2</v>
       </c>
-      <c r="C25" t="s">
-        <v>25</v>
+      <c r="C25">
+        <v>24</v>
       </c>
       <c r="D25">
         <v>2.5930126523408099E-2</v>
@@ -12932,8 +12738,8 @@
       <c r="B26">
         <v>7.5380475411144496E-2</v>
       </c>
-      <c r="C26" t="s">
-        <v>26</v>
+      <c r="C26">
+        <v>25</v>
       </c>
       <c r="D26">
         <v>2.5148921525704301E-2</v>
@@ -12946,8 +12752,8 @@
       <c r="B27">
         <v>7.2831769628116896E-2</v>
       </c>
-      <c r="C27" t="s">
-        <v>27</v>
+      <c r="C27">
+        <v>26</v>
       </c>
       <c r="D27">
         <v>2.43580490858449E-2</v>
@@ -12960,8 +12766,8 @@
       <c r="B28">
         <v>6.9804344280290004E-2</v>
       </c>
-      <c r="C28" t="s">
-        <v>28</v>
+      <c r="C28">
+        <v>27</v>
       </c>
       <c r="D28">
         <v>2.39200192322373E-2</v>
@@ -12974,8 +12780,8 @@
       <c r="B29">
         <v>6.5863900094645794E-2</v>
       </c>
-      <c r="C29" t="s">
-        <v>29</v>
+      <c r="C29">
+        <v>28</v>
       </c>
       <c r="D29">
         <v>2.38549444972334E-2</v>
@@ -12988,8 +12794,8 @@
       <c r="B30">
         <v>6.4905166309931595E-2</v>
       </c>
-      <c r="C30" t="s">
-        <v>30</v>
+      <c r="C30">
+        <v>29</v>
       </c>
       <c r="D30">
         <v>2.19312872326431E-2</v>
@@ -13002,8 +12808,8 @@
       <c r="B31">
         <v>6.3663639343299494E-2</v>
       </c>
-      <c r="C31" t="s">
-        <v>31</v>
+      <c r="C31">
+        <v>30</v>
       </c>
       <c r="D31">
         <v>2.1594455293049802E-2</v>
@@ -13016,8 +12822,8 @@
       <c r="B32">
         <v>6.1062337134811101E-2</v>
       </c>
-      <c r="C32" t="s">
-        <v>32</v>
+      <c r="C32">
+        <v>31</v>
       </c>
       <c r="D32">
         <v>2.10413824630626E-2</v>
@@ -13030,8 +12836,8 @@
       <c r="B33">
         <v>6.0974153083806201E-2</v>
       </c>
-      <c r="C33" t="s">
-        <v>33</v>
+      <c r="C33">
+        <v>32</v>
       </c>
       <c r="D33">
         <v>2.0514102597500399E-2</v>
@@ -13044,8 +12850,8 @@
       <c r="B34">
         <v>5.9697188375601701E-2</v>
       </c>
-      <c r="C34" t="s">
-        <v>34</v>
+      <c r="C34">
+        <v>33</v>
       </c>
       <c r="D34">
         <v>2.02481156285493E-2</v>
@@ -13058,8 +12864,8 @@
       <c r="B35">
         <v>5.8235627647746702E-2</v>
       </c>
-      <c r="C35" t="s">
-        <v>35</v>
+      <c r="C35">
+        <v>34</v>
       </c>
       <c r="D35">
         <v>1.9312676687198899E-2</v>
@@ -13072,8 +12878,8 @@
       <c r="B36">
         <v>5.7523394060693199E-2</v>
       </c>
-      <c r="C36" t="s">
-        <v>36</v>
+      <c r="C36">
+        <v>35</v>
       </c>
       <c r="D36">
         <v>1.90694781455286E-2</v>
@@ -13086,8 +12892,8 @@
       <c r="B37">
         <v>5.3070164930587797E-2</v>
       </c>
-      <c r="C37" t="s">
-        <v>37</v>
+      <c r="C37">
+        <v>36</v>
       </c>
       <c r="D37">
         <v>1.8689364112695499E-2</v>
@@ -13100,8 +12906,8 @@
       <c r="B38">
         <v>5.2148403946328997E-2</v>
       </c>
-      <c r="C38" t="s">
-        <v>38</v>
+      <c r="C38">
+        <v>37</v>
       </c>
       <c r="D38">
         <v>1.7678810341686502E-2</v>
@@ -13114,8 +12920,8 @@
       <c r="B39">
         <v>4.7935878989361698E-2</v>
       </c>
-      <c r="C39" t="s">
-        <v>39</v>
+      <c r="C39">
+        <v>38</v>
       </c>
       <c r="D39">
         <v>1.7586942160676199E-2</v>
@@ -13128,8 +12934,8 @@
       <c r="B40">
         <v>4.5717478012335201E-2</v>
       </c>
-      <c r="C40" t="s">
-        <v>40</v>
+      <c r="C40">
+        <v>39</v>
       </c>
       <c r="D40">
         <v>1.72203223041947E-2</v>
@@ -13142,8 +12948,8 @@
       <c r="B41">
         <v>4.2880229859735101E-2</v>
       </c>
-      <c r="C41" t="s">
-        <v>41</v>
+      <c r="C41">
+        <v>40</v>
       </c>
       <c r="D41">
         <v>1.6482968705710699E-2</v>
@@ -13156,8 +12962,8 @@
       <c r="B42">
         <v>4.23775604470732E-2</v>
       </c>
-      <c r="C42" t="s">
-        <v>42</v>
+      <c r="C42">
+        <v>41</v>
       </c>
       <c r="D42">
         <v>1.5700469331038899E-2</v>
@@ -13170,8 +12976,8 @@
       <c r="B43">
         <v>4.2565971503969298E-2</v>
       </c>
-      <c r="C43" t="s">
-        <v>43</v>
+      <c r="C43">
+        <v>42</v>
       </c>
       <c r="D43">
         <v>1.53200867184663E-2</v>
@@ -13184,8 +12990,8 @@
       <c r="B44">
         <v>4.0802560182957803E-2</v>
       </c>
-      <c r="C44" t="s">
-        <v>44</v>
+      <c r="C44">
+        <v>43</v>
       </c>
       <c r="D44">
         <v>1.4356114620424699E-2</v>
@@ -13198,8 +13004,8 @@
       <c r="B45">
         <v>3.8901584759120603E-2</v>
       </c>
-      <c r="C45" t="s">
-        <v>45</v>
+      <c r="C45">
+        <v>44</v>
       </c>
       <c r="D45">
         <v>1.4019312615009299E-2</v>
@@ -13212,8 +13018,8 @@
       <c r="B46">
         <v>3.7614529315325197E-2</v>
       </c>
-      <c r="C46" t="s">
-        <v>46</v>
+      <c r="C46">
+        <v>45</v>
       </c>
       <c r="D46">
         <v>1.38872225507841E-2</v>
@@ -13226,8 +13032,8 @@
       <c r="B47">
         <v>3.5281791151543902E-2</v>
       </c>
-      <c r="C47" t="s">
-        <v>47</v>
+      <c r="C47">
+        <v>46</v>
       </c>
       <c r="D47">
         <v>1.37061346806392E-2</v>
@@ -13240,8 +13046,8 @@
       <c r="B48">
         <v>3.4466552881035901E-2</v>
       </c>
-      <c r="C48" t="s">
-        <v>48</v>
+      <c r="C48">
+        <v>47</v>
       </c>
       <c r="D48">
         <v>1.3428926441428899E-2</v>
@@ -13254,8 +13060,8 @@
       <c r="B49">
         <v>3.3966376027798603E-2</v>
       </c>
-      <c r="C49" t="s">
-        <v>49</v>
+      <c r="C49">
+        <v>48</v>
       </c>
       <c r="D49">
         <v>1.3172627966171101E-2</v>
@@ -13268,8 +13074,8 @@
       <c r="B50">
         <v>3.2108879977000203E-2</v>
       </c>
-      <c r="C50" t="s">
-        <v>50</v>
+      <c r="C50">
+        <v>49</v>
       </c>
       <c r="D50">
         <v>1.2673635248618901E-2</v>
@@ -13282,8 +13088,8 @@
       <c r="B51">
         <v>3.1206307745831701E-2</v>
       </c>
-      <c r="C51" t="s">
-        <v>51</v>
+      <c r="C51">
+        <v>50</v>
       </c>
       <c r="D51">
         <v>1.2600264350854699E-2</v>
@@ -13296,8 +13102,8 @@
       <c r="B52">
         <v>3.0832354784116899E-2</v>
       </c>
-      <c r="C52" t="s">
-        <v>52</v>
+      <c r="C52">
+        <v>51</v>
       </c>
       <c r="D52">
         <v>1.25343739732538E-2</v>
@@ -13310,8 +13116,8 @@
       <c r="B53">
         <v>2.6932382254637899E-2</v>
       </c>
-      <c r="C53" t="s">
-        <v>53</v>
+      <c r="C53">
+        <v>52</v>
       </c>
       <c r="D53">
         <v>1.24396342929151E-2</v>
@@ -13324,8 +13130,8 @@
       <c r="B54">
         <v>2.6607946964281599E-2</v>
       </c>
-      <c r="C54" t="s">
-        <v>54</v>
+      <c r="C54">
+        <v>53</v>
       </c>
       <c r="D54">
         <v>1.22661371115567E-2</v>
@@ -13338,8 +13144,8 @@
       <c r="B55">
         <v>2.6603271204905601E-2</v>
       </c>
-      <c r="C55" t="s">
-        <v>55</v>
+      <c r="C55">
+        <v>54</v>
       </c>
       <c r="D55">
         <v>1.2211386046059E-2</v>
@@ -13352,8 +13158,8 @@
       <c r="B56">
         <v>2.6353743317352601E-2</v>
       </c>
-      <c r="C56" t="s">
-        <v>56</v>
+      <c r="C56">
+        <v>55</v>
       </c>
       <c r="D56">
         <v>1.22470248796145E-2</v>
@@ -13366,8 +13172,8 @@
       <c r="B57">
         <v>2.58008703583094E-2</v>
       </c>
-      <c r="C57" t="s">
-        <v>57</v>
+      <c r="C57">
+        <v>56</v>
       </c>
       <c r="D57">
         <v>1.19322102775377E-2</v>
@@ -13380,8 +13186,8 @@
       <c r="B58">
         <v>2.3430680760085899E-2</v>
       </c>
-      <c r="C58" t="s">
-        <v>58</v>
+      <c r="C58">
+        <v>57</v>
       </c>
       <c r="D58">
         <v>1.1278553370128E-2</v>
@@ -13394,8 +13200,8 @@
       <c r="B59">
         <v>2.3147045866607499E-2</v>
       </c>
-      <c r="C59" t="s">
-        <v>59</v>
+      <c r="C59">
+        <v>58</v>
       </c>
       <c r="D59">
         <v>1.1234938197526899E-2</v>
@@ -13408,8 +13214,8 @@
       <c r="B60">
         <v>2.2737615191229299E-2</v>
       </c>
-      <c r="C60" t="s">
-        <v>60</v>
+      <c r="C60">
+        <v>59</v>
       </c>
       <c r="D60">
         <v>1.1207669931559E-2</v>
@@ -13422,8 +13228,8 @@
       <c r="B61">
         <v>2.2375714118101901E-2</v>
       </c>
-      <c r="C61" t="s">
-        <v>61</v>
+      <c r="C61">
+        <v>60</v>
       </c>
       <c r="D61">
         <v>1.11214860857934E-2</v>
@@ -13436,8 +13242,8 @@
       <c r="B62">
         <v>2.06754057482436E-2</v>
       </c>
-      <c r="C62" t="s">
-        <v>62</v>
+      <c r="C62">
+        <v>61</v>
       </c>
       <c r="D62">
         <v>1.08408385522512E-2</v>
@@ -13450,8 +13256,8 @@
       <c r="B63">
         <v>2.0422532142128198E-2</v>
       </c>
-      <c r="C63" t="s">
-        <v>63</v>
+      <c r="C63">
+        <v>62</v>
       </c>
       <c r="D63">
         <v>1.0761187520518901E-2</v>
@@ -13464,8 +13270,8 @@
       <c r="B64">
         <v>1.9951577105645699E-2</v>
       </c>
-      <c r="C64" t="s">
-        <v>64</v>
+      <c r="C64">
+        <v>63</v>
       </c>
       <c r="D64">
         <v>1.06864347009179E-2</v>
@@ -13478,8 +13284,8 @@
       <c r="B65">
         <v>1.9839470893254101E-2</v>
       </c>
-      <c r="C65" t="s">
-        <v>65</v>
+      <c r="C65">
+        <v>64</v>
       </c>
       <c r="D65">
         <v>1.0582557118743501E-2</v>
@@ -13492,8 +13298,8 @@
       <c r="B66">
         <v>1.9473258059402001E-2</v>
       </c>
-      <c r="C66" t="s">
-        <v>66</v>
+      <c r="C66">
+        <v>65</v>
       </c>
       <c r="D66">
         <v>1.06353399980451E-2</v>
@@ -13506,8 +13312,8 @@
       <c r="B67">
         <v>1.90500853175011E-2</v>
       </c>
-      <c r="C67" t="s">
-        <v>67</v>
+      <c r="C67">
+        <v>66</v>
       </c>
       <c r="D67">
         <v>1.0642553813495E-2</v>
@@ -13520,8 +13326,8 @@
       <c r="B68">
         <v>1.80244992193348E-2</v>
       </c>
-      <c r="C68" t="s">
-        <v>68</v>
+      <c r="C68">
+        <v>67</v>
       </c>
       <c r="D68">
         <v>1.03163331230575E-2</v>
@@ -13534,8 +13340,8 @@
       <c r="B69">
         <v>1.80719191284298E-2</v>
       </c>
-      <c r="C69" t="s">
-        <v>69</v>
+      <c r="C69">
+        <v>68</v>
       </c>
       <c r="D69">
         <v>1.0170418752764599E-2</v>
@@ -13548,8 +13354,8 @@
       <c r="B70">
         <v>1.7957824332433502E-2</v>
       </c>
-      <c r="C70" t="s">
-        <v>70</v>
+      <c r="C70">
+        <v>69</v>
       </c>
       <c r="D70">
         <v>1.0049070616387001E-2</v>
@@ -13562,8 +13368,8 @@
       <c r="B71">
         <v>1.7957824332433502E-2</v>
       </c>
-      <c r="C71" t="s">
-        <v>71</v>
+      <c r="C71">
+        <v>70</v>
       </c>
       <c r="D71">
         <v>1.0049070616387001E-2</v>
@@ -13585,14 +13391,14 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2"/>
+      <c r="D1" s="3"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
@@ -14582,4 +14388,2716 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L71"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="3"/>
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="3"/>
+      <c r="I1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="3"/>
+      <c r="L1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>757.1</v>
+      </c>
+      <c r="C2">
+        <v>366.1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>0.68884288448075603</v>
+      </c>
+      <c r="F2">
+        <v>0.74643435415784498</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>0.26070199936674299</v>
+      </c>
+      <c r="I2">
+        <v>0.12488100860519601</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>0.766327328951392</v>
+      </c>
+      <c r="L2">
+        <v>0.65785967184468397</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>708.93333333333305</v>
+      </c>
+      <c r="C3">
+        <v>335.3</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>0.70314472428445796</v>
+      </c>
+      <c r="F3">
+        <v>0.75931399314186998</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>0.24569335427127501</v>
+      </c>
+      <c r="I3">
+        <v>0.114352284307533</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>0.81028008950052399</v>
+      </c>
+      <c r="L3">
+        <v>0.76878519026251202</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>646.6</v>
+      </c>
+      <c r="C4">
+        <v>278.7</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>0.71986048987838902</v>
+      </c>
+      <c r="F4">
+        <v>0.77501245376561301</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>0.21862555087809299</v>
+      </c>
+      <c r="I4">
+        <v>9.39288119990946E-2</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>0.82334868823943097</v>
+      </c>
+      <c r="L4">
+        <v>0.79585710269721699</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>603.96666666666601</v>
+      </c>
+      <c r="C5">
+        <v>252.933333333333</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>0.73356026085486203</v>
+      </c>
+      <c r="F5">
+        <v>0.78491030668751505</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>0.20741124922750201</v>
+      </c>
+      <c r="I5">
+        <v>8.4781818453746202E-2</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>0.83177270166272699</v>
+      </c>
+      <c r="L5">
+        <v>0.79560272586738701</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>554.93333333333305</v>
+      </c>
+      <c r="C6">
+        <v>226.56666666666601</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>0.74487886485935095</v>
+      </c>
+      <c r="F6">
+        <v>0.79369378338761998</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>0.199080648969579</v>
+      </c>
+      <c r="I6">
+        <v>7.2137447445350306E-2</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>0.83462490203242601</v>
+      </c>
+      <c r="L6">
+        <v>0.79034724970395498</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>503.7</v>
+      </c>
+      <c r="C7">
+        <v>195</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>0.75615098121000901</v>
+      </c>
+      <c r="F7">
+        <v>0.80046780221254299</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+      <c r="H7">
+        <v>0.17663795023315901</v>
+      </c>
+      <c r="I7">
+        <v>6.2838439544546695E-2</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>0.85029133127237899</v>
+      </c>
+      <c r="L7">
+        <v>0.83887158288117103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>468.9</v>
+      </c>
+      <c r="C8">
+        <v>166</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8">
+        <v>0.76574801368551804</v>
+      </c>
+      <c r="F8">
+        <v>0.80671418660317096</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+      <c r="H8">
+        <v>0.176118040566489</v>
+      </c>
+      <c r="I8">
+        <v>5.5685630485540698E-2</v>
+      </c>
+      <c r="J8">
+        <v>7</v>
+      </c>
+      <c r="K8">
+        <v>0.85302560474017097</v>
+      </c>
+      <c r="L8">
+        <v>0.84812795711163103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>452.33333333333297</v>
+      </c>
+      <c r="C9">
+        <v>158.833333333333</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+      <c r="E9">
+        <v>0.77178283252776803</v>
+      </c>
+      <c r="F9">
+        <v>0.81065807409239399</v>
+      </c>
+      <c r="G9">
+        <v>8</v>
+      </c>
+      <c r="H9">
+        <v>0.17294063125426301</v>
+      </c>
+      <c r="I9">
+        <v>5.1725776191935802E-2</v>
+      </c>
+      <c r="J9">
+        <v>8</v>
+      </c>
+      <c r="K9">
+        <v>0.85489516763487405</v>
+      </c>
+      <c r="L9">
+        <v>0.85768402597443205</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>428.06666666666598</v>
+      </c>
+      <c r="C10">
+        <v>145.9</v>
+      </c>
+      <c r="D10">
+        <v>9</v>
+      </c>
+      <c r="E10">
+        <v>0.77817696783470003</v>
+      </c>
+      <c r="F10">
+        <v>0.81460987400212603</v>
+      </c>
+      <c r="G10">
+        <v>9</v>
+      </c>
+      <c r="H10">
+        <v>0.17127953041896701</v>
+      </c>
+      <c r="I10">
+        <v>4.6420094853518098E-2</v>
+      </c>
+      <c r="J10">
+        <v>9</v>
+      </c>
+      <c r="K10">
+        <v>0.87489784121783898</v>
+      </c>
+      <c r="L10">
+        <v>0.84805252868182102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>410.3</v>
+      </c>
+      <c r="C11">
+        <v>136.433333333333</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11">
+        <v>0.78325327465915395</v>
+      </c>
+      <c r="F11">
+        <v>0.81743322825359399</v>
+      </c>
+      <c r="G11">
+        <v>10</v>
+      </c>
+      <c r="H11">
+        <v>0.16703731551889101</v>
+      </c>
+      <c r="I11">
+        <v>4.2840286682438902E-2</v>
+      </c>
+      <c r="J11">
+        <v>10</v>
+      </c>
+      <c r="K11">
+        <v>0.87315759285928796</v>
+      </c>
+      <c r="L11">
+        <v>0.81129981934165796</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>371.433333333333</v>
+      </c>
+      <c r="C12">
+        <v>134.13333333333301</v>
+      </c>
+      <c r="D12">
+        <v>11</v>
+      </c>
+      <c r="E12">
+        <v>0.789628746784378</v>
+      </c>
+      <c r="F12">
+        <v>0.81965974495805904</v>
+      </c>
+      <c r="G12">
+        <v>11</v>
+      </c>
+      <c r="H12">
+        <v>0.14737615503968399</v>
+      </c>
+      <c r="I12">
+        <v>4.1567348868420499E-2</v>
+      </c>
+      <c r="J12">
+        <v>11</v>
+      </c>
+      <c r="K12">
+        <v>0.87854885324290199</v>
+      </c>
+      <c r="L12">
+        <v>0.77821256913167003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>356.86666666666599</v>
+      </c>
+      <c r="C13">
+        <v>123.766666666666</v>
+      </c>
+      <c r="D13">
+        <v>12</v>
+      </c>
+      <c r="E13">
+        <v>0.79348987699242701</v>
+      </c>
+      <c r="F13">
+        <v>0.82182871758003595</v>
+      </c>
+      <c r="G13">
+        <v>12</v>
+      </c>
+      <c r="H13">
+        <v>0.139370501662094</v>
+      </c>
+      <c r="I13">
+        <v>3.95898280000039E-2</v>
+      </c>
+      <c r="J13">
+        <v>12</v>
+      </c>
+      <c r="K13">
+        <v>0.89383434590856503</v>
+      </c>
+      <c r="L13">
+        <v>0.74389195325088298</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>342.933333333333</v>
+      </c>
+      <c r="C14">
+        <v>120.06666666666599</v>
+      </c>
+      <c r="D14">
+        <v>13</v>
+      </c>
+      <c r="E14">
+        <v>0.79695635557753997</v>
+      </c>
+      <c r="F14">
+        <v>0.82322835140788697</v>
+      </c>
+      <c r="G14">
+        <v>13</v>
+      </c>
+      <c r="H14">
+        <v>0.134198949147457</v>
+      </c>
+      <c r="I14">
+        <v>3.8296349145494103E-2</v>
+      </c>
+      <c r="J14">
+        <v>13</v>
+      </c>
+      <c r="K14">
+        <v>0.87751344808780096</v>
+      </c>
+      <c r="L14">
+        <v>0.72641497036548097</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>324.86666666666599</v>
+      </c>
+      <c r="C15">
+        <v>114.833333333333</v>
+      </c>
+      <c r="D15">
+        <v>14</v>
+      </c>
+      <c r="E15">
+        <v>0.80026903103066105</v>
+      </c>
+      <c r="F15">
+        <v>0.82444137961872299</v>
+      </c>
+      <c r="G15">
+        <v>14</v>
+      </c>
+      <c r="H15">
+        <v>0.12848419495073399</v>
+      </c>
+      <c r="I15">
+        <v>3.5921620049663101E-2</v>
+      </c>
+      <c r="J15">
+        <v>14</v>
+      </c>
+      <c r="K15">
+        <v>0.84461262772019896</v>
+      </c>
+      <c r="L15">
+        <v>0.70378202490046005</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>308.03333333333302</v>
+      </c>
+      <c r="C16">
+        <v>113.266666666666</v>
+      </c>
+      <c r="D16">
+        <v>15</v>
+      </c>
+      <c r="E16">
+        <v>0.803299557952454</v>
+      </c>
+      <c r="F16">
+        <v>0.82533250506185296</v>
+      </c>
+      <c r="G16">
+        <v>15</v>
+      </c>
+      <c r="H16">
+        <v>0.124335792509762</v>
+      </c>
+      <c r="I16">
+        <v>3.5019330534999803E-2</v>
+      </c>
+      <c r="J16">
+        <v>15</v>
+      </c>
+      <c r="K16">
+        <v>0.82511048118899399</v>
+      </c>
+      <c r="L16">
+        <v>0.68977105070322897</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>279.60000000000002</v>
+      </c>
+      <c r="C17">
+        <v>111.56666666666599</v>
+      </c>
+      <c r="D17">
+        <v>16</v>
+      </c>
+      <c r="E17">
+        <v>0.80729497224190105</v>
+      </c>
+      <c r="F17">
+        <v>0.82594094923894001</v>
+      </c>
+      <c r="G17">
+        <v>16</v>
+      </c>
+      <c r="H17">
+        <v>0.112277800907381</v>
+      </c>
+      <c r="I17">
+        <v>3.4483123674123102E-2</v>
+      </c>
+      <c r="J17">
+        <v>16</v>
+      </c>
+      <c r="K17">
+        <v>0.81221615539852599</v>
+      </c>
+      <c r="L17">
+        <v>0.67927305549972905</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>275.26666666666603</v>
+      </c>
+      <c r="C18">
+        <v>106.2</v>
+      </c>
+      <c r="D18">
+        <v>17</v>
+      </c>
+      <c r="E18">
+        <v>0.80871178458094495</v>
+      </c>
+      <c r="F18">
+        <v>0.82669980800590204</v>
+      </c>
+      <c r="G18">
+        <v>17</v>
+      </c>
+      <c r="H18">
+        <v>0.111203285059739</v>
+      </c>
+      <c r="I18">
+        <v>3.3479557379548101E-2</v>
+      </c>
+      <c r="J18">
+        <v>17</v>
+      </c>
+      <c r="K18">
+        <v>0.80125635003364204</v>
+      </c>
+      <c r="L18">
+        <v>0.67031192566827902</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>260.96666666666601</v>
+      </c>
+      <c r="C19">
+        <v>104.333333333333</v>
+      </c>
+      <c r="D19">
+        <v>18</v>
+      </c>
+      <c r="E19">
+        <v>0.81094378583295901</v>
+      </c>
+      <c r="F19">
+        <v>0.82725116223501205</v>
+      </c>
+      <c r="G19">
+        <v>18</v>
+      </c>
+      <c r="H19">
+        <v>0.10299640475463701</v>
+      </c>
+      <c r="I19">
+        <v>3.3276569864292102E-2</v>
+      </c>
+      <c r="J19">
+        <v>18</v>
+      </c>
+      <c r="K19">
+        <v>0.79037244782224803</v>
+      </c>
+      <c r="L19">
+        <v>0.668494426648095</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>254</v>
+      </c>
+      <c r="C20">
+        <v>101.23333333333299</v>
+      </c>
+      <c r="D20">
+        <v>19</v>
+      </c>
+      <c r="E20">
+        <v>0.81264051969756002</v>
+      </c>
+      <c r="F20">
+        <v>0.82772129625360003</v>
+      </c>
+      <c r="G20">
+        <v>19</v>
+      </c>
+      <c r="H20">
+        <v>0.100019155921117</v>
+      </c>
+      <c r="I20">
+        <v>3.1870215221005999E-2</v>
+      </c>
+      <c r="J20">
+        <v>19</v>
+      </c>
+      <c r="K20">
+        <v>0.77868012774593098</v>
+      </c>
+      <c r="L20">
+        <v>0.66440811429056401</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>244.166666666666</v>
+      </c>
+      <c r="C21">
+        <v>98.033333333333303</v>
+      </c>
+      <c r="D21">
+        <v>20</v>
+      </c>
+      <c r="E21">
+        <v>0.81417664714586901</v>
+      </c>
+      <c r="F21">
+        <v>0.82829726981318996</v>
+      </c>
+      <c r="G21">
+        <v>20</v>
+      </c>
+      <c r="H21">
+        <v>9.7091598652251795E-2</v>
+      </c>
+      <c r="I21">
+        <v>3.0563786365766701E-2</v>
+      </c>
+      <c r="J21">
+        <v>20</v>
+      </c>
+      <c r="K21">
+        <v>0.76376931486520105</v>
+      </c>
+      <c r="L21">
+        <v>0.65519974043786</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>236.06666666666601</v>
+      </c>
+      <c r="C22">
+        <v>95.633333333333297</v>
+      </c>
+      <c r="D22">
+        <v>21</v>
+      </c>
+      <c r="E22">
+        <v>0.81553098105630295</v>
+      </c>
+      <c r="F22">
+        <v>0.82874028676149003</v>
+      </c>
+      <c r="G22">
+        <v>21</v>
+      </c>
+      <c r="H22">
+        <v>9.3586669734792793E-2</v>
+      </c>
+      <c r="I22">
+        <v>2.9963802381725399E-2</v>
+      </c>
+      <c r="J22">
+        <v>21</v>
+      </c>
+      <c r="K22">
+        <v>0.75265977772009596</v>
+      </c>
+      <c r="L22">
+        <v>0.65058988357973901</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>226.73333333333301</v>
+      </c>
+      <c r="C23">
+        <v>91.966666666666598</v>
+      </c>
+      <c r="D23">
+        <v>22</v>
+      </c>
+      <c r="E23">
+        <v>0.81682080166618398</v>
+      </c>
+      <c r="F23">
+        <v>0.82912818750026196</v>
+      </c>
+      <c r="G23">
+        <v>22</v>
+      </c>
+      <c r="H23">
+        <v>8.9667037502854E-2</v>
+      </c>
+      <c r="I23">
+        <v>2.8359916294929399E-2</v>
+      </c>
+      <c r="J23">
+        <v>22</v>
+      </c>
+      <c r="K23">
+        <v>0.73639902090263898</v>
+      </c>
+      <c r="L23">
+        <v>0.65211485898766797</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>221.1</v>
+      </c>
+      <c r="C24">
+        <v>90.3333333333333</v>
+      </c>
+      <c r="D24">
+        <v>23</v>
+      </c>
+      <c r="E24">
+        <v>0.81811677929202498</v>
+      </c>
+      <c r="F24">
+        <v>0.82951138096016597</v>
+      </c>
+      <c r="G24">
+        <v>23</v>
+      </c>
+      <c r="H24">
+        <v>8.7411760850928305E-2</v>
+      </c>
+      <c r="I24">
+        <v>2.8174266071330299E-2</v>
+      </c>
+      <c r="J24">
+        <v>23</v>
+      </c>
+      <c r="K24">
+        <v>0.72735402655937997</v>
+      </c>
+      <c r="L24">
+        <v>0.643747873115321</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>212.766666666666</v>
+      </c>
+      <c r="C25">
+        <v>83.433333333333294</v>
+      </c>
+      <c r="D25">
+        <v>24</v>
+      </c>
+      <c r="E25">
+        <v>0.819071745567297</v>
+      </c>
+      <c r="F25">
+        <v>0.82998467645361496</v>
+      </c>
+      <c r="G25">
+        <v>24</v>
+      </c>
+      <c r="H25">
+        <v>8.3103209200931602E-2</v>
+      </c>
+      <c r="I25">
+        <v>2.5930126523408099E-2</v>
+      </c>
+      <c r="J25">
+        <v>24</v>
+      </c>
+      <c r="K25">
+        <v>0.72298202648197096</v>
+      </c>
+      <c r="L25">
+        <v>0.63842573539364</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>199.2</v>
+      </c>
+      <c r="C26">
+        <v>81.066666666666606</v>
+      </c>
+      <c r="D26">
+        <v>25</v>
+      </c>
+      <c r="E26">
+        <v>0.82057292212501398</v>
+      </c>
+      <c r="F26">
+        <v>0.83030682375528697</v>
+      </c>
+      <c r="G26">
+        <v>25</v>
+      </c>
+      <c r="H26">
+        <v>7.5380475411144496E-2</v>
+      </c>
+      <c r="I26">
+        <v>2.5148921525704301E-2</v>
+      </c>
+      <c r="J26">
+        <v>25</v>
+      </c>
+      <c r="K26">
+        <v>0.72048916237364102</v>
+      </c>
+      <c r="L26">
+        <v>0.63587619201027401</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>195.7</v>
+      </c>
+      <c r="C27">
+        <v>79.400000000000006</v>
+      </c>
+      <c r="D27">
+        <v>26</v>
+      </c>
+      <c r="E27">
+        <v>0.82133555370175504</v>
+      </c>
+      <c r="F27">
+        <v>0.83061500642076302</v>
+      </c>
+      <c r="G27">
+        <v>26</v>
+      </c>
+      <c r="H27">
+        <v>7.2831769628116896E-2</v>
+      </c>
+      <c r="I27">
+        <v>2.43580490858449E-2</v>
+      </c>
+      <c r="J27">
+        <v>26</v>
+      </c>
+      <c r="K27">
+        <v>0.71743209919367501</v>
+      </c>
+      <c r="L27">
+        <v>0.62540598616874998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>187.06666666666601</v>
+      </c>
+      <c r="C28">
+        <v>78</v>
+      </c>
+      <c r="D28">
+        <v>27</v>
+      </c>
+      <c r="E28">
+        <v>0.82206040478056897</v>
+      </c>
+      <c r="F28">
+        <v>0.83086354026496301</v>
+      </c>
+      <c r="G28">
+        <v>27</v>
+      </c>
+      <c r="H28">
+        <v>6.9804344280290004E-2</v>
+      </c>
+      <c r="I28">
+        <v>2.39200192322373E-2</v>
+      </c>
+      <c r="J28">
+        <v>27</v>
+      </c>
+      <c r="K28">
+        <v>0.71099587521481999</v>
+      </c>
+      <c r="L28">
+        <v>0.62059281124683296</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>178.5</v>
+      </c>
+      <c r="C29">
+        <v>77.566666666666606</v>
+      </c>
+      <c r="D29">
+        <v>28</v>
+      </c>
+      <c r="E29">
+        <v>0.82307323827250001</v>
+      </c>
+      <c r="F29">
+        <v>0.83104494080182001</v>
+      </c>
+      <c r="G29">
+        <v>28</v>
+      </c>
+      <c r="H29">
+        <v>6.5863900094645794E-2</v>
+      </c>
+      <c r="I29">
+        <v>2.38549444972334E-2</v>
+      </c>
+      <c r="J29">
+        <v>28</v>
+      </c>
+      <c r="K29">
+        <v>0.70323181416706104</v>
+      </c>
+      <c r="L29">
+        <v>0.61696652022170595</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>176.56666666666601</v>
+      </c>
+      <c r="C30">
+        <v>73.433333333333294</v>
+      </c>
+      <c r="D30">
+        <v>29</v>
+      </c>
+      <c r="E30">
+        <v>0.82339367383640205</v>
+      </c>
+      <c r="F30">
+        <v>0.83136824963983602</v>
+      </c>
+      <c r="G30">
+        <v>29</v>
+      </c>
+      <c r="H30">
+        <v>6.4905166309931595E-2</v>
+      </c>
+      <c r="I30">
+        <v>2.19312872326431E-2</v>
+      </c>
+      <c r="J30">
+        <v>29</v>
+      </c>
+      <c r="K30">
+        <v>0.69503470929871403</v>
+      </c>
+      <c r="L30">
+        <v>0.61861723971659499</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>174.23333333333301</v>
+      </c>
+      <c r="C31">
+        <v>72.233333333333306</v>
+      </c>
+      <c r="D31">
+        <v>30</v>
+      </c>
+      <c r="E31">
+        <v>0.82387204340966902</v>
+      </c>
+      <c r="F31">
+        <v>0.83157100323204003</v>
+      </c>
+      <c r="G31">
+        <v>30</v>
+      </c>
+      <c r="H31">
+        <v>6.3663639343299494E-2</v>
+      </c>
+      <c r="I31">
+        <v>2.1594455293049802E-2</v>
+      </c>
+      <c r="J31">
+        <v>30</v>
+      </c>
+      <c r="K31">
+        <v>0.68906973129747895</v>
+      </c>
+      <c r="L31">
+        <v>0.61999149640982498</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>166.63333333333301</v>
+      </c>
+      <c r="C32">
+        <v>70.400000000000006</v>
+      </c>
+      <c r="D32">
+        <v>31</v>
+      </c>
+      <c r="E32">
+        <v>0.82464370527648401</v>
+      </c>
+      <c r="F32">
+        <v>0.83179488281233604</v>
+      </c>
+      <c r="G32">
+        <v>31</v>
+      </c>
+      <c r="H32">
+        <v>6.1062337134811101E-2</v>
+      </c>
+      <c r="I32">
+        <v>2.10413824630626E-2</v>
+      </c>
+      <c r="J32">
+        <v>31</v>
+      </c>
+      <c r="K32">
+        <v>0.68477729271847698</v>
+      </c>
+      <c r="L32">
+        <v>0.61903531959722502</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>166.433333333333</v>
+      </c>
+      <c r="C33">
+        <v>68.566666666666606</v>
+      </c>
+      <c r="D33">
+        <v>32</v>
+      </c>
+      <c r="E33">
+        <v>0.82487748848245002</v>
+      </c>
+      <c r="F33">
+        <v>0.83195484296028599</v>
+      </c>
+      <c r="G33">
+        <v>32</v>
+      </c>
+      <c r="H33">
+        <v>6.0974153083806201E-2</v>
+      </c>
+      <c r="I33">
+        <v>2.0514102597500399E-2</v>
+      </c>
+      <c r="J33">
+        <v>32</v>
+      </c>
+      <c r="K33">
+        <v>0.67884544887061504</v>
+      </c>
+      <c r="L33">
+        <v>0.60992137765255305</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>163.266666666666</v>
+      </c>
+      <c r="C34">
+        <v>67.5</v>
+      </c>
+      <c r="D34">
+        <v>33</v>
+      </c>
+      <c r="E34">
+        <v>0.82528001759247205</v>
+      </c>
+      <c r="F34">
+        <v>0.83210599115206196</v>
+      </c>
+      <c r="G34">
+        <v>33</v>
+      </c>
+      <c r="H34">
+        <v>5.9697188375601701E-2</v>
+      </c>
+      <c r="I34">
+        <v>2.02481156285493E-2</v>
+      </c>
+      <c r="J34">
+        <v>33</v>
+      </c>
+      <c r="K34">
+        <v>0.67226918092824095</v>
+      </c>
+      <c r="L34">
+        <v>0.60678090823830599</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>159.86666666666599</v>
+      </c>
+      <c r="C35">
+        <v>64.400000000000006</v>
+      </c>
+      <c r="D35">
+        <v>34</v>
+      </c>
+      <c r="E35">
+        <v>0.82580955589836902</v>
+      </c>
+      <c r="F35">
+        <v>0.83229159243313999</v>
+      </c>
+      <c r="G35">
+        <v>34</v>
+      </c>
+      <c r="H35">
+        <v>5.8235627647746702E-2</v>
+      </c>
+      <c r="I35">
+        <v>1.9312676687198899E-2</v>
+      </c>
+      <c r="J35">
+        <v>34</v>
+      </c>
+      <c r="K35">
+        <v>0.66651065380779495</v>
+      </c>
+      <c r="L35">
+        <v>0.60137228443586499</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>156.9</v>
+      </c>
+      <c r="C36">
+        <v>63.2</v>
+      </c>
+      <c r="D36">
+        <v>35</v>
+      </c>
+      <c r="E36">
+        <v>0.82609773044531698</v>
+      </c>
+      <c r="F36">
+        <v>0.83238044559678204</v>
+      </c>
+      <c r="G36">
+        <v>35</v>
+      </c>
+      <c r="H36">
+        <v>5.7523394060693199E-2</v>
+      </c>
+      <c r="I36">
+        <v>1.90694781455286E-2</v>
+      </c>
+      <c r="J36">
+        <v>35</v>
+      </c>
+      <c r="K36">
+        <v>0.65983022103404199</v>
+      </c>
+      <c r="L36">
+        <v>0.60666678218751802</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>148.6</v>
+      </c>
+      <c r="C37">
+        <v>60.266666666666602</v>
+      </c>
+      <c r="D37">
+        <v>36</v>
+      </c>
+      <c r="E37">
+        <v>0.826434837985766</v>
+      </c>
+      <c r="F37">
+        <v>0.83254586409221298</v>
+      </c>
+      <c r="G37">
+        <v>36</v>
+      </c>
+      <c r="H37">
+        <v>5.3070164930587797E-2</v>
+      </c>
+      <c r="I37">
+        <v>1.8689364112695499E-2</v>
+      </c>
+      <c r="J37">
+        <v>36</v>
+      </c>
+      <c r="K37">
+        <v>0.65960200845087402</v>
+      </c>
+      <c r="L37">
+        <v>0.60179813704780505</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>146.86666666666599</v>
+      </c>
+      <c r="C38">
+        <v>57.1666666666666</v>
+      </c>
+      <c r="D38">
+        <v>37</v>
+      </c>
+      <c r="E38">
+        <v>0.82666695312074201</v>
+      </c>
+      <c r="F38">
+        <v>0.83271850507303102</v>
+      </c>
+      <c r="G38">
+        <v>37</v>
+      </c>
+      <c r="H38">
+        <v>5.2148403946328997E-2</v>
+      </c>
+      <c r="I38">
+        <v>1.7678810341686502E-2</v>
+      </c>
+      <c r="J38">
+        <v>37</v>
+      </c>
+      <c r="K38">
+        <v>0.66029389869948496</v>
+      </c>
+      <c r="L38">
+        <v>0.59901943508168198</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>138.6</v>
+      </c>
+      <c r="C39">
+        <v>57</v>
+      </c>
+      <c r="D39">
+        <v>38</v>
+      </c>
+      <c r="E39">
+        <v>0.82731439173223598</v>
+      </c>
+      <c r="F39">
+        <v>0.83280352429340199</v>
+      </c>
+      <c r="G39">
+        <v>38</v>
+      </c>
+      <c r="H39">
+        <v>4.7935878989361698E-2</v>
+      </c>
+      <c r="I39">
+        <v>1.7586942160676199E-2</v>
+      </c>
+      <c r="J39">
+        <v>38</v>
+      </c>
+      <c r="K39">
+        <v>0.66043748103364397</v>
+      </c>
+      <c r="L39">
+        <v>0.59573295620852496</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>134.03333333333299</v>
+      </c>
+      <c r="C40">
+        <v>55.4</v>
+      </c>
+      <c r="D40">
+        <v>39</v>
+      </c>
+      <c r="E40">
+        <v>0.82782725806158597</v>
+      </c>
+      <c r="F40">
+        <v>0.83294113578342399</v>
+      </c>
+      <c r="G40">
+        <v>39</v>
+      </c>
+      <c r="H40">
+        <v>4.5717478012335201E-2</v>
+      </c>
+      <c r="I40">
+        <v>1.72203223041947E-2</v>
+      </c>
+      <c r="J40">
+        <v>39</v>
+      </c>
+      <c r="K40">
+        <v>0.65410736450821005</v>
+      </c>
+      <c r="L40">
+        <v>0.59454290676101895</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>127.533333333333</v>
+      </c>
+      <c r="C41">
+        <v>53.366666666666603</v>
+      </c>
+      <c r="D41">
+        <v>40</v>
+      </c>
+      <c r="E41">
+        <v>0.82825522743754898</v>
+      </c>
+      <c r="F41">
+        <v>0.833089436901154</v>
+      </c>
+      <c r="G41">
+        <v>40</v>
+      </c>
+      <c r="H41">
+        <v>4.2880229859735101E-2</v>
+      </c>
+      <c r="I41">
+        <v>1.6482968705710699E-2</v>
+      </c>
+      <c r="J41">
+        <v>40</v>
+      </c>
+      <c r="K41">
+        <v>0.64995627790920696</v>
+      </c>
+      <c r="L41">
+        <v>0.59372909873417701</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>125.5</v>
+      </c>
+      <c r="C42">
+        <v>50.5</v>
+      </c>
+      <c r="D42">
+        <v>41</v>
+      </c>
+      <c r="E42">
+        <v>0.82855214407382405</v>
+      </c>
+      <c r="F42">
+        <v>0.83321780850055904</v>
+      </c>
+      <c r="G42">
+        <v>41</v>
+      </c>
+      <c r="H42">
+        <v>4.23775604470732E-2</v>
+      </c>
+      <c r="I42">
+        <v>1.5700469331038899E-2</v>
+      </c>
+      <c r="J42">
+        <v>41</v>
+      </c>
+      <c r="K42">
+        <v>0.644044497560191</v>
+      </c>
+      <c r="L42">
+        <v>0.59246863393919302</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>122.9</v>
+      </c>
+      <c r="C43">
+        <v>49.466666666666598</v>
+      </c>
+      <c r="D43">
+        <v>42</v>
+      </c>
+      <c r="E43">
+        <v>0.82875297632771405</v>
+      </c>
+      <c r="F43">
+        <v>0.83327315177734196</v>
+      </c>
+      <c r="G43">
+        <v>42</v>
+      </c>
+      <c r="H43">
+        <v>4.2565971503969298E-2</v>
+      </c>
+      <c r="I43">
+        <v>1.53200867184663E-2</v>
+      </c>
+      <c r="J43">
+        <v>42</v>
+      </c>
+      <c r="K43">
+        <v>0.640681368796576</v>
+      </c>
+      <c r="L43">
+        <v>0.59196079793068002</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>115.666666666666</v>
+      </c>
+      <c r="C44">
+        <v>45.733333333333299</v>
+      </c>
+      <c r="D44">
+        <v>43</v>
+      </c>
+      <c r="E44">
+        <v>0.82916370605899203</v>
+      </c>
+      <c r="F44">
+        <v>0.83338489506698099</v>
+      </c>
+      <c r="G44">
+        <v>43</v>
+      </c>
+      <c r="H44">
+        <v>4.0802560182957803E-2</v>
+      </c>
+      <c r="I44">
+        <v>1.4356114620424699E-2</v>
+      </c>
+      <c r="J44">
+        <v>43</v>
+      </c>
+      <c r="K44">
+        <v>0.63750494020191495</v>
+      </c>
+      <c r="L44">
+        <v>0.59289269221373397</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>108.966666666666</v>
+      </c>
+      <c r="C45">
+        <v>43.966666666666598</v>
+      </c>
+      <c r="D45">
+        <v>44</v>
+      </c>
+      <c r="E45">
+        <v>0.82944491138787702</v>
+      </c>
+      <c r="F45">
+        <v>0.83347724157300995</v>
+      </c>
+      <c r="G45">
+        <v>44</v>
+      </c>
+      <c r="H45">
+        <v>3.8901584759120603E-2</v>
+      </c>
+      <c r="I45">
+        <v>1.4019312615009299E-2</v>
+      </c>
+      <c r="J45">
+        <v>44</v>
+      </c>
+      <c r="K45">
+        <v>0.63198466526347996</v>
+      </c>
+      <c r="L45">
+        <v>0.58801689661593204</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>106.533333333333</v>
+      </c>
+      <c r="C46">
+        <v>43.733333333333299</v>
+      </c>
+      <c r="D46">
+        <v>45</v>
+      </c>
+      <c r="E46">
+        <v>0.82972256224088103</v>
+      </c>
+      <c r="F46">
+        <v>0.83356081978964403</v>
+      </c>
+      <c r="G46">
+        <v>45</v>
+      </c>
+      <c r="H46">
+        <v>3.7614529315325197E-2</v>
+      </c>
+      <c r="I46">
+        <v>1.38872225507841E-2</v>
+      </c>
+      <c r="J46">
+        <v>45</v>
+      </c>
+      <c r="K46">
+        <v>0.63054092663786498</v>
+      </c>
+      <c r="L46">
+        <v>0.58615804415236406</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>98</v>
+      </c>
+      <c r="C47">
+        <v>43.133333333333297</v>
+      </c>
+      <c r="D47">
+        <v>46</v>
+      </c>
+      <c r="E47">
+        <v>0.83030089380658301</v>
+      </c>
+      <c r="F47">
+        <v>0.83365713997264002</v>
+      </c>
+      <c r="G47">
+        <v>46</v>
+      </c>
+      <c r="H47">
+        <v>3.5281791151543902E-2</v>
+      </c>
+      <c r="I47">
+        <v>1.37061346806392E-2</v>
+      </c>
+      <c r="J47">
+        <v>46</v>
+      </c>
+      <c r="K47">
+        <v>0.62997831697649098</v>
+      </c>
+      <c r="L47">
+        <v>0.58108015357718501</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>95.533333333333303</v>
+      </c>
+      <c r="C48">
+        <v>42.1666666666666</v>
+      </c>
+      <c r="D48">
+        <v>47</v>
+      </c>
+      <c r="E48">
+        <v>0.83046756990527404</v>
+      </c>
+      <c r="F48">
+        <v>0.83373079709689202</v>
+      </c>
+      <c r="G48">
+        <v>47</v>
+      </c>
+      <c r="H48">
+        <v>3.4466552881035901E-2</v>
+      </c>
+      <c r="I48">
+        <v>1.3428926441428899E-2</v>
+      </c>
+      <c r="J48">
+        <v>47</v>
+      </c>
+      <c r="K48">
+        <v>0.62615828724044498</v>
+      </c>
+      <c r="L48">
+        <v>0.57217800795839302</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>94.866666666666603</v>
+      </c>
+      <c r="C49">
+        <v>41.433333333333302</v>
+      </c>
+      <c r="D49">
+        <v>48</v>
+      </c>
+      <c r="E49">
+        <v>0.83060876207124401</v>
+      </c>
+      <c r="F49">
+        <v>0.83379931027447896</v>
+      </c>
+      <c r="G49">
+        <v>48</v>
+      </c>
+      <c r="H49">
+        <v>3.3966376027798603E-2</v>
+      </c>
+      <c r="I49">
+        <v>1.3172627966171101E-2</v>
+      </c>
+      <c r="J49">
+        <v>48</v>
+      </c>
+      <c r="K49">
+        <v>0.62734237468041298</v>
+      </c>
+      <c r="L49">
+        <v>0.57133534445259104</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>91.133333333333297</v>
+      </c>
+      <c r="C50">
+        <v>40.566666666666599</v>
+      </c>
+      <c r="D50">
+        <v>49</v>
+      </c>
+      <c r="E50">
+        <v>0.83083917420180597</v>
+      </c>
+      <c r="F50">
+        <v>0.83387454813616202</v>
+      </c>
+      <c r="G50">
+        <v>49</v>
+      </c>
+      <c r="H50">
+        <v>3.2108879977000203E-2</v>
+      </c>
+      <c r="I50">
+        <v>1.2673635248618901E-2</v>
+      </c>
+      <c r="J50">
+        <v>49</v>
+      </c>
+      <c r="K50">
+        <v>0.62414815142538005</v>
+      </c>
+      <c r="L50">
+        <v>0.56838327019546797</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>88.233333333333306</v>
+      </c>
+      <c r="C51">
+        <v>40.5</v>
+      </c>
+      <c r="D51">
+        <v>50</v>
+      </c>
+      <c r="E51">
+        <v>0.83109091318764605</v>
+      </c>
+      <c r="F51">
+        <v>0.83399286764284597</v>
+      </c>
+      <c r="G51">
+        <v>50</v>
+      </c>
+      <c r="H51">
+        <v>3.1206307745831701E-2</v>
+      </c>
+      <c r="I51">
+        <v>1.2600264350854699E-2</v>
+      </c>
+      <c r="J51">
+        <v>50</v>
+      </c>
+      <c r="K51">
+        <v>0.61887902899456004</v>
+      </c>
+      <c r="L51">
+        <v>0.56841543665190497</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>87</v>
+      </c>
+      <c r="C52">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="D52">
+        <v>51</v>
+      </c>
+      <c r="E52">
+        <v>0.83117102426196199</v>
+      </c>
+      <c r="F52">
+        <v>0.83408932755953602</v>
+      </c>
+      <c r="G52">
+        <v>51</v>
+      </c>
+      <c r="H52">
+        <v>3.0832354784116899E-2</v>
+      </c>
+      <c r="I52">
+        <v>1.25343739732538E-2</v>
+      </c>
+      <c r="J52">
+        <v>51</v>
+      </c>
+      <c r="K52">
+        <v>0.61278252378585596</v>
+      </c>
+      <c r="L52">
+        <v>0.56516241411409496</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>75.5</v>
+      </c>
+      <c r="C53">
+        <v>39.466666666666598</v>
+      </c>
+      <c r="D53">
+        <v>52</v>
+      </c>
+      <c r="E53">
+        <v>0.83154242769130604</v>
+      </c>
+      <c r="F53">
+        <v>0.83415639100003203</v>
+      </c>
+      <c r="G53">
+        <v>52</v>
+      </c>
+      <c r="H53">
+        <v>2.6932382254637899E-2</v>
+      </c>
+      <c r="I53">
+        <v>1.24396342929151E-2</v>
+      </c>
+      <c r="J53">
+        <v>52</v>
+      </c>
+      <c r="K53">
+        <v>0.61126520231954695</v>
+      </c>
+      <c r="L53">
+        <v>0.56240424475067297</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>74.066666666666606</v>
+      </c>
+      <c r="C54">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="D54">
+        <v>53</v>
+      </c>
+      <c r="E54">
+        <v>0.83161246047283099</v>
+      </c>
+      <c r="F54">
+        <v>0.83416208514812396</v>
+      </c>
+      <c r="G54">
+        <v>53</v>
+      </c>
+      <c r="H54">
+        <v>2.6607946964281599E-2</v>
+      </c>
+      <c r="I54">
+        <v>1.22661371115567E-2</v>
+      </c>
+      <c r="J54">
+        <v>53</v>
+      </c>
+      <c r="K54">
+        <v>0.60928406811964597</v>
+      </c>
+      <c r="L54">
+        <v>0.56229445491262497</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>73.7</v>
+      </c>
+      <c r="C55">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="D55">
+        <v>54</v>
+      </c>
+      <c r="E55">
+        <v>0.83168864153695798</v>
+      </c>
+      <c r="F55">
+        <v>0.83422113136783804</v>
+      </c>
+      <c r="G55">
+        <v>54</v>
+      </c>
+      <c r="H55">
+        <v>2.6603271204905601E-2</v>
+      </c>
+      <c r="I55">
+        <v>1.2211386046059E-2</v>
+      </c>
+      <c r="J55">
+        <v>54</v>
+      </c>
+      <c r="K55">
+        <v>0.60615338415291198</v>
+      </c>
+      <c r="L55">
+        <v>0.56210403064740699</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>72.966666666666598</v>
+      </c>
+      <c r="C56">
+        <v>37.933333333333302</v>
+      </c>
+      <c r="D56">
+        <v>55</v>
+      </c>
+      <c r="E56">
+        <v>0.831793153607854</v>
+      </c>
+      <c r="F56">
+        <v>0.83425073744457801</v>
+      </c>
+      <c r="G56">
+        <v>55</v>
+      </c>
+      <c r="H56">
+        <v>2.6353743317352601E-2</v>
+      </c>
+      <c r="I56">
+        <v>1.22470248796145E-2</v>
+      </c>
+      <c r="J56">
+        <v>55</v>
+      </c>
+      <c r="K56">
+        <v>0.60342455516900795</v>
+      </c>
+      <c r="L56">
+        <v>0.56320858531235296</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>71.733333333333306</v>
+      </c>
+      <c r="C57">
+        <v>36.533333333333303</v>
+      </c>
+      <c r="D57">
+        <v>56</v>
+      </c>
+      <c r="E57">
+        <v>0.83189143879594196</v>
+      </c>
+      <c r="F57">
+        <v>0.83431475294383906</v>
+      </c>
+      <c r="G57">
+        <v>56</v>
+      </c>
+      <c r="H57">
+        <v>2.58008703583094E-2</v>
+      </c>
+      <c r="I57">
+        <v>1.19322102775377E-2</v>
+      </c>
+      <c r="J57">
+        <v>56</v>
+      </c>
+      <c r="K57">
+        <v>0.60255006745098805</v>
+      </c>
+      <c r="L57">
+        <v>0.55919337935240898</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>68.066666666666606</v>
+      </c>
+      <c r="C58">
+        <v>34.3333333333333</v>
+      </c>
+      <c r="D58">
+        <v>57</v>
+      </c>
+      <c r="E58">
+        <v>0.83228256214306695</v>
+      </c>
+      <c r="F58">
+        <v>0.83441267133097696</v>
+      </c>
+      <c r="G58">
+        <v>57</v>
+      </c>
+      <c r="H58">
+        <v>2.3430680760085899E-2</v>
+      </c>
+      <c r="I58">
+        <v>1.1278553370128E-2</v>
+      </c>
+      <c r="J58">
+        <v>57</v>
+      </c>
+      <c r="K58">
+        <v>0.59902987081057002</v>
+      </c>
+      <c r="L58">
+        <v>0.55201906386788901</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>66.266666666666595</v>
+      </c>
+      <c r="C59">
+        <v>33.966666666666598</v>
+      </c>
+      <c r="D59">
+        <v>58</v>
+      </c>
+      <c r="E59">
+        <v>0.83239659357197004</v>
+      </c>
+      <c r="F59">
+        <v>0.83444036480275896</v>
+      </c>
+      <c r="G59">
+        <v>58</v>
+      </c>
+      <c r="H59">
+        <v>2.3147045866607499E-2</v>
+      </c>
+      <c r="I59">
+        <v>1.1234938197526899E-2</v>
+      </c>
+      <c r="J59">
+        <v>58</v>
+      </c>
+      <c r="K59">
+        <v>0.59621234806785195</v>
+      </c>
+      <c r="L59">
+        <v>0.55189030443926002</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>65.266666666666595</v>
+      </c>
+      <c r="C60">
+        <v>33.5</v>
+      </c>
+      <c r="D60">
+        <v>59</v>
+      </c>
+      <c r="E60">
+        <v>0.83247404097271405</v>
+      </c>
+      <c r="F60">
+        <v>0.834482520712027</v>
+      </c>
+      <c r="G60">
+        <v>59</v>
+      </c>
+      <c r="H60">
+        <v>2.2737615191229299E-2</v>
+      </c>
+      <c r="I60">
+        <v>1.1207669931559E-2</v>
+      </c>
+      <c r="J60">
+        <v>59</v>
+      </c>
+      <c r="K60">
+        <v>0.59379821765230101</v>
+      </c>
+      <c r="L60">
+        <v>0.55235808292267297</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>64</v>
+      </c>
+      <c r="C61">
+        <v>32.6666666666666</v>
+      </c>
+      <c r="D61">
+        <v>60</v>
+      </c>
+      <c r="E61">
+        <v>0.83261602787407696</v>
+      </c>
+      <c r="F61">
+        <v>0.83451293899087098</v>
+      </c>
+      <c r="G61">
+        <v>60</v>
+      </c>
+      <c r="H61">
+        <v>2.2375714118101901E-2</v>
+      </c>
+      <c r="I61">
+        <v>1.11214860857934E-2</v>
+      </c>
+      <c r="J61">
+        <v>60</v>
+      </c>
+      <c r="K61">
+        <v>0.590989217035776</v>
+      </c>
+      <c r="L61">
+        <v>0.55403685691287996</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>60.933333333333302</v>
+      </c>
+      <c r="C62">
+        <v>31.1666666666666</v>
+      </c>
+      <c r="D62">
+        <v>61</v>
+      </c>
+      <c r="E62">
+        <v>0.832739168193257</v>
+      </c>
+      <c r="F62">
+        <v>0.83456176718410002</v>
+      </c>
+      <c r="G62">
+        <v>61</v>
+      </c>
+      <c r="H62">
+        <v>2.06754057482436E-2</v>
+      </c>
+      <c r="I62">
+        <v>1.08408385522512E-2</v>
+      </c>
+      <c r="J62">
+        <v>61</v>
+      </c>
+      <c r="K62">
+        <v>0.59087769919958799</v>
+      </c>
+      <c r="L62">
+        <v>0.55112708068848704</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>59.9</v>
+      </c>
+      <c r="C63">
+        <v>30.1</v>
+      </c>
+      <c r="D63">
+        <v>62</v>
+      </c>
+      <c r="E63">
+        <v>0.83275938591232801</v>
+      </c>
+      <c r="F63">
+        <v>0.83457872736139405</v>
+      </c>
+      <c r="G63">
+        <v>62</v>
+      </c>
+      <c r="H63">
+        <v>2.0422532142128198E-2</v>
+      </c>
+      <c r="I63">
+        <v>1.0761187520518901E-2</v>
+      </c>
+      <c r="J63">
+        <v>62</v>
+      </c>
+      <c r="K63">
+        <v>0.58865451722088302</v>
+      </c>
+      <c r="L63">
+        <v>0.549381423177977</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>58</v>
+      </c>
+      <c r="C64">
+        <v>29.8</v>
+      </c>
+      <c r="D64">
+        <v>63</v>
+      </c>
+      <c r="E64">
+        <v>0.832899748409481</v>
+      </c>
+      <c r="F64">
+        <v>0.83461091851150104</v>
+      </c>
+      <c r="G64">
+        <v>63</v>
+      </c>
+      <c r="H64">
+        <v>1.9951577105645699E-2</v>
+      </c>
+      <c r="I64">
+        <v>1.06864347009179E-2</v>
+      </c>
+      <c r="J64">
+        <v>63</v>
+      </c>
+      <c r="K64">
+        <v>0.58208297535624598</v>
+      </c>
+      <c r="L64">
+        <v>0.54790210541944995</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>56.733333333333299</v>
+      </c>
+      <c r="C65">
+        <v>29.3</v>
+      </c>
+      <c r="D65">
+        <v>64</v>
+      </c>
+      <c r="E65">
+        <v>0.83297343173380201</v>
+      </c>
+      <c r="F65">
+        <v>0.83465841050126599</v>
+      </c>
+      <c r="G65">
+        <v>64</v>
+      </c>
+      <c r="H65">
+        <v>1.9839470893254101E-2</v>
+      </c>
+      <c r="I65">
+        <v>1.0582557118743501E-2</v>
+      </c>
+      <c r="J65">
+        <v>64</v>
+      </c>
+      <c r="K65">
+        <v>0.58584005692535002</v>
+      </c>
+      <c r="L65">
+        <v>0.545220815309994</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>55.8333333333333</v>
+      </c>
+      <c r="C66">
+        <v>29.1666666666666</v>
+      </c>
+      <c r="D66">
+        <v>65</v>
+      </c>
+      <c r="E66">
+        <v>0.83307887827378602</v>
+      </c>
+      <c r="F66">
+        <v>0.83467005206477496</v>
+      </c>
+      <c r="G66">
+        <v>65</v>
+      </c>
+      <c r="H66">
+        <v>1.9473258059402001E-2</v>
+      </c>
+      <c r="I66">
+        <v>1.06353399980451E-2</v>
+      </c>
+      <c r="J66">
+        <v>65</v>
+      </c>
+      <c r="K66">
+        <v>0.58307570775395201</v>
+      </c>
+      <c r="L66">
+        <v>0.54704200004397796</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>54.233333333333299</v>
+      </c>
+      <c r="C67">
+        <v>29.066666666666599</v>
+      </c>
+      <c r="D67">
+        <v>66</v>
+      </c>
+      <c r="E67">
+        <v>0.83316967024245103</v>
+      </c>
+      <c r="F67">
+        <v>0.83466167677639902</v>
+      </c>
+      <c r="G67">
+        <v>66</v>
+      </c>
+      <c r="H67">
+        <v>1.90500853175011E-2</v>
+      </c>
+      <c r="I67">
+        <v>1.0642553813495E-2</v>
+      </c>
+      <c r="J67">
+        <v>66</v>
+      </c>
+      <c r="K67">
+        <v>0.57981293783868104</v>
+      </c>
+      <c r="L67">
+        <v>0.55043135657992504</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>50</v>
+      </c>
+      <c r="C68">
+        <v>27.3</v>
+      </c>
+      <c r="D68">
+        <v>67</v>
+      </c>
+      <c r="E68">
+        <v>0.83329008575456898</v>
+      </c>
+      <c r="F68">
+        <v>0.83467927448867896</v>
+      </c>
+      <c r="G68">
+        <v>67</v>
+      </c>
+      <c r="H68">
+        <v>1.80244992193348E-2</v>
+      </c>
+      <c r="I68">
+        <v>1.03163331230575E-2</v>
+      </c>
+      <c r="J68">
+        <v>67</v>
+      </c>
+      <c r="K68">
+        <v>0.57713306137931397</v>
+      </c>
+      <c r="L68">
+        <v>0.54964438714199304</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>50</v>
+      </c>
+      <c r="C69">
+        <v>26.8666666666666</v>
+      </c>
+      <c r="D69">
+        <v>68</v>
+      </c>
+      <c r="E69">
+        <v>0.83333733321036696</v>
+      </c>
+      <c r="F69">
+        <v>0.83468283769791496</v>
+      </c>
+      <c r="G69">
+        <v>68</v>
+      </c>
+      <c r="H69">
+        <v>1.80719191284298E-2</v>
+      </c>
+      <c r="I69">
+        <v>1.0170418752764599E-2</v>
+      </c>
+      <c r="J69">
+        <v>68</v>
+      </c>
+      <c r="K69">
+        <v>0.57899113104956001</v>
+      </c>
+      <c r="L69">
+        <v>0.54721221855914803</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>49.7</v>
+      </c>
+      <c r="C70">
+        <v>26.3333333333333</v>
+      </c>
+      <c r="D70">
+        <v>69</v>
+      </c>
+      <c r="E70">
+        <v>0.83340637912266802</v>
+      </c>
+      <c r="F70">
+        <v>0.83473400643054396</v>
+      </c>
+      <c r="G70">
+        <v>69</v>
+      </c>
+      <c r="H70">
+        <v>1.7957824332433502E-2</v>
+      </c>
+      <c r="I70">
+        <v>1.0049070616387001E-2</v>
+      </c>
+      <c r="J70">
+        <v>69</v>
+      </c>
+      <c r="K70">
+        <v>0.57599198680548103</v>
+      </c>
+      <c r="L70">
+        <v>0.54483784949371905</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>49.7</v>
+      </c>
+      <c r="C71">
+        <v>26.3333333333333</v>
+      </c>
+      <c r="D71">
+        <v>70</v>
+      </c>
+      <c r="E71">
+        <v>0.83340637912266802</v>
+      </c>
+      <c r="F71">
+        <v>0.83473400643054396</v>
+      </c>
+      <c r="G71">
+        <v>70</v>
+      </c>
+      <c r="H71">
+        <v>1.7957824332433502E-2</v>
+      </c>
+      <c r="I71">
+        <v>1.0049070616387001E-2</v>
+      </c>
+      <c r="J71">
+        <v>70</v>
+      </c>
+      <c r="K71">
+        <v>0.57599198680548103</v>
+      </c>
+      <c r="L71">
+        <v>0.54483784949371905</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>